--- a/DocumentsAndReports/worklog/WorkLog_DesmondChua_W26_4495_S2.xlsx
+++ b/DocumentsAndReports/worklog/WorkLog_DesmondChua_W26_4495_S2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4f25ae689476683/Desmond_New/Winter2026_DouglasCollege/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{08655895-4010-492B-B73A-F5D36A9F8AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B371C32D-278F-4B5E-8FE8-78F7DCF23A27}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="8_{08655895-4010-492B-B73A-F5D36A9F8AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F0C5E6B-2E78-41F0-8095-29D68DBF36E4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="413">
   <si>
     <t>CSIS 4495 - Applied Research Project</t>
   </si>
@@ -1178,6 +1178,102 @@
   </si>
   <si>
     <t>Mid-term Video Demonstration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   3E: Multi-Turn Chatbot Enhancement</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>Sprint 3</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>Post-cruise return: Reviewed Sprint 3 roadmap tracker, organized project files and mockups into consolidated project workspace</t>
+  </si>
+  <si>
+    <t>Studied existing 1_Home.py placeholder code, compared against UI mockup, identified all sections needing rebuild</t>
+  </si>
+  <si>
+    <t>Rebuilt Home page Welcome Header section with personalized greeting using session_state username, added health overview subtitle</t>
+  </si>
+  <si>
+    <t>Created Quick Actions row (3 styled cards with icons: Check Symptoms, Find Facility, Health Info) with st.page_link() navigation</t>
+  </si>
+  <si>
+    <t>Created My Health Summary card querying SQLite database via get_assessment_stats() - displays total assessments, last check relative time, most common symptom with percentage</t>
+  </si>
+  <si>
+    <t>Created Recent Activity list showing 3 most recent assessments from database with color-coded urgency dots (green/yellow/red)</t>
+  </si>
+  <si>
+    <t>Added BC Health Tip of the Day banner with rotating BC-specific health tips and Find Nearest Pharmacy navigation button</t>
+  </si>
+  <si>
+    <t>Added most_common_symptom_count to get_assessment_stats() in database.py for percentage calculation (backward-compatible change)</t>
+  </si>
+  <si>
+    <t>Verified all dashboard data against SQLite database using Python queries - confirmed 33 assessments, Chest pain 33%, recent activity entries all match live data</t>
+  </si>
+  <si>
+    <t>Git commit - 'Sprint 3A: Rebuild Home Dashboard to match UI mockup'</t>
+  </si>
+  <si>
+    <t>Studied My Personal Health Dashboard mockup (2 pages), identified 5 sections: stat cards, trend chart, symptoms breakdown, assessment history table, date filter</t>
+  </si>
+  <si>
+    <t>Built dashboard layout with 4 stat summary cards (Total Checks, This Month, Most Common, Avg Urgency) with colored icon boxes and status indicators</t>
+  </si>
+  <si>
+    <t>Created Plotly filled area chart for Symptom Trends Over Time - grouped assessments by month, teal color scheme, responsive layout with export_plotly_chart()</t>
+  </si>
+  <si>
+    <t>Created Plotly donut pie chart for Symptoms Breakdown - shows distribution of primary symptoms with percentages, rare symptoms grouped as Other</t>
+  </si>
+  <si>
+    <t>Created Assessment History HTML table with styled colored badges (green Home Care, yellow Walk-in Clinic, orange Urgent Care, red Emergency)</t>
+  </si>
+  <si>
+    <t>Implemented date filter dropdown (All Time, Last 6 Months, Last 3 Months, Last Year) that filters all dashboard sections simultaneously</t>
+  </si>
+  <si>
+    <t>Fixed UI issues - Plotly X-axis tick intervals (dtick=5), donut chart label clipping (moved labels inside slices with legend below), button styling for Export Report and New Assessment</t>
+  </si>
+  <si>
+    <t>Automated data verification against SQLite - confirmed all 4 stat cards, trend chart, donut chart percentages, and history table entries match real database values</t>
+  </si>
+  <si>
+    <t>Git commit - 'Sprint 3B: Rebuild My Dashboard with Plotly charts, date filter, and live data'</t>
+  </si>
+  <si>
+    <t>Added auto-redirect in app.py to route users to Home Dashboard after login instead of showing old placeholder page; Git commit</t>
+  </si>
+  <si>
+    <t>Researched agentic AI frameworks in healthcare triage (reviewed Thamma 2025, Wang et al. 2024); Evaluated feasibility for project integration</t>
+  </si>
+  <si>
+    <t>Updated work log, prepared Progress Report 2, updated task tracker with Sprint 3A and 3B completion status</t>
+  </si>
+  <si>
+    <t>3A</t>
+  </si>
+  <si>
+    <t>3B</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1281,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -1318,7 +1414,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1441,6 +1537,12 @@
         <fgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -1547,7 +1649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1720,6 +1822,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1740,7 +1861,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1748,23 +1868,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2248,43 +2353,43 @@
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="27.21875" style="69" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.21875" style="69" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="20" customWidth="1"/>
     <col min="7" max="7" width="209.77734375" style="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="94"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="102"/>
     </row>
     <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="94"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="102"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="90"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="99"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F4" s="17"/>
@@ -4886,7 +4991,7 @@
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="100">
+      <c r="A119" s="84">
         <v>46066</v>
       </c>
       <c r="B119" s="24" t="s">
@@ -4895,19 +5000,19 @@
       <c r="C119" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D119" s="101">
+      <c r="D119" s="85">
         <v>4</v>
       </c>
       <c r="E119" s="83" t="s">
-        <v>211</v>
-      </c>
-      <c r="F119" s="103"/>
+        <v>37</v>
+      </c>
+      <c r="F119" s="87"/>
       <c r="G119" s="21" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="100">
+      <c r="A120" s="84">
         <v>46066</v>
       </c>
       <c r="B120" s="24" t="s">
@@ -4916,214 +5021,518 @@
       <c r="C120" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="102">
+      <c r="D120" s="86">
         <v>2</v>
       </c>
       <c r="E120" s="83" t="s">
-        <v>211</v>
-      </c>
-      <c r="F120" s="103"/>
+        <v>37</v>
+      </c>
+      <c r="F120" s="87"/>
       <c r="G120" s="21" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="1"/>
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="27"/>
-      <c r="F121" s="18"/>
-      <c r="G121" s="21"/>
+      <c r="A121" s="84" t="s">
+        <v>382</v>
+      </c>
+      <c r="B121" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D121" s="86">
+        <v>1</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F121" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="G121" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="2"/>
-      <c r="E122" s="25"/>
-      <c r="F122" s="18"/>
-      <c r="G122" s="21"/>
+      <c r="A122" s="84" t="s">
+        <v>382</v>
+      </c>
+      <c r="B122" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D122" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="E122" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F122" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="G122" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="2"/>
-      <c r="E123" s="25"/>
-      <c r="F123" s="18"/>
-      <c r="G123" s="21"/>
+      <c r="A123" s="84" t="s">
+        <v>382</v>
+      </c>
+      <c r="B123" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D123" s="86">
+        <v>1</v>
+      </c>
+      <c r="E123" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F123" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="G123" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="25"/>
-      <c r="F124" s="18"/>
-      <c r="G124" s="21"/>
+      <c r="A124" s="84" t="s">
+        <v>384</v>
+      </c>
+      <c r="B124" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D124" s="86">
+        <v>0.75</v>
+      </c>
+      <c r="E124" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F124" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="G124" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="2"/>
-      <c r="E125" s="25"/>
-      <c r="F125" s="18"/>
-      <c r="G125" s="21"/>
+      <c r="A125" s="84" t="s">
+        <v>384</v>
+      </c>
+      <c r="B125" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D125" s="86">
+        <v>1</v>
+      </c>
+      <c r="E125" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F125" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="G125" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="2"/>
-      <c r="E126" s="25"/>
-      <c r="F126" s="18"/>
-      <c r="G126" s="21"/>
+      <c r="A126" s="84" t="s">
+        <v>384</v>
+      </c>
+      <c r="B126" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D126" s="86">
+        <v>0.75</v>
+      </c>
+      <c r="E126" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F126" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="G126" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="1"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="2"/>
-      <c r="E127" s="25"/>
-      <c r="F127" s="18"/>
-      <c r="G127" s="21"/>
+      <c r="A127" s="84" t="s">
+        <v>385</v>
+      </c>
+      <c r="B127" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D127" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="E127" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F127" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="G127" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="1"/>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="2"/>
-      <c r="E128" s="25"/>
-      <c r="F128" s="18"/>
-      <c r="G128" s="21"/>
+      <c r="A128" s="84" t="s">
+        <v>385</v>
+      </c>
+      <c r="B128" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D128" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="E128" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F128" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="G128" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="1"/>
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="25"/>
-      <c r="F129" s="18"/>
-      <c r="G129" s="21"/>
+      <c r="A129" s="84" t="s">
+        <v>385</v>
+      </c>
+      <c r="B129" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D129" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="E129" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F129" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="G129" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="1"/>
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="D130" s="2"/>
-      <c r="E130" s="25"/>
-      <c r="F130" s="18"/>
-      <c r="G130" s="21"/>
+      <c r="A130" s="84" t="s">
+        <v>385</v>
+      </c>
+      <c r="B130" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D130" s="86">
+        <v>0.25</v>
+      </c>
+      <c r="E130" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F130" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="G130" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="25"/>
-      <c r="F131" s="18"/>
-      <c r="G131" s="21"/>
+      <c r="A131" s="84" t="s">
+        <v>386</v>
+      </c>
+      <c r="B131" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D131" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="E131" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F131" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G131" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="1"/>
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="25"/>
-      <c r="F132" s="18"/>
-      <c r="G132" s="21"/>
+      <c r="A132" s="84" t="s">
+        <v>386</v>
+      </c>
+      <c r="B132" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D132" s="86">
+        <v>1.5</v>
+      </c>
+      <c r="E132" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F132" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G132" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="1"/>
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="25"/>
-      <c r="F133" s="18"/>
-      <c r="G133" s="21"/>
+      <c r="A133" s="84" t="s">
+        <v>387</v>
+      </c>
+      <c r="B133" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D133" s="86">
+        <v>1.5</v>
+      </c>
+      <c r="E133" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F133" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G133" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" s="1"/>
-      <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
-      <c r="D134" s="2"/>
-      <c r="E134" s="25"/>
-      <c r="F134" s="18"/>
-      <c r="G134" s="21"/>
+      <c r="A134" s="84" t="s">
+        <v>387</v>
+      </c>
+      <c r="B134" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D134" s="86">
+        <v>1</v>
+      </c>
+      <c r="E134" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F134" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G134" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="1"/>
-      <c r="B135" s="1"/>
-      <c r="C135" s="1"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="25"/>
-      <c r="F135" s="18"/>
-      <c r="G135" s="21"/>
+      <c r="A135" s="84" t="s">
+        <v>387</v>
+      </c>
+      <c r="B135" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D135" s="86">
+        <v>1</v>
+      </c>
+      <c r="E135" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F135" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G135" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" s="1"/>
-      <c r="B136" s="1"/>
-      <c r="C136" s="1"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="25"/>
-      <c r="F136" s="18"/>
-      <c r="G136" s="21"/>
+      <c r="A136" s="84" t="s">
+        <v>388</v>
+      </c>
+      <c r="B136" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D136" s="86">
+        <v>0.75</v>
+      </c>
+      <c r="E136" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F136" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G136" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="1"/>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="25"/>
-      <c r="F137" s="18"/>
-      <c r="G137" s="21"/>
+      <c r="A137" s="84" t="s">
+        <v>388</v>
+      </c>
+      <c r="B137" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D137" s="86">
+        <v>0.75</v>
+      </c>
+      <c r="E137" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F137" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G137" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="1"/>
-      <c r="B138" s="1"/>
-      <c r="C138" s="1"/>
-      <c r="D138" s="2"/>
-      <c r="E138" s="25"/>
-      <c r="F138" s="18"/>
-      <c r="G138" s="21"/>
+      <c r="A138" s="84" t="s">
+        <v>388</v>
+      </c>
+      <c r="B138" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D138" s="86">
+        <v>0.5</v>
+      </c>
+      <c r="E138" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F138" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G138" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="1"/>
-      <c r="B139" s="1"/>
-      <c r="C139" s="1"/>
-      <c r="D139" s="2"/>
-      <c r="E139" s="25"/>
-      <c r="F139" s="18"/>
-      <c r="G139" s="21"/>
+      <c r="A139" s="84" t="s">
+        <v>388</v>
+      </c>
+      <c r="B139" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D139" s="86">
+        <v>0.25</v>
+      </c>
+      <c r="E139" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F139" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G139" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" s="1"/>
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="25"/>
-      <c r="F140" s="18"/>
-      <c r="G140" s="21"/>
+      <c r="A140" s="84" t="s">
+        <v>388</v>
+      </c>
+      <c r="B140" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D140" s="86">
+        <v>0.25</v>
+      </c>
+      <c r="E140" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="F140" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G140" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141" s="1"/>
-      <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="25"/>
+      <c r="A141" s="84" t="s">
+        <v>388</v>
+      </c>
+      <c r="B141" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D141" s="86">
+        <v>0.75</v>
+      </c>
+      <c r="E141" s="25" t="s">
+        <v>17</v>
+      </c>
       <c r="F141" s="18"/>
-      <c r="G141" s="21"/>
+      <c r="G141" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" s="1"/>
-      <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="25"/>
+      <c r="A142" s="84" t="s">
+        <v>388</v>
+      </c>
+      <c r="B142" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D142" s="86">
+        <v>0.75</v>
+      </c>
+      <c r="E142" s="25" t="s">
+        <v>37</v>
+      </c>
       <c r="F142" s="18"/>
-      <c r="G142" s="21"/>
+      <c r="G142" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
@@ -5171,15 +5580,15 @@
       <c r="G147" s="21"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148" s="84" t="s">
+      <c r="A148" s="93" t="s">
         <v>137</v>
       </c>
-      <c r="B148" s="85"/>
-      <c r="C148" s="85"/>
-      <c r="D148" s="86"/>
+      <c r="B148" s="94"/>
+      <c r="C148" s="94"/>
+      <c r="D148" s="95"/>
       <c r="E148" s="74">
         <f>SUM(D6:D147)</f>
-        <v>85.6</v>
+        <v>101.85</v>
       </c>
       <c r="F148" s="19"/>
       <c r="G148" s="22"/>
@@ -5274,7 +5683,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -5282,31 +5691,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="92" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
     </row>
     <row r="3" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="88" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
@@ -5336,7 +5745,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="38">
-        <f>B45</f>
+        <f>B46</f>
         <v>11.85</v>
       </c>
       <c r="E5" s="39">
@@ -5355,7 +5764,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="38">
-        <f>SUM(B46:B50)</f>
+        <f>SUM(B47:B51)</f>
         <v>14.26</v>
       </c>
       <c r="E6" s="39">
@@ -5374,8 +5783,8 @@
         <v>25</v>
       </c>
       <c r="D7" s="38">
-        <f>SUM(B51:B54)</f>
-        <v>35.99</v>
+        <f>SUM(B52:B55)</f>
+        <v>29.990000000000002</v>
       </c>
       <c r="E7" s="39">
         <f t="shared" si="0"/>
@@ -5393,12 +5802,12 @@
         <v>20</v>
       </c>
       <c r="D8" s="38">
-        <f>SUM(B55:B58)</f>
-        <v>0</v>
+        <f>SUM(B56:B59)</f>
+        <v>6.75</v>
       </c>
       <c r="E8" s="39">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.33750000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -5412,7 +5821,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="38">
-        <f>SUM(B59:B60)</f>
+        <f>SUM(B60:B61)</f>
         <v>0</v>
       </c>
       <c r="E9" s="39">
@@ -5431,7 +5840,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="38">
-        <f>SUM(B61:B62)</f>
+        <f>SUM(B62:B63)</f>
         <v>0</v>
       </c>
       <c r="E10" s="39">
@@ -5450,12 +5859,12 @@
         <v>18</v>
       </c>
       <c r="D11" s="38">
-        <f>SUM(B63)</f>
-        <v>6.5</v>
+        <f>SUM(B64)</f>
+        <v>13.25</v>
       </c>
       <c r="E11" s="39">
         <f t="shared" si="0"/>
-        <v>0.3611111111111111</v>
+        <v>0.73611111111111116</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -5469,30 +5878,30 @@
       </c>
       <c r="D12" s="55">
         <f>SUM(D5:D11)</f>
-        <v>68.599999999999994</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="E12" s="56">
         <f>IF(C12=0,0,D12/C12)</f>
-        <v>0.58135593220338977</v>
+        <v>0.64491525423728813</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="97" t="s">
+      <c r="A14" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="98"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="98"/>
-      <c r="N14" s="98"/>
+      <c r="B14" s="91"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="91"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
@@ -5887,8 +6296,8 @@
       <c r="N33" s="53"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="52" t="s">
-        <v>197</v>
+      <c r="A34" s="81" t="s">
+        <v>381</v>
       </c>
       <c r="B34" s="53"/>
       <c r="C34" s="53"/>
@@ -5896,57 +6305,55 @@
       <c r="E34" s="53"/>
       <c r="F34" s="53"/>
       <c r="G34" s="53"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="63"/>
       <c r="K34" s="63"/>
       <c r="L34" s="53"/>
       <c r="M34" s="53"/>
       <c r="N34" s="53"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="81" t="s">
-        <v>198</v>
+      <c r="A35" s="52" t="s">
+        <v>197</v>
       </c>
       <c r="B35" s="53"/>
       <c r="C35" s="53"/>
       <c r="D35" s="53"/>
       <c r="E35" s="53"/>
-      <c r="F35" s="64" t="s">
-        <v>199</v>
-      </c>
+      <c r="F35" s="53"/>
       <c r="G35" s="53"/>
       <c r="H35" s="47"/>
       <c r="I35" s="47"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
+      <c r="J35" s="47"/>
+      <c r="K35" s="63"/>
       <c r="L35" s="53"/>
       <c r="M35" s="53"/>
       <c r="N35" s="53"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="81" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B36" s="53"/>
       <c r="C36" s="53"/>
       <c r="D36" s="53"/>
       <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
+      <c r="F36" s="64" t="s">
+        <v>199</v>
+      </c>
       <c r="G36" s="53"/>
-      <c r="H36" s="53"/>
+      <c r="H36" s="47"/>
       <c r="I36" s="47"/>
-      <c r="J36" s="47"/>
+      <c r="J36" s="53"/>
       <c r="K36" s="53"/>
       <c r="L36" s="53"/>
       <c r="M36" s="53"/>
-      <c r="N36" s="64" t="s">
-        <v>199</v>
-      </c>
+      <c r="N36" s="53"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="52" t="s">
-        <v>201</v>
+      <c r="A37" s="81" t="s">
+        <v>200</v>
       </c>
       <c r="B37" s="53"/>
       <c r="C37" s="53"/>
@@ -5955,16 +6362,18 @@
       <c r="F37" s="53"/>
       <c r="G37" s="53"/>
       <c r="H37" s="53"/>
-      <c r="I37" s="53"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="49"/>
+      <c r="I37" s="47"/>
+      <c r="J37" s="47"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
       <c r="M37" s="53"/>
-      <c r="N37" s="53"/>
+      <c r="N37" s="64" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="81" t="s">
-        <v>202</v>
+      <c r="A38" s="52" t="s">
+        <v>201</v>
       </c>
       <c r="B38" s="53"/>
       <c r="C38" s="53"/>
@@ -5976,13 +6385,13 @@
       <c r="I38" s="53"/>
       <c r="J38" s="49"/>
       <c r="K38" s="49"/>
-      <c r="L38" s="53"/>
+      <c r="L38" s="49"/>
       <c r="M38" s="53"/>
       <c r="N38" s="53"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="81" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B39" s="53"/>
       <c r="C39" s="53"/>
@@ -5992,15 +6401,15 @@
       <c r="G39" s="53"/>
       <c r="H39" s="53"/>
       <c r="I39" s="53"/>
-      <c r="J39" s="53"/>
+      <c r="J39" s="49"/>
       <c r="K39" s="49"/>
-      <c r="L39" s="49"/>
+      <c r="L39" s="53"/>
       <c r="M39" s="53"/>
       <c r="N39" s="53"/>
     </row>
-    <row r="40" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="52" t="s">
-        <v>204</v>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="81" t="s">
+        <v>203</v>
       </c>
       <c r="B40" s="53"/>
       <c r="C40" s="53"/>
@@ -6011,251 +6420,269 @@
       <c r="H40" s="53"/>
       <c r="I40" s="53"/>
       <c r="J40" s="53"/>
-      <c r="K40" s="53"/>
-      <c r="L40" s="51"/>
-      <c r="M40" s="51"/>
-      <c r="N40" s="51"/>
+      <c r="K40" s="49"/>
+      <c r="L40" s="49"/>
+      <c r="M40" s="53"/>
+      <c r="N40" s="53"/>
     </row>
     <row r="41" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="80"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="A41" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="B41" s="53"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="51"/>
+      <c r="M41" s="51"/>
+      <c r="N41" s="51"/>
+    </row>
+    <row r="42" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="80"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="75"/>
-    </row>
-    <row r="43" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="65" t="s">
+      <c r="C43" s="75"/>
+    </row>
+    <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="65" t="s">
         <v>205</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="4"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="34" t="s">
+      <c r="B44" s="5"/>
+      <c r="C44" s="4"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="66" t="s">
+      <c r="B45" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="4"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="36" t="s">
+      <c r="C45" s="4"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="38">
+      <c r="B46" s="38">
         <f>SUMIF('Work Log'!E:E,"0: Environment Setup",'Work Log'!D:D)</f>
         <v>11.85</v>
       </c>
-      <c r="C45" s="4"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="41" t="s">
+      <c r="C46" s="4"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="B46" s="38">
+      <c r="B47" s="38">
         <f>SUMIF('Work Log'!E:E,"1A: UI Mockups",'Work Log'!D:D)</f>
         <v>2.81</v>
       </c>
-      <c r="C46" s="4"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="41" t="s">
+      <c r="C47" s="4"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B47" s="38">
+      <c r="B48" s="38">
         <f>SUMIF('Work Log'!E:E,"1B: Project Structure",'Work Log'!D:D)</f>
         <v>0.67</v>
       </c>
-      <c r="C47" s="4"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="41" t="s">
+      <c r="C48" s="4"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="B48" s="38">
+      <c r="B49" s="38">
         <f>SUMIF('Work Log'!E:E,"1C: Database Setup",'Work Log'!D:D)</f>
         <v>3.18</v>
       </c>
-      <c r="C48" s="4"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="41" t="s">
+      <c r="C49" s="4"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="B49" s="38">
+      <c r="B50" s="38">
         <f>SUMIF('Work Log'!E:E,"1D: Authentication Feature",'Work Log'!D:D)</f>
         <v>6</v>
       </c>
-      <c r="C49" s="4"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="41" t="s">
+      <c r="C50" s="4"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="B50" s="38">
+      <c r="B51" s="38">
         <f>SUMIF('Work Log'!E:E,"1E: Basic Navigation",'Work Log'!D:D)</f>
         <v>1.5999999999999999</v>
       </c>
-      <c r="C50" s="4"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="43" t="s">
+      <c r="C51" s="4"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="B51" s="38">
+      <c r="B52" s="38">
         <f>SUMIF('Work Log'!E:E,"2A: Open AI Integration",'Work Log'!D:D)</f>
         <v>2.08</v>
       </c>
-      <c r="C51" s="4"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="43" t="s">
+      <c r="C52" s="4"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="43" t="s">
         <v>209</v>
       </c>
-      <c r="B52" s="38">
+      <c r="B53" s="38">
         <f>SUMIF('Work Log'!E:E,"2B: Safety Layer - CTAS Rules",'Work Log'!D:D)</f>
         <v>2.75</v>
       </c>
-      <c r="C52" s="4"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="43" t="s">
+      <c r="C53" s="4"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="B53" s="38">
+      <c r="B54" s="38">
         <f>SUMIF('Work Log'!E:E,"2C: ML Model Training",'Work Log'!D:D)</f>
         <v>9</v>
       </c>
-      <c r="C53" s="4"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="43" t="s">
+      <c r="C54" s="4"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="B54" s="38">
+      <c r="B55" s="38">
         <f>SUMIF('Work Log'!E:E,"2D: Chatbot UI + Integration",'Work Log'!D:D)</f>
-        <v>22.16</v>
-      </c>
-      <c r="C54" s="4"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="B55" s="38">
-        <f>SUMIF('Work Log'!E:E,"3A: Home Dashboard",'Work Log'!D:D)</f>
-        <v>0</v>
+        <v>16.16</v>
       </c>
       <c r="C55" s="4"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="B56" s="38">
+        <f>SUMIF('Work Log'!E:E,"3A: Home Dashboard",'Work Log'!D:D)</f>
+        <v>6.75</v>
+      </c>
+      <c r="C56" s="4"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="B56" s="38">
+      <c r="B57" s="38">
         <f>SUMIF('Work Log'!E:E,"3B: My Dashboard - Personal Analytics",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
-      <c r="C56" s="4"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="45" t="s">
+      <c r="C57" s="4"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="B57" s="38">
+      <c r="B58" s="38">
         <f>SUMIF('Work Log'!E:E,"3C: Facility Finder",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
-      <c r="C57" s="4"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="45" t="s">
+      <c r="C58" s="4"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="45" t="s">
         <v>215</v>
       </c>
-      <c r="B58" s="38">
+      <c r="B59" s="38">
         <f>SUMIF('Work Log'!E:E,"3D: Health Education Library",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
-      <c r="C58" s="4"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="47" t="s">
+      <c r="C59" s="4"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="47" t="s">
         <v>216</v>
       </c>
-      <c r="B59" s="38">
+      <c r="B60" s="38">
         <f>SUMIF('Work Log'!E:E,"4A: System Analytics Data",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
-      <c r="C59" s="4"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="47" t="s">
+      <c r="C60" s="4"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="47" t="s">
         <v>217</v>
       </c>
-      <c r="B60" s="38">
+      <c r="B61" s="38">
         <f>SUMIF('Work Log'!E:E,"4B: System Analytics Dashboard",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
-      <c r="C60" s="4"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="49" t="s">
+      <c r="C61" s="4"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="B61" s="38">
+      <c r="B62" s="38">
         <f>SUMIF('Work Log'!E:E,"5A: Deployment",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="49" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="B62" s="38">
+      <c r="B63" s="38">
         <f>SUMIF('Work Log'!E:E,"5B: Testing",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="51" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="B63" s="38">
+      <c r="B64" s="38">
         <f>SUMIF('Work Log'!E:E,"6: Documentation + Submission",'Work Log'!D:D)</f>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="67" t="s">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B64" s="38">
+      <c r="B65" s="38">
         <f>SUMIF('Work Log'!E:E,"Learning &amp; Research",'Work Log'!D:D)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="68" t="s">
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="68" t="s">
         <v>220</v>
       </c>
-      <c r="B65" s="38">
+      <c r="B66" s="38">
         <f>SUMIF('Work Log'!E:E,"Proof of Concept",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="52" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="B66" s="55">
-        <f>SUM(B45:B65)</f>
-        <v>85.600000000000009</v>
+      <c r="B67" s="55">
+        <f>SUM(B46:B66)</f>
+        <v>93.850000000000009</v>
       </c>
     </row>
   </sheetData>

--- a/DocumentsAndReports/worklog/WorkLog_DesmondChua_W26_4495_S2.xlsx
+++ b/DocumentsAndReports/worklog/WorkLog_DesmondChua_W26_4495_S2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4f25ae689476683/Desmond_New/Winter2026_DouglasCollege/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4f25ae689476683/Desmond_New/BC-Health-Platform/DocumentsAndReports/worklog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="8_{08655895-4010-492B-B73A-F5D36A9F8AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F0C5E6B-2E78-41F0-8095-29D68DBF36E4}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="8_{08655895-4010-492B-B73A-F5D36A9F8AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47B02F83-99C8-4CB2-8FB6-80065E4D42CC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
     <sheet name="Categories" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="440">
   <si>
     <t>CSIS 4495 - Applied Research Project</t>
   </si>
@@ -1274,14 +1274,96 @@
   </si>
   <si>
     <t>3B</t>
+  </si>
+  <si>
+    <t>3E: Multi-Turn Chatbot Enhancement</t>
+  </si>
+  <si>
+    <t>Multi-turn dialog state, slot-filling, session management, edge case handling</t>
+  </si>
+  <si>
+    <t>NLP Research: Reviewed CSIS 3400 NLP course materials (chatbot theory, dialog system pipeline); identified key concepts applicable to multi-turn chatbot upgrade</t>
+  </si>
+  <si>
+    <t>NLP Research: Studied chatbot taxonomy classification (FAQ bots vs. flow-based bots vs. AI bots); mapped existing single-turn chatbot against academic taxonomy to identify upgrade path</t>
+  </si>
+  <si>
+    <t>NLP Research: Studied Dialog System Pipeline (NLU → Dialog Manager → NLG); identified how CTAS rules map to dialog management layer; documented slot-filling theory for symptom collection</t>
+  </si>
+  <si>
+    <t>NLP Research: Researched Intent and Slot concepts in task-oriented dialog systems; mapped to healthcare context: Intent = assess symptoms, Slots = duration/severity/body location/additional info</t>
+  </si>
+  <si>
+    <t>NLP Research: Studied stateful vs. stateless dialog systems and session_state management patterns; researched temperature parameter tuning (0.3 deterministic vs. 0.5 conversational) for GPT calls</t>
+  </si>
+  <si>
+    <t>NLP Research: Documented all NLP concepts with academic framing; organized findings into technical notes mapping theoretical concepts to planned Sprint 3E implementation tasks</t>
+  </si>
+  <si>
+    <t>NLP Research: Final review and consolidation of research notes; confirmed 7 sub-tasks for Sprint 3E aligned with dialog system theory</t>
+  </si>
+  <si>
+    <t>Sprint 3B Enhancements: Added teal filled section headers to all dashboard sections (Symptom Trends, Symptoms Breakdown, Assessment History) matching platform visual standard</t>
+  </si>
+  <si>
+    <t>Sprint 3B Enhancements: Redesigned KPI cards with teal top border strips and inline icons (Total Checks, This Month, Most Common, Avg Urgency); darkened subtitle text for readability</t>
+  </si>
+  <si>
+    <t>Sprint 3B Enhancements: Added urgency filter slicer (All/Emergency/Urgent/Routine/Self-Care) applied additively with existing date filter; inserted 70 synthetic test records for realistic dashboard data</t>
+  </si>
+  <si>
+    <t>Sprint 3B Enhancements: Added logo (assets/logo.png, 55px) beside page title; fixed navigation bug (st.query_params.clear() interfering with st.switch_page()); added View All toggle for assessment history</t>
+  </si>
+  <si>
+    <t>Sprint 3B Enhancements: Fixed trend chart date grouping bug ('%B' to '%b %Y'); added linear trendline using numpy.polyfit as orange dashed trace; cleaned up chart legend</t>
+  </si>
+  <si>
+    <t>1 hr 30 min</t>
+  </si>
+  <si>
+    <t>3E</t>
+  </si>
+  <si>
+    <t>Sprint 3E: Built multi-turn chatbot backend — initialize_dialog_state(), get_follow_up_question() slot-filling, process_multiturn_message() turn orchestrator in chatbot.py; MULTITURN_EXTRACTION_PROMPT and extract_symptoms_multiturn() in openai_utils.py</t>
+  </si>
+  <si>
+    <t>Sprint 3E: Built multi-turn UI in 2_Symptom_Assessment.py — chat history display, input handler, sidebar progress panel (collected symptoms, remaining turns), Start New Assessment reset button</t>
+  </si>
+  <si>
+    <t>Sprint 3E: Ran all 6 test scenarios; identified edge case bug where vague health complaints triggered immediate redirect on turn 1; redesigned logic to apply gentle detail prompt on turn 1, redirect only after multiple failed turns</t>
+  </si>
+  <si>
+    <t>Sprint 3E: Fix edge case — gentle prompt for vague health complaints on turn 1 instead of immediate redirect; confirmed fix with retest; git commit</t>
+  </si>
+  <si>
+    <t>Sprint 3E: Git commits for backend, UI, and edge case fixes with descriptive messages</t>
+  </si>
+  <si>
+    <t>3C</t>
+  </si>
+  <si>
+    <t>Sprint 3C: Created Implementation/data/facilities.csv with 24 facilities across 5 BC regions (later rebuilt to 45 facilities with focused Lower Mainland coverage)</t>
+  </si>
+  <si>
+    <t>Sprint 3C: Built 4_Facility_Finder.py — Emergency Contacts section, Search filter dropdowns, interactive Folium map with colored markers, facility cards, Health Tips, Understanding Facility Types sections</t>
+  </si>
+  <si>
+    <t>Sprint 3C: Refined facility CSV to 45 records, removed Pharmacy type, separated Urgent Care (orange) from Walk-In Clinic (green) on map, verified all filter and map interactions</t>
+  </si>
+  <si>
+    <t>Sprint 3C: Git commits; updated work log and task tracker with Sprint 3B, 3E, and 3C completion status</t>
+  </si>
+  <si>
+    <t>Prepared Progress Report 3; updated commit history, work log entries, and Gantt chart for PR3 reporting period (Mar 3–9)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -1649,12 +1731,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1834,12 +1915,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1861,6 +1938,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1868,8 +1946,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2055,10 +2155,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2346,2709 +2442,2709 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="34.21875" style="69" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="20" customWidth="1"/>
-    <col min="7" max="7" width="209.77734375" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.21875" style="68" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="19" customWidth="1"/>
+    <col min="7" max="7" width="209.77734375" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="102"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="98"/>
     </row>
     <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="102"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="98"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="99"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="94"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F4" s="17"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="27" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <v>0</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="28">
         <v>2</v>
       </c>
-      <c r="E6" s="70" t="s">
+      <c r="E6" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="31" t="s">
+      <c r="F6" s="29"/>
+      <c r="G6" s="30" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <v>0</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="28">
         <v>1.5</v>
       </c>
-      <c r="E7" s="70" t="s">
+      <c r="E7" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="31" t="s">
+      <c r="F7" s="29"/>
+      <c r="G7" s="30" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="23">
         <v>0</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="28">
         <v>2</v>
       </c>
-      <c r="E8" s="71" t="s">
+      <c r="E8" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31" t="s">
+      <c r="F8" s="29"/>
+      <c r="G8" s="30" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <v>0</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="70" t="s">
+      <c r="E9" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="31" t="s">
+      <c r="F9" s="29"/>
+      <c r="G9" s="30" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="23">
         <v>0</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="28">
         <v>2.5</v>
       </c>
-      <c r="E10" s="71" t="s">
+      <c r="E10" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="31" t="s">
+      <c r="F10" s="29"/>
+      <c r="G10" s="30" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="23">
         <v>0</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="28">
         <v>2</v>
       </c>
-      <c r="E11" s="70" t="s">
+      <c r="E11" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="31" t="s">
+      <c r="F11" s="29"/>
+      <c r="G11" s="30" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="23">
         <v>0</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="28">
         <v>3</v>
       </c>
-      <c r="E12" s="71" t="s">
+      <c r="E12" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="31" t="s">
+      <c r="F12" s="29"/>
+      <c r="G12" s="30" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="23">
         <v>0</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="28">
         <v>2.5</v>
       </c>
-      <c r="E13" s="70" t="s">
+      <c r="E13" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="31" t="s">
+      <c r="F13" s="29"/>
+      <c r="G13" s="30" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="23">
         <v>0</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="28">
         <v>3</v>
       </c>
-      <c r="E14" s="71" t="s">
+      <c r="E14" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="31" t="s">
+      <c r="F14" s="29"/>
+      <c r="G14" s="30" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="23">
         <v>0</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="28">
         <v>2.5</v>
       </c>
-      <c r="E15" s="71" t="s">
+      <c r="E15" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="31" t="s">
+      <c r="F15" s="29"/>
+      <c r="G15" s="30" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="23">
         <v>0</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="28">
         <v>3</v>
       </c>
-      <c r="E16" s="72" t="s">
+      <c r="E16" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="31" t="s">
+      <c r="F16" s="29"/>
+      <c r="G16" s="30" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="23">
         <v>0</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="28">
         <v>3.5</v>
       </c>
-      <c r="E17" s="72" t="s">
+      <c r="E17" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="31" t="s">
+      <c r="F17" s="29"/>
+      <c r="G17" s="30" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="23">
         <v>0</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="28">
         <v>0.25</v>
       </c>
-      <c r="E18" s="70" t="s">
+      <c r="E18" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="30" t="s">
+      <c r="F18" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="30" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="23">
         <v>0</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="28">
         <v>0.25</v>
       </c>
-      <c r="E19" s="70" t="s">
+      <c r="E19" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="F19" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="30" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="23">
         <v>0</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="28">
         <v>0.25</v>
       </c>
-      <c r="E20" s="70" t="s">
+      <c r="E20" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F20" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="23">
         <v>0</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="28">
         <v>0.25</v>
       </c>
-      <c r="E21" s="70" t="s">
+      <c r="E21" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="30" t="s">
+      <c r="F21" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="30" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="23">
         <v>0</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="28">
         <v>0.1</v>
       </c>
-      <c r="E22" s="70" t="s">
+      <c r="E22" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="30" t="s">
+      <c r="F22" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="G22" s="30" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="23">
         <v>0</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="28">
         <v>1</v>
       </c>
-      <c r="E23" s="70" t="s">
+      <c r="E23" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="30"/>
-      <c r="G23" s="31" t="s">
+      <c r="F23" s="29"/>
+      <c r="G23" s="30" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="23">
         <v>0</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="28">
         <v>0.17</v>
       </c>
-      <c r="E24" s="70" t="s">
+      <c r="E24" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="30" t="s">
+      <c r="F24" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="30" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="23">
         <v>0</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="28">
         <v>0.08</v>
       </c>
-      <c r="E25" s="70" t="s">
+      <c r="E25" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="30" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="23">
         <v>0</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="28">
         <v>0.25</v>
       </c>
-      <c r="E26" s="70" t="s">
+      <c r="E26" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="30" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="23">
         <v>0</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="28">
         <v>0.08</v>
       </c>
-      <c r="E27" s="70" t="s">
+      <c r="E27" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="30" t="s">
+      <c r="F27" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="30" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="23">
         <v>0</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="28">
         <v>0.17</v>
       </c>
-      <c r="E28" s="70" t="s">
+      <c r="E28" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="30" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="23">
         <v>1</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="31">
         <v>0.42</v>
       </c>
-      <c r="E29" s="71" t="s">
+      <c r="E29" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="F29" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="G29" s="22" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="23">
         <v>1</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="31">
         <v>0.57999999999999996</v>
       </c>
-      <c r="E30" s="71" t="s">
+      <c r="E30" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="G30" s="22" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="23">
         <v>1</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D31" s="32">
+      <c r="D31" s="31">
         <v>0.5</v>
       </c>
-      <c r="E31" s="71" t="s">
+      <c r="E31" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="F31" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="G31" s="23" t="s">
+      <c r="G31" s="22" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="24" t="s">
+      <c r="A32" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="23">
         <v>1</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="32">
+      <c r="D32" s="31">
         <v>0.25</v>
       </c>
-      <c r="E32" s="71" t="s">
+      <c r="E32" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F32" s="26" t="s">
+      <c r="F32" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="G32" s="22" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B33" s="23">
         <v>1</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="31">
         <v>0.33</v>
       </c>
-      <c r="E33" s="71" t="s">
+      <c r="E33" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="F33" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="G33" s="23" t="s">
+      <c r="G33" s="22" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B34" s="23">
         <v>1</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="31">
         <v>0.33</v>
       </c>
-      <c r="E34" s="71" t="s">
+      <c r="E34" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F34" s="26" t="s">
+      <c r="F34" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="G34" s="23" t="s">
+      <c r="G34" s="22" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="24" t="s">
+      <c r="A35" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B35" s="23">
         <v>1</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="31">
         <v>0.42</v>
       </c>
-      <c r="E35" s="71" t="s">
+      <c r="E35" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="F35" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="G35" s="23" t="s">
+      <c r="G35" s="22" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
+      <c r="A36" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B36" s="23">
         <v>1</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="31">
         <v>0.25</v>
       </c>
-      <c r="E36" s="71" t="s">
+      <c r="E36" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F36" s="26" t="s">
+      <c r="F36" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="23" t="s">
+      <c r="G36" s="22" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="23">
         <v>1</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="32">
+      <c r="D37" s="31">
         <v>0.25</v>
       </c>
-      <c r="E37" s="71" t="s">
+      <c r="E37" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="F37" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="23" t="s">
+      <c r="G37" s="22" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="23">
         <v>1</v>
       </c>
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="31">
         <v>0.67</v>
       </c>
-      <c r="E38" s="71" t="s">
+      <c r="E38" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="F38" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="G38" s="23" t="s">
+      <c r="G38" s="22" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="31">
         <v>0.33</v>
       </c>
-      <c r="E39" s="73" t="s">
+      <c r="E39" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F39" s="26" t="s">
+      <c r="F39" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="G39" s="23" t="s">
+      <c r="G39" s="22" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="32">
+      <c r="D40" s="31">
         <v>0.33</v>
       </c>
-      <c r="E40" s="73" t="s">
+      <c r="E40" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F40" s="26" t="s">
+      <c r="F40" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="G40" s="23" t="s">
+      <c r="G40" s="22" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="24" t="s">
+      <c r="A41" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="31">
         <v>0.33</v>
       </c>
-      <c r="E41" s="73" t="s">
+      <c r="E41" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F41" s="26" t="s">
+      <c r="F41" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="G41" s="22" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B42" s="24" t="s">
+      <c r="B42" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="31">
         <v>0.33</v>
       </c>
-      <c r="E42" s="73" t="s">
+      <c r="E42" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F42" s="26" t="s">
+      <c r="F42" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="G42" s="23" t="s">
+      <c r="G42" s="22" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="24" t="s">
+      <c r="A43" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B43" s="24" t="s">
+      <c r="B43" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D43" s="32">
+      <c r="D43" s="31">
         <v>0.33</v>
       </c>
-      <c r="E43" s="73" t="s">
+      <c r="E43" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="26" t="s">
+      <c r="F43" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="G43" s="23" t="s">
+      <c r="G43" s="22" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="24" t="s">
+      <c r="A44" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B44" s="24" t="s">
+      <c r="B44" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C44" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="31">
         <v>0.33</v>
       </c>
-      <c r="E44" s="73" t="s">
+      <c r="E44" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F44" s="26" t="s">
+      <c r="F44" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="G44" s="23" t="s">
+      <c r="G44" s="22" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="24" t="s">
+      <c r="A45" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="24" t="s">
+      <c r="B45" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="31">
         <v>0.33</v>
       </c>
-      <c r="E45" s="73" t="s">
+      <c r="E45" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F45" s="26" t="s">
+      <c r="F45" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="G45" s="23" t="s">
+      <c r="G45" s="22" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="24" t="s">
+      <c r="A46" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="24" t="s">
+      <c r="B46" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="24" t="s">
+      <c r="C46" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="32">
+      <c r="D46" s="31">
         <v>0.33</v>
       </c>
-      <c r="E46" s="73" t="s">
+      <c r="E46" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F46" s="26" t="s">
+      <c r="F46" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="G46" s="23" t="s">
+      <c r="G46" s="22" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="24" t="s">
+      <c r="A47" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="32">
+      <c r="D47" s="31">
         <v>0.17</v>
       </c>
-      <c r="E47" s="73" t="s">
+      <c r="E47" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="F47" s="26" t="s">
+      <c r="F47" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="G47" s="23" t="s">
+      <c r="G47" s="22" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
+      <c r="A48" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="24" t="s">
+      <c r="B48" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="31">
         <v>0.25</v>
       </c>
-      <c r="E48" s="73" t="s">
+      <c r="E48" s="72" t="s">
         <v>113</v>
       </c>
-      <c r="F48" s="26" t="s">
+      <c r="F48" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="G48" s="23" t="s">
+      <c r="G48" s="22" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="24" t="s">
+      <c r="A49" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B49" s="24" t="s">
+      <c r="B49" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D49" s="32">
+      <c r="D49" s="31">
         <v>0.17</v>
       </c>
-      <c r="E49" s="73" t="s">
+      <c r="E49" s="72" t="s">
         <v>113</v>
       </c>
-      <c r="F49" s="26" t="s">
+      <c r="F49" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="G49" s="23" t="s">
+      <c r="G49" s="22" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="24" t="s">
+      <c r="A50" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="B50" s="24" t="s">
+      <c r="B50" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C50" s="24" t="s">
+      <c r="C50" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="31">
         <v>0.25</v>
       </c>
-      <c r="E50" s="73" t="s">
+      <c r="E50" s="72" t="s">
         <v>113</v>
       </c>
-      <c r="F50" s="26" t="s">
+      <c r="F50" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="G50" s="23" t="s">
+      <c r="G50" s="22" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="24" t="s">
+      <c r="A51" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C51" s="30" t="s">
+      <c r="C51" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="32">
+      <c r="D51" s="31">
         <v>0.5</v>
       </c>
-      <c r="E51" s="73" t="s">
+      <c r="E51" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="F51" s="26" t="s">
+      <c r="F51" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="G51" s="23" t="s">
+      <c r="G51" s="22" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="24" t="s">
+      <c r="A52" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B52" s="24" t="s">
+      <c r="B52" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C52" s="30" t="s">
+      <c r="C52" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D52" s="32">
+      <c r="D52" s="31">
         <v>0.5</v>
       </c>
-      <c r="E52" s="73" t="s">
+      <c r="E52" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="F52" s="26" t="s">
+      <c r="F52" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="G52" s="23" t="s">
+      <c r="G52" s="22" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="24" t="s">
+      <c r="A53" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B53" s="24" t="s">
+      <c r="B53" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C53" s="30" t="s">
+      <c r="C53" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="31">
         <v>0.5</v>
       </c>
-      <c r="E53" s="73" t="s">
+      <c r="E53" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="F53" s="26" t="s">
+      <c r="F53" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="G53" s="23" t="s">
+      <c r="G53" s="22" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="24" t="s">
+      <c r="A54" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="26" t="s">
+      <c r="B54" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C54" s="30" t="s">
+      <c r="C54" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="31">
         <v>0.75</v>
       </c>
-      <c r="E54" s="73" t="s">
+      <c r="E54" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="F54" s="26" t="s">
+      <c r="F54" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="G54" s="23" t="s">
+      <c r="G54" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="26" t="s">
+      <c r="A55" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B55" s="26" t="s">
+      <c r="B55" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C55" s="30" t="s">
+      <c r="C55" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="32">
+      <c r="D55" s="31">
         <v>0.5</v>
       </c>
-      <c r="E55" s="73" t="s">
+      <c r="E55" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="F55" s="26" t="s">
+      <c r="F55" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="G55" s="23" t="s">
+      <c r="G55" s="22" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="26" t="s">
+      <c r="A56" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B56" s="26" t="s">
+      <c r="B56" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C56" s="30" t="s">
+      <c r="C56" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="31">
         <v>0.33</v>
       </c>
-      <c r="E56" s="73" t="s">
+      <c r="E56" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="F56" s="26" t="s">
+      <c r="F56" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="G56" s="23" t="s">
+      <c r="G56" s="22" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="26" t="s">
+      <c r="A57" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B57" s="26" t="s">
+      <c r="B57" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C57" s="26" t="s">
+      <c r="C57" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D57" s="29">
+      <c r="D57" s="28">
         <v>0.1</v>
       </c>
-      <c r="E57" s="73" t="s">
+      <c r="E57" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="F57" s="26" t="s">
+      <c r="F57" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="G57" s="23" t="s">
+      <c r="G57" s="22" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="78" t="s">
+      <c r="A58" s="77" t="s">
         <v>245</v>
       </c>
-      <c r="B58" s="78" t="s">
+      <c r="B58" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="78" t="s">
+      <c r="C58" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="D58" s="78">
+      <c r="D58" s="77">
         <v>0.75</v>
       </c>
-      <c r="E58" s="76" t="s">
+      <c r="E58" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="F58" s="78" t="s">
+      <c r="F58" s="77" t="s">
         <v>246</v>
       </c>
-      <c r="G58" s="79" t="s">
+      <c r="G58" s="78" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="78" t="s">
+      <c r="A59" s="77" t="s">
         <v>245</v>
       </c>
-      <c r="B59" s="78" t="s">
+      <c r="B59" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C59" s="78" t="s">
+      <c r="C59" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="D59" s="78">
+      <c r="D59" s="77">
         <v>1</v>
       </c>
-      <c r="E59" s="76" t="s">
+      <c r="E59" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="F59" s="78" t="s">
+      <c r="F59" s="77" t="s">
         <v>248</v>
       </c>
-      <c r="G59" s="79" t="s">
+      <c r="G59" s="78" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="78" t="s">
+      <c r="A60" s="77" t="s">
         <v>245</v>
       </c>
-      <c r="B60" s="78" t="s">
+      <c r="B60" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C60" s="78" t="s">
+      <c r="C60" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="D60" s="78">
+      <c r="D60" s="77">
         <v>1.5</v>
       </c>
-      <c r="E60" s="76" t="s">
+      <c r="E60" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="F60" s="78" t="s">
+      <c r="F60" s="77" t="s">
         <v>250</v>
       </c>
-      <c r="G60" s="79" t="s">
+      <c r="G60" s="78" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="78" t="s">
+      <c r="A61" s="77" t="s">
         <v>245</v>
       </c>
-      <c r="B61" s="78" t="s">
+      <c r="B61" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C61" s="78" t="s">
+      <c r="C61" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="D61" s="78">
+      <c r="D61" s="77">
         <v>0.75</v>
       </c>
-      <c r="E61" s="76" t="s">
+      <c r="E61" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="F61" s="78" t="s">
+      <c r="F61" s="77" t="s">
         <v>252</v>
       </c>
-      <c r="G61" s="79" t="s">
+      <c r="G61" s="78" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="78" t="s">
+      <c r="A62" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="B62" s="78" t="s">
+      <c r="B62" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C62" s="78" t="s">
+      <c r="C62" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="D62" s="78">
+      <c r="D62" s="77">
         <v>0.75</v>
       </c>
-      <c r="E62" s="76" t="s">
+      <c r="E62" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="F62" s="78" t="s">
+      <c r="F62" s="77" t="s">
         <v>255</v>
       </c>
-      <c r="G62" s="79" t="s">
+      <c r="G62" s="78" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="78" t="s">
+      <c r="A63" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="B63" s="78" t="s">
+      <c r="B63" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C63" s="78" t="s">
+      <c r="C63" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="D63" s="78">
+      <c r="D63" s="77">
         <v>0.25</v>
       </c>
-      <c r="E63" s="76" t="s">
+      <c r="E63" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="F63" s="78" t="s">
+      <c r="F63" s="77" t="s">
         <v>257</v>
       </c>
-      <c r="G63" s="79" t="s">
+      <c r="G63" s="78" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="78" t="s">
+      <c r="A64" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="B64" s="78" t="s">
+      <c r="B64" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C64" s="78" t="s">
+      <c r="C64" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="D64" s="78">
+      <c r="D64" s="77">
         <v>0.5</v>
       </c>
-      <c r="E64" s="76" t="s">
+      <c r="E64" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="F64" s="78" t="s">
+      <c r="F64" s="77" t="s">
         <v>259</v>
       </c>
-      <c r="G64" s="79" t="s">
+      <c r="G64" s="78" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="78" t="s">
+      <c r="A65" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="B65" s="78" t="s">
+      <c r="B65" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C65" s="78" t="s">
+      <c r="C65" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="D65" s="78">
+      <c r="D65" s="77">
         <v>0.5</v>
       </c>
-      <c r="E65" s="76" t="s">
+      <c r="E65" s="75" t="s">
         <v>206</v>
       </c>
-      <c r="F65" s="78" t="s">
+      <c r="F65" s="77" t="s">
         <v>261</v>
       </c>
-      <c r="G65" s="79" t="s">
+      <c r="G65" s="78" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="78" t="s">
+      <c r="A66" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="B66" s="78" t="s">
+      <c r="B66" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C66" s="78" t="s">
+      <c r="C66" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="78">
+      <c r="D66" s="77">
         <v>0.5</v>
       </c>
-      <c r="E66" s="77" t="s">
+      <c r="E66" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="F66" s="78" t="s">
+      <c r="F66" s="77" t="s">
         <v>263</v>
       </c>
-      <c r="G66" s="79" t="s">
+      <c r="G66" s="78" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="78" t="s">
+      <c r="A67" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="B67" s="78" t="s">
+      <c r="B67" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C67" s="78" t="s">
+      <c r="C67" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="D67" s="78">
+      <c r="D67" s="77">
         <v>0.17</v>
       </c>
-      <c r="E67" s="77" t="s">
+      <c r="E67" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="F67" s="78" t="s">
+      <c r="F67" s="77" t="s">
         <v>265</v>
       </c>
-      <c r="G67" s="79" t="s">
+      <c r="G67" s="78" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="78" t="s">
+      <c r="A68" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="B68" s="78" t="s">
+      <c r="B68" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C68" s="78" t="s">
+      <c r="C68" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="D68" s="78">
+      <c r="D68" s="77">
         <v>0.17</v>
       </c>
-      <c r="E68" s="77" t="s">
+      <c r="E68" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="F68" s="78" t="s">
+      <c r="F68" s="77" t="s">
         <v>267</v>
       </c>
-      <c r="G68" s="79" t="s">
+      <c r="G68" s="78" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="78" t="s">
+      <c r="A69" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="B69" s="78" t="s">
+      <c r="B69" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C69" s="78" t="s">
+      <c r="C69" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="78">
+      <c r="D69" s="77">
         <v>0.17</v>
       </c>
-      <c r="E69" s="77" t="s">
+      <c r="E69" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="F69" s="78" t="s">
+      <c r="F69" s="77" t="s">
         <v>269</v>
       </c>
-      <c r="G69" s="79" t="s">
+      <c r="G69" s="78" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="78" t="s">
+      <c r="A70" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="B70" s="78" t="s">
+      <c r="B70" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C70" s="78" t="s">
+      <c r="C70" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="D70" s="78">
+      <c r="D70" s="77">
         <v>0.17</v>
       </c>
-      <c r="E70" s="77" t="s">
+      <c r="E70" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="F70" s="78" t="s">
+      <c r="F70" s="77" t="s">
         <v>271</v>
       </c>
-      <c r="G70" s="79" t="s">
+      <c r="G70" s="78" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="78" t="s">
+      <c r="A71" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="B71" s="78" t="s">
+      <c r="B71" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C71" s="78" t="s">
+      <c r="C71" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="D71" s="78">
+      <c r="D71" s="77">
         <v>0.17</v>
       </c>
-      <c r="E71" s="77" t="s">
+      <c r="E71" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="F71" s="78" t="s">
+      <c r="F71" s="77" t="s">
         <v>273</v>
       </c>
-      <c r="G71" s="79" t="s">
+      <c r="G71" s="78" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="78" t="s">
+      <c r="A72" s="77" t="s">
         <v>254</v>
       </c>
-      <c r="B72" s="78" t="s">
+      <c r="B72" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="C72" s="78" t="s">
+      <c r="C72" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="D72" s="78">
+      <c r="D72" s="77">
         <v>0.25</v>
       </c>
-      <c r="E72" s="77" t="s">
+      <c r="E72" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="F72" s="78" t="s">
+      <c r="F72" s="77" t="s">
         <v>275</v>
       </c>
-      <c r="G72" s="79" t="s">
+      <c r="G72" s="78" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="24" t="s">
+      <c r="A73" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="B73" s="24" t="s">
+      <c r="B73" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C73" s="24" t="s">
+      <c r="C73" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D73" s="24">
+      <c r="D73" s="23">
         <v>0.17</v>
       </c>
-      <c r="E73" s="83" t="s">
+      <c r="E73" s="82" t="s">
         <v>208</v>
       </c>
-      <c r="F73" s="24" t="s">
+      <c r="F73" s="23" t="s">
         <v>283</v>
       </c>
-      <c r="G73" s="82" t="s">
+      <c r="G73" s="81" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="24" t="s">
+      <c r="A74" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="B74" s="24" t="s">
+      <c r="B74" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C74" s="24" t="s">
+      <c r="C74" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D74" s="24">
+      <c r="D74" s="23">
         <v>0.08</v>
       </c>
-      <c r="E74" s="83" t="s">
+      <c r="E74" s="82" t="s">
         <v>208</v>
       </c>
-      <c r="F74" s="24" t="s">
+      <c r="F74" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="G74" s="82" t="s">
+      <c r="G74" s="81" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="24" t="s">
+      <c r="A75" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="B75" s="24" t="s">
+      <c r="B75" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C75" s="24" t="s">
+      <c r="C75" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="24">
+      <c r="D75" s="23">
         <v>0.5</v>
       </c>
-      <c r="E75" s="83" t="s">
+      <c r="E75" s="82" t="s">
         <v>208</v>
       </c>
-      <c r="F75" s="24" t="s">
+      <c r="F75" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="G75" s="82" t="s">
+      <c r="G75" s="81" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="24" t="s">
+      <c r="A76" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="B76" s="24" t="s">
+      <c r="B76" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C76" s="24" t="s">
+      <c r="C76" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D76" s="24">
+      <c r="D76" s="23">
         <v>1</v>
       </c>
-      <c r="E76" s="83" t="s">
+      <c r="E76" s="82" t="s">
         <v>208</v>
       </c>
-      <c r="F76" s="24" t="s">
+      <c r="F76" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="G76" s="82" t="s">
+      <c r="G76" s="81" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="24" t="s">
+      <c r="A77" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="B77" s="24" t="s">
+      <c r="B77" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C77" s="24" t="s">
+      <c r="C77" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D77" s="24">
+      <c r="D77" s="23">
         <v>0.33</v>
       </c>
-      <c r="E77" s="83" t="s">
+      <c r="E77" s="82" t="s">
         <v>208</v>
       </c>
-      <c r="F77" s="24" t="s">
+      <c r="F77" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="G77" s="82" t="s">
+      <c r="G77" s="81" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="24" t="s">
+      <c r="A78" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="B78" s="24" t="s">
+      <c r="B78" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C78" s="24" t="s">
+      <c r="C78" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D78" s="24">
+      <c r="D78" s="23">
         <v>0.5</v>
       </c>
-      <c r="E78" s="83" t="s">
+      <c r="E78" s="82" t="s">
         <v>209</v>
       </c>
-      <c r="F78" s="24" t="s">
+      <c r="F78" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="G78" s="82" t="s">
+      <c r="G78" s="81" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="24" t="s">
+      <c r="A79" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="B79" s="24" t="s">
+      <c r="B79" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C79" s="24" t="s">
+      <c r="C79" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D79" s="24">
+      <c r="D79" s="23">
         <v>1</v>
       </c>
-      <c r="E79" s="83" t="s">
+      <c r="E79" s="82" t="s">
         <v>209</v>
       </c>
-      <c r="F79" s="24" t="s">
+      <c r="F79" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="G79" s="82" t="s">
+      <c r="G79" s="81" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="B80" s="24" t="s">
+      <c r="B80" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C80" s="24" t="s">
+      <c r="C80" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D80" s="24">
+      <c r="D80" s="23">
         <v>0.75</v>
       </c>
-      <c r="E80" s="83" t="s">
+      <c r="E80" s="82" t="s">
         <v>209</v>
       </c>
-      <c r="F80" s="24" t="s">
+      <c r="F80" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="G80" s="82" t="s">
+      <c r="G80" s="81" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="24" t="s">
+      <c r="A81" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="B81" s="24" t="s">
+      <c r="B81" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C81" s="24" t="s">
+      <c r="C81" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D81" s="24">
+      <c r="D81" s="23">
         <v>0.5</v>
       </c>
-      <c r="E81" s="83" t="s">
+      <c r="E81" s="82" t="s">
         <v>209</v>
       </c>
-      <c r="F81" s="24" t="s">
+      <c r="F81" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="G81" s="82" t="s">
+      <c r="G81" s="81" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="24" t="s">
+      <c r="A82" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="B82" s="24" t="s">
+      <c r="B82" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C82" s="24" t="s">
+      <c r="C82" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="24">
+      <c r="D82" s="23">
         <v>2</v>
       </c>
-      <c r="E82" s="83" t="s">
+      <c r="E82" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="F82" s="24" t="s">
+      <c r="F82" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="G82" s="82" t="s">
+      <c r="G82" s="81" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="24" t="s">
+      <c r="A83" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="B83" s="24" t="s">
+      <c r="B83" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C83" s="24" t="s">
+      <c r="C83" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D83" s="24">
+      <c r="D83" s="23">
         <v>0.5</v>
       </c>
-      <c r="E83" s="83" t="s">
+      <c r="E83" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="F83" s="24" t="s">
+      <c r="F83" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="G83" s="82" t="s">
+      <c r="G83" s="81" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="24" t="s">
+      <c r="A84" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="B84" s="24" t="s">
+      <c r="B84" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C84" s="24" t="s">
+      <c r="C84" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D84" s="24">
+      <c r="D84" s="23">
         <v>0.75</v>
       </c>
-      <c r="E84" s="83" t="s">
+      <c r="E84" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="F84" s="24" t="s">
+      <c r="F84" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="G84" s="82" t="s">
+      <c r="G84" s="81" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="24" t="s">
+      <c r="A85" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="B85" s="24" t="s">
+      <c r="B85" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C85" s="24" t="s">
+      <c r="C85" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D85" s="24">
+      <c r="D85" s="23">
         <v>1</v>
       </c>
-      <c r="E85" s="83" t="s">
+      <c r="E85" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="F85" s="24" t="s">
+      <c r="F85" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="G85" s="82" t="s">
+      <c r="G85" s="81" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="24" t="s">
+      <c r="A86" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="B86" s="24" t="s">
+      <c r="B86" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C86" s="24" t="s">
+      <c r="C86" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D86" s="24">
+      <c r="D86" s="23">
         <v>1</v>
       </c>
-      <c r="E86" s="83" t="s">
+      <c r="E86" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="F86" s="24" t="s">
+      <c r="F86" s="23" t="s">
         <v>309</v>
       </c>
-      <c r="G86" s="82" t="s">
+      <c r="G86" s="81" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="24" t="s">
+      <c r="A87" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="B87" s="24" t="s">
+      <c r="B87" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C87" s="24" t="s">
+      <c r="C87" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D87" s="24">
+      <c r="D87" s="23">
         <v>1</v>
       </c>
-      <c r="E87" s="83" t="s">
+      <c r="E87" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="F87" s="24" t="s">
+      <c r="F87" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="G87" s="82" t="s">
+      <c r="G87" s="81" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="24" t="s">
+      <c r="A88" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="B88" s="24" t="s">
+      <c r="B88" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C88" s="24" t="s">
+      <c r="C88" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D88" s="24">
+      <c r="D88" s="23">
         <v>2</v>
       </c>
-      <c r="E88" s="83" t="s">
+      <c r="E88" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="F88" s="24" t="s">
+      <c r="F88" s="23" t="s">
         <v>313</v>
       </c>
-      <c r="G88" s="82" t="s">
+      <c r="G88" s="81" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="24" t="s">
+      <c r="A89" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="B89" s="24" t="s">
+      <c r="B89" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C89" s="24" t="s">
+      <c r="C89" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D89" s="24">
+      <c r="D89" s="23">
         <v>0.5</v>
       </c>
-      <c r="E89" s="83" t="s">
+      <c r="E89" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="F89" s="24" t="s">
+      <c r="F89" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="G89" s="82" t="s">
+      <c r="G89" s="81" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="24" t="s">
+      <c r="A90" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="B90" s="24" t="s">
+      <c r="B90" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C90" s="24" t="s">
+      <c r="C90" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D90" s="24">
+      <c r="D90" s="23">
         <v>0.25</v>
       </c>
-      <c r="E90" s="83" t="s">
+      <c r="E90" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="F90" s="24" t="s">
+      <c r="F90" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="G90" s="82" t="s">
+      <c r="G90" s="81" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="24" t="s">
+      <c r="A91" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="B91" s="24" t="s">
+      <c r="B91" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C91" s="24" t="s">
+      <c r="C91" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D91" s="24">
+      <c r="D91" s="23">
         <v>1</v>
       </c>
-      <c r="E91" s="83" t="s">
+      <c r="E91" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F91" s="24" t="s">
+      <c r="F91" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G91" s="82" t="s">
+      <c r="G91" s="81" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="24" t="s">
+      <c r="A92" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="B92" s="24" t="s">
+      <c r="B92" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C92" s="24" t="s">
+      <c r="C92" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D92" s="24">
+      <c r="D92" s="23">
         <v>1.5</v>
       </c>
-      <c r="E92" s="83" t="s">
+      <c r="E92" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F92" s="24" t="s">
+      <c r="F92" s="23" t="s">
         <v>324</v>
       </c>
-      <c r="G92" s="82" t="s">
+      <c r="G92" s="81" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="24" t="s">
+      <c r="A93" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="B93" s="24" t="s">
+      <c r="B93" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C93" s="24" t="s">
+      <c r="C93" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D93" s="24">
+      <c r="D93" s="23">
         <v>0.33</v>
       </c>
-      <c r="E93" s="83" t="s">
+      <c r="E93" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F93" s="24" t="s">
+      <c r="F93" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="G93" s="82" t="s">
+      <c r="G93" s="81" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" s="24" t="s">
+      <c r="A94" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="B94" s="24" t="s">
+      <c r="B94" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C94" s="24" t="s">
+      <c r="C94" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D94" s="24">
+      <c r="D94" s="23">
         <v>0.75</v>
       </c>
-      <c r="E94" s="83" t="s">
+      <c r="E94" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F94" s="24" t="s">
+      <c r="F94" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="G94" s="82" t="s">
+      <c r="G94" s="81" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="24" t="s">
+      <c r="A95" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="B95" s="24" t="s">
+      <c r="B95" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C95" s="24" t="s">
+      <c r="C95" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D95" s="24">
+      <c r="D95" s="23">
         <v>2</v>
       </c>
-      <c r="E95" s="83" t="s">
+      <c r="E95" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F95" s="24" t="s">
+      <c r="F95" s="23" t="s">
         <v>330</v>
       </c>
-      <c r="G95" s="82" t="s">
+      <c r="G95" s="81" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="24" t="s">
+      <c r="A96" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B96" s="24" t="s">
+      <c r="B96" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C96" s="24" t="s">
+      <c r="C96" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D96" s="24">
+      <c r="D96" s="23">
         <v>1</v>
       </c>
-      <c r="E96" s="83" t="s">
+      <c r="E96" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F96" s="24" t="s">
+      <c r="F96" s="23" t="s">
         <v>332</v>
       </c>
-      <c r="G96" s="82" t="s">
+      <c r="G96" s="81" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="24" t="s">
+      <c r="A97" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B97" s="24" t="s">
+      <c r="B97" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C97" s="24" t="s">
+      <c r="C97" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D97" s="24">
+      <c r="D97" s="23">
         <v>0.75</v>
       </c>
-      <c r="E97" s="83" t="s">
+      <c r="E97" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F97" s="24" t="s">
+      <c r="F97" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="G97" s="82" t="s">
+      <c r="G97" s="81" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="24" t="s">
+      <c r="A98" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B98" s="24" t="s">
+      <c r="B98" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C98" s="24" t="s">
+      <c r="C98" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D98" s="24">
+      <c r="D98" s="23">
         <v>0.5</v>
       </c>
-      <c r="E98" s="83" t="s">
+      <c r="E98" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F98" s="24" t="s">
+      <c r="F98" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="G98" s="82" t="s">
+      <c r="G98" s="81" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="24" t="s">
+      <c r="A99" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B99" s="24" t="s">
+      <c r="B99" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C99" s="24" t="s">
+      <c r="C99" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D99" s="24">
+      <c r="D99" s="23">
         <v>0.75</v>
       </c>
-      <c r="E99" s="83" t="s">
+      <c r="E99" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F99" s="24" t="s">
+      <c r="F99" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="G99" s="82" t="s">
+      <c r="G99" s="81" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="24" t="s">
+      <c r="A100" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B100" s="24" t="s">
+      <c r="B100" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C100" s="24" t="s">
+      <c r="C100" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D100" s="24">
+      <c r="D100" s="23">
         <v>0.25</v>
       </c>
-      <c r="E100" s="83" t="s">
+      <c r="E100" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F100" s="24" t="s">
+      <c r="F100" s="23" t="s">
         <v>339</v>
       </c>
-      <c r="G100" s="82" t="s">
+      <c r="G100" s="81" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="24" t="s">
+      <c r="A101" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B101" s="24" t="s">
+      <c r="B101" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C101" s="24" t="s">
+      <c r="C101" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D101" s="24">
+      <c r="D101" s="23">
         <v>0.25</v>
       </c>
-      <c r="E101" s="83" t="s">
+      <c r="E101" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F101" s="24" t="s">
+      <c r="F101" s="23" t="s">
         <v>340</v>
       </c>
-      <c r="G101" s="82" t="s">
+      <c r="G101" s="81" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="24" t="s">
+      <c r="A102" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B102" s="24" t="s">
+      <c r="B102" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C102" s="24" t="s">
+      <c r="C102" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D102" s="24">
+      <c r="D102" s="23">
         <v>0.25</v>
       </c>
-      <c r="E102" s="83" t="s">
+      <c r="E102" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F102" s="24" t="s">
+      <c r="F102" s="23" t="s">
         <v>341</v>
       </c>
-      <c r="G102" s="82" t="s">
+      <c r="G102" s="81" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="24" t="s">
+      <c r="A103" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B103" s="24" t="s">
+      <c r="B103" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C103" s="24" t="s">
+      <c r="C103" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D103" s="24">
+      <c r="D103" s="23">
         <v>0.5</v>
       </c>
-      <c r="E103" s="83" t="s">
+      <c r="E103" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F103" s="24" t="s">
+      <c r="F103" s="23" t="s">
         <v>343</v>
       </c>
-      <c r="G103" s="82" t="s">
+      <c r="G103" s="81" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="24" t="s">
+      <c r="A104" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B104" s="24" t="s">
+      <c r="B104" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C104" s="24" t="s">
+      <c r="C104" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D104" s="24">
+      <c r="D104" s="23">
         <v>0.33</v>
       </c>
-      <c r="E104" s="83" t="s">
+      <c r="E104" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F104" s="24" t="s">
+      <c r="F104" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="G104" s="82" t="s">
+      <c r="G104" s="81" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="24" t="s">
+      <c r="A105" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B105" s="24" t="s">
+      <c r="B105" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C105" s="24" t="s">
+      <c r="C105" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D105" s="24">
+      <c r="D105" s="23">
         <v>0.25</v>
       </c>
-      <c r="E105" s="83" t="s">
+      <c r="E105" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F105" s="24" t="s">
+      <c r="F105" s="23" t="s">
         <v>346</v>
       </c>
-      <c r="G105" s="82" t="s">
+      <c r="G105" s="81" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" s="24" t="s">
+      <c r="A106" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B106" s="24" t="s">
+      <c r="B106" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C106" s="24" t="s">
+      <c r="C106" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D106" s="24">
+      <c r="D106" s="23">
         <v>0.33</v>
       </c>
-      <c r="E106" s="83" t="s">
+      <c r="E106" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F106" s="24" t="s">
+      <c r="F106" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="G106" s="82" t="s">
+      <c r="G106" s="81" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="24" t="s">
+      <c r="A107" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B107" s="24" t="s">
+      <c r="B107" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C107" s="24" t="s">
+      <c r="C107" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D107" s="24">
+      <c r="D107" s="23">
         <v>0.5</v>
       </c>
-      <c r="E107" s="83" t="s">
+      <c r="E107" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F107" s="24" t="s">
+      <c r="F107" s="23" t="s">
         <v>349</v>
       </c>
-      <c r="G107" s="82" t="s">
+      <c r="G107" s="81" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="24" t="s">
+      <c r="A108" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B108" s="24" t="s">
+      <c r="B108" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C108" s="24" t="s">
+      <c r="C108" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D108" s="24">
+      <c r="D108" s="23">
         <v>0.17</v>
       </c>
-      <c r="E108" s="83" t="s">
+      <c r="E108" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F108" s="24" t="s">
+      <c r="F108" s="23" t="s">
         <v>350</v>
       </c>
-      <c r="G108" s="82" t="s">
+      <c r="G108" s="81" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="24" t="s">
+      <c r="A109" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="B109" s="24" t="s">
+      <c r="B109" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C109" s="24" t="s">
+      <c r="C109" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D109" s="24">
+      <c r="D109" s="23">
         <v>0.17</v>
       </c>
-      <c r="E109" s="83" t="s">
+      <c r="E109" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F109" s="24" t="s">
+      <c r="F109" s="23" t="s">
         <v>351</v>
       </c>
-      <c r="G109" s="82" t="s">
+      <c r="G109" s="81" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="24" t="s">
+      <c r="A110" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="B110" s="24" t="s">
+      <c r="B110" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C110" s="24" t="s">
+      <c r="C110" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D110" s="24">
+      <c r="D110" s="23">
         <v>0.5</v>
       </c>
-      <c r="E110" s="83" t="s">
+      <c r="E110" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F110" s="24" t="s">
+      <c r="F110" s="23" t="s">
         <v>353</v>
       </c>
-      <c r="G110" s="82" t="s">
+      <c r="G110" s="81" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="24" t="s">
+      <c r="A111" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="B111" s="24" t="s">
+      <c r="B111" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C111" s="24" t="s">
+      <c r="C111" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D111" s="24">
+      <c r="D111" s="23">
         <v>0.25</v>
       </c>
-      <c r="E111" s="83" t="s">
+      <c r="E111" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F111" s="24" t="s">
+      <c r="F111" s="23" t="s">
         <v>355</v>
       </c>
-      <c r="G111" s="82" t="s">
+      <c r="G111" s="81" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="24" t="s">
+      <c r="A112" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="B112" s="24" t="s">
+      <c r="B112" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C112" s="24" t="s">
+      <c r="C112" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D112" s="24">
+      <c r="D112" s="23">
         <v>1</v>
       </c>
-      <c r="E112" s="83" t="s">
+      <c r="E112" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F112" s="24" t="s">
+      <c r="F112" s="23" t="s">
         <v>357</v>
       </c>
-      <c r="G112" s="82" t="s">
+      <c r="G112" s="81" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" s="24" t="s">
+      <c r="A113" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="B113" s="24" t="s">
+      <c r="B113" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C113" s="24" t="s">
+      <c r="C113" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D113" s="24">
+      <c r="D113" s="23">
         <v>0.5</v>
       </c>
-      <c r="E113" s="83" t="s">
+      <c r="E113" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F113" s="24" t="s">
+      <c r="F113" s="23" t="s">
         <v>359</v>
       </c>
-      <c r="G113" s="82" t="s">
+      <c r="G113" s="81" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="24" t="s">
+      <c r="A114" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="B114" s="24" t="s">
+      <c r="B114" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="24" t="s">
+      <c r="C114" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D114" s="24">
+      <c r="D114" s="23">
         <v>0.75</v>
       </c>
-      <c r="E114" s="83" t="s">
+      <c r="E114" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F114" s="24" t="s">
+      <c r="F114" s="23" t="s">
         <v>361</v>
       </c>
-      <c r="G114" s="82" t="s">
+      <c r="G114" s="81" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="B115" s="24" t="s">
+      <c r="B115" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C115" s="24" t="s">
+      <c r="C115" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D115" s="24">
+      <c r="D115" s="23">
         <v>0.5</v>
       </c>
-      <c r="E115" s="83" t="s">
+      <c r="E115" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F115" s="24" t="s">
+      <c r="F115" s="23" t="s">
         <v>363</v>
       </c>
-      <c r="G115" s="82" t="s">
+      <c r="G115" s="81" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="24" t="s">
+      <c r="A116" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="B116" s="24" t="s">
+      <c r="B116" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C116" s="24" t="s">
+      <c r="C116" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D116" s="24">
+      <c r="D116" s="23">
         <v>0.5</v>
       </c>
-      <c r="E116" s="83" t="s">
+      <c r="E116" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F116" s="24" t="s">
+      <c r="F116" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="G116" s="82" t="s">
+      <c r="G116" s="81" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="24" t="s">
+      <c r="A117" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="B117" s="24" t="s">
+      <c r="B117" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C117" s="24" t="s">
+      <c r="C117" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D117" s="24">
+      <c r="D117" s="23">
         <v>0.33</v>
       </c>
-      <c r="E117" s="83" t="s">
+      <c r="E117" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F117" s="24" t="s">
+      <c r="F117" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="G117" s="82" t="s">
+      <c r="G117" s="81" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="24" t="s">
+      <c r="A118" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="B118" s="24" t="s">
+      <c r="B118" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="C118" s="24" t="s">
+      <c r="C118" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="D118" s="24">
+      <c r="D118" s="23">
         <v>0.25</v>
       </c>
-      <c r="E118" s="83" t="s">
+      <c r="E118" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="F118" s="24" t="s">
+      <c r="F118" s="23" t="s">
         <v>369</v>
       </c>
-      <c r="G118" s="82" t="s">
+      <c r="G118" s="81" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="84">
+      <c r="A119" s="83">
         <v>46066</v>
       </c>
-      <c r="B119" s="24" t="s">
+      <c r="B119" s="23" t="s">
         <v>279</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D119" s="85">
+      <c r="D119" s="84">
         <v>4</v>
       </c>
-      <c r="E119" s="83" t="s">
+      <c r="E119" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="F119" s="87"/>
-      <c r="G119" s="21" t="s">
+      <c r="F119" s="86"/>
+      <c r="G119" s="20" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="84">
+      <c r="A120" s="83">
         <v>46066</v>
       </c>
-      <c r="B120" s="24" t="s">
+      <c r="B120" s="23" t="s">
         <v>279</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="86">
+      <c r="D120" s="85">
         <v>2</v>
       </c>
-      <c r="E120" s="83" t="s">
+      <c r="E120" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="F120" s="87"/>
-      <c r="G120" s="21" t="s">
+      <c r="F120" s="86"/>
+      <c r="G120" s="20" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="84" t="s">
+      <c r="A121" s="83" t="s">
         <v>382</v>
       </c>
-      <c r="B121" s="24" t="s">
+      <c r="B121" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D121" s="86">
+      <c r="D121" s="85">
         <v>1</v>
       </c>
-      <c r="E121" s="27" t="s">
+      <c r="E121" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="F121" s="18" t="s">
+      <c r="F121" s="17" t="s">
         <v>411</v>
       </c>
       <c r="G121" t="s">
@@ -5056,22 +5152,22 @@
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="84" t="s">
+      <c r="A122" s="83" t="s">
         <v>382</v>
       </c>
-      <c r="B122" s="24" t="s">
+      <c r="B122" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D122" s="86">
+      <c r="D122" s="85">
         <v>0.5</v>
       </c>
-      <c r="E122" s="27" t="s">
+      <c r="E122" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="F122" s="18" t="s">
+      <c r="F122" s="17" t="s">
         <v>411</v>
       </c>
       <c r="G122" t="s">
@@ -5079,22 +5175,22 @@
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="84" t="s">
+      <c r="A123" s="83" t="s">
         <v>382</v>
       </c>
-      <c r="B123" s="24" t="s">
+      <c r="B123" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D123" s="86">
+      <c r="D123" s="85">
         <v>1</v>
       </c>
-      <c r="E123" s="27" t="s">
+      <c r="E123" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="F123" s="18" t="s">
+      <c r="F123" s="17" t="s">
         <v>411</v>
       </c>
       <c r="G123" t="s">
@@ -5102,22 +5198,22 @@
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="84" t="s">
+      <c r="A124" s="83" t="s">
         <v>384</v>
       </c>
-      <c r="B124" s="24" t="s">
+      <c r="B124" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D124" s="86">
+      <c r="D124" s="85">
         <v>0.75</v>
       </c>
-      <c r="E124" s="27" t="s">
+      <c r="E124" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="F124" s="18" t="s">
+      <c r="F124" s="17" t="s">
         <v>411</v>
       </c>
       <c r="G124" t="s">
@@ -5125,22 +5221,22 @@
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="84" t="s">
+      <c r="A125" s="83" t="s">
         <v>384</v>
       </c>
-      <c r="B125" s="24" t="s">
+      <c r="B125" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D125" s="86">
+      <c r="D125" s="85">
         <v>1</v>
       </c>
-      <c r="E125" s="27" t="s">
+      <c r="E125" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="F125" s="18" t="s">
+      <c r="F125" s="17" t="s">
         <v>411</v>
       </c>
       <c r="G125" t="s">
@@ -5148,22 +5244,22 @@
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="84" t="s">
+      <c r="A126" s="83" t="s">
         <v>384</v>
       </c>
-      <c r="B126" s="24" t="s">
+      <c r="B126" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D126" s="86">
+      <c r="D126" s="85">
         <v>0.75</v>
       </c>
-      <c r="E126" s="27" t="s">
+      <c r="E126" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="F126" s="18" t="s">
+      <c r="F126" s="17" t="s">
         <v>411</v>
       </c>
       <c r="G126" t="s">
@@ -5171,22 +5267,22 @@
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="84" t="s">
+      <c r="A127" s="83" t="s">
         <v>385</v>
       </c>
-      <c r="B127" s="24" t="s">
+      <c r="B127" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D127" s="86">
+      <c r="D127" s="85">
         <v>0.5</v>
       </c>
-      <c r="E127" s="27" t="s">
+      <c r="E127" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="F127" s="18" t="s">
+      <c r="F127" s="17" t="s">
         <v>411</v>
       </c>
       <c r="G127" t="s">
@@ -5194,22 +5290,22 @@
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="84" t="s">
+      <c r="A128" s="83" t="s">
         <v>385</v>
       </c>
-      <c r="B128" s="24" t="s">
+      <c r="B128" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D128" s="86">
+      <c r="D128" s="85">
         <v>0.5</v>
       </c>
-      <c r="E128" s="27" t="s">
+      <c r="E128" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="F128" s="18" t="s">
+      <c r="F128" s="17" t="s">
         <v>411</v>
       </c>
       <c r="G128" t="s">
@@ -5217,22 +5313,22 @@
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="84" t="s">
+      <c r="A129" s="83" t="s">
         <v>385</v>
       </c>
-      <c r="B129" s="24" t="s">
+      <c r="B129" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D129" s="86">
+      <c r="D129" s="85">
         <v>0.5</v>
       </c>
-      <c r="E129" s="27" t="s">
+      <c r="E129" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="F129" s="18" t="s">
+      <c r="F129" s="17" t="s">
         <v>411</v>
       </c>
       <c r="G129" t="s">
@@ -5240,22 +5336,22 @@
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="84" t="s">
+      <c r="A130" s="83" t="s">
         <v>385</v>
       </c>
-      <c r="B130" s="24" t="s">
+      <c r="B130" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D130" s="86">
+      <c r="D130" s="85">
         <v>0.25</v>
       </c>
-      <c r="E130" s="27" t="s">
+      <c r="E130" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="F130" s="18" t="s">
+      <c r="F130" s="17" t="s">
         <v>411</v>
       </c>
       <c r="G130" t="s">
@@ -5263,22 +5359,22 @@
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="84" t="s">
+      <c r="A131" s="83" t="s">
         <v>386</v>
       </c>
-      <c r="B131" s="24" t="s">
+      <c r="B131" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D131" s="86">
+      <c r="D131" s="85">
         <v>0.5</v>
       </c>
-      <c r="E131" s="104" t="s">
+      <c r="E131" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="F131" s="18" t="s">
+      <c r="F131" s="17" t="s">
         <v>412</v>
       </c>
       <c r="G131" t="s">
@@ -5286,22 +5382,22 @@
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="84" t="s">
+      <c r="A132" s="83" t="s">
         <v>386</v>
       </c>
-      <c r="B132" s="24" t="s">
+      <c r="B132" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D132" s="86">
+      <c r="D132" s="85">
         <v>1.5</v>
       </c>
-      <c r="E132" s="104" t="s">
+      <c r="E132" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="F132" s="18" t="s">
+      <c r="F132" s="17" t="s">
         <v>412</v>
       </c>
       <c r="G132" t="s">
@@ -5309,22 +5405,22 @@
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="84" t="s">
+      <c r="A133" s="83" t="s">
         <v>387</v>
       </c>
-      <c r="B133" s="24" t="s">
+      <c r="B133" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D133" s="86">
+      <c r="D133" s="85">
         <v>1.5</v>
       </c>
-      <c r="E133" s="104" t="s">
+      <c r="E133" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="F133" s="18" t="s">
+      <c r="F133" s="17" t="s">
         <v>412</v>
       </c>
       <c r="G133" t="s">
@@ -5332,22 +5428,22 @@
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" s="84" t="s">
+      <c r="A134" s="83" t="s">
         <v>387</v>
       </c>
-      <c r="B134" s="24" t="s">
+      <c r="B134" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D134" s="86">
+      <c r="D134" s="85">
         <v>1</v>
       </c>
-      <c r="E134" s="104" t="s">
+      <c r="E134" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="F134" s="18" t="s">
+      <c r="F134" s="17" t="s">
         <v>412</v>
       </c>
       <c r="G134" t="s">
@@ -5355,22 +5451,22 @@
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="84" t="s">
+      <c r="A135" s="83" t="s">
         <v>387</v>
       </c>
-      <c r="B135" s="24" t="s">
+      <c r="B135" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D135" s="86">
+      <c r="D135" s="85">
         <v>1</v>
       </c>
-      <c r="E135" s="104" t="s">
+      <c r="E135" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="F135" s="18" t="s">
+      <c r="F135" s="17" t="s">
         <v>412</v>
       </c>
       <c r="G135" t="s">
@@ -5378,22 +5474,22 @@
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" s="84" t="s">
+      <c r="A136" s="83" t="s">
         <v>388</v>
       </c>
-      <c r="B136" s="24" t="s">
+      <c r="B136" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D136" s="86">
+      <c r="D136" s="85">
         <v>0.75</v>
       </c>
-      <c r="E136" s="104" t="s">
+      <c r="E136" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="F136" s="18" t="s">
+      <c r="F136" s="17" t="s">
         <v>412</v>
       </c>
       <c r="G136" t="s">
@@ -5401,22 +5497,22 @@
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="84" t="s">
+      <c r="A137" s="83" t="s">
         <v>388</v>
       </c>
-      <c r="B137" s="24" t="s">
+      <c r="B137" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D137" s="86">
+      <c r="D137" s="85">
         <v>0.75</v>
       </c>
-      <c r="E137" s="104" t="s">
+      <c r="E137" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="F137" s="18" t="s">
+      <c r="F137" s="17" t="s">
         <v>412</v>
       </c>
       <c r="G137" t="s">
@@ -5424,22 +5520,22 @@
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="84" t="s">
+      <c r="A138" s="83" t="s">
         <v>388</v>
       </c>
-      <c r="B138" s="24" t="s">
+      <c r="B138" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D138" s="86">
+      <c r="D138" s="85">
         <v>0.5</v>
       </c>
-      <c r="E138" s="104" t="s">
+      <c r="E138" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="F138" s="18" t="s">
+      <c r="F138" s="17" t="s">
         <v>412</v>
       </c>
       <c r="G138" t="s">
@@ -5447,22 +5543,22 @@
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="84" t="s">
+      <c r="A139" s="83" t="s">
         <v>388</v>
       </c>
-      <c r="B139" s="24" t="s">
+      <c r="B139" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D139" s="86">
+      <c r="D139" s="85">
         <v>0.25</v>
       </c>
-      <c r="E139" s="104" t="s">
+      <c r="E139" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="F139" s="18" t="s">
+      <c r="F139" s="17" t="s">
         <v>412</v>
       </c>
       <c r="G139" t="s">
@@ -5470,22 +5566,22 @@
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" s="84" t="s">
+      <c r="A140" s="83" t="s">
         <v>388</v>
       </c>
-      <c r="B140" s="24" t="s">
+      <c r="B140" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D140" s="86">
+      <c r="D140" s="85">
         <v>0.25</v>
       </c>
-      <c r="E140" s="104" t="s">
+      <c r="E140" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="F140" s="18" t="s">
+      <c r="F140" s="17" t="s">
         <v>412</v>
       </c>
       <c r="G140" t="s">
@@ -5493,114 +5589,559 @@
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141" s="84" t="s">
+      <c r="A141" s="83" t="s">
         <v>388</v>
       </c>
-      <c r="B141" s="24" t="s">
+      <c r="B141" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D141" s="86">
+      <c r="D141" s="85">
         <v>0.75</v>
       </c>
-      <c r="E141" s="25" t="s">
+      <c r="E141" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="F141" s="18"/>
+      <c r="F141" s="17"/>
       <c r="G141" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" s="84" t="s">
+      <c r="A142" s="83" t="s">
         <v>388</v>
       </c>
-      <c r="B142" s="24" t="s">
+      <c r="B142" s="23" t="s">
         <v>383</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D142" s="86">
+      <c r="D142" s="85">
         <v>0.75</v>
       </c>
-      <c r="E142" s="25" t="s">
+      <c r="E142" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="F142" s="18"/>
+      <c r="F142" s="17"/>
       <c r="G142" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" s="1"/>
-      <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="25"/>
-      <c r="F143" s="18"/>
-      <c r="G143" s="21"/>
+      <c r="A143" s="105">
+        <v>46084</v>
+      </c>
+      <c r="B143" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D143" s="108">
+        <v>1</v>
+      </c>
+      <c r="E143" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F143" s="17"/>
+      <c r="G143" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" s="1"/>
-      <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="25"/>
-      <c r="F144" s="18"/>
-      <c r="G144" s="21"/>
+      <c r="A144" s="105">
+        <v>46084</v>
+      </c>
+      <c r="B144" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D144" s="108">
+        <v>0.75</v>
+      </c>
+      <c r="E144" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F144" s="17"/>
+      <c r="G144" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" s="1"/>
-      <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="25"/>
-      <c r="F145" s="18"/>
-      <c r="G145" s="21"/>
+      <c r="A145" s="105">
+        <v>46085</v>
+      </c>
+      <c r="B145" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D145" s="108">
+        <v>1</v>
+      </c>
+      <c r="E145" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F145" s="17"/>
+      <c r="G145" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146" s="1"/>
-      <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="25"/>
-      <c r="F146" s="18"/>
-      <c r="G146" s="21"/>
+      <c r="A146" s="105">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D146" s="108">
+        <v>0.75</v>
+      </c>
+      <c r="E146" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F146" s="17"/>
+      <c r="G146" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="1"/>
-      <c r="B147" s="1"/>
-      <c r="C147" s="1"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="25"/>
-      <c r="F147" s="18"/>
-      <c r="G147" s="21"/>
+      <c r="A147" s="105">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D147" s="108">
+        <v>1</v>
+      </c>
+      <c r="E147" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F147" s="17"/>
+      <c r="G147" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148" s="93" t="s">
+      <c r="A148" s="105">
+        <v>46086</v>
+      </c>
+      <c r="B148" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D148" s="108">
+        <v>0.5</v>
+      </c>
+      <c r="E148" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F148" s="17"/>
+      <c r="G148" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" s="105">
+        <v>46087</v>
+      </c>
+      <c r="B149" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D149" s="108">
+        <v>0.5</v>
+      </c>
+      <c r="E149" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F149" s="17"/>
+      <c r="G149" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" s="105">
+        <v>46088</v>
+      </c>
+      <c r="B150" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D150" s="108">
+        <v>1</v>
+      </c>
+      <c r="E150" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="F150" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="G150" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" s="105">
+        <v>46088</v>
+      </c>
+      <c r="B151" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D151" s="108">
+        <v>0.75</v>
+      </c>
+      <c r="E151" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="F151" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="G151" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="105">
+        <v>46089</v>
+      </c>
+      <c r="B152" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D152" s="108">
+        <v>0.75</v>
+      </c>
+      <c r="E152" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="F152" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="G152" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="105">
+        <v>46089</v>
+      </c>
+      <c r="B153" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D153" s="108">
+        <v>0.5</v>
+      </c>
+      <c r="E153" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="F153" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="G153" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" s="105">
+        <v>46089</v>
+      </c>
+      <c r="B154" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D154" s="108">
+        <v>0.5</v>
+      </c>
+      <c r="E154" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="F154" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="G154" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="105">
+        <v>46089</v>
+      </c>
+      <c r="B155" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D155" s="108">
+        <v>1.5</v>
+      </c>
+      <c r="E155" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="F155" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="G155" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="105">
+        <v>46090</v>
+      </c>
+      <c r="B156" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D156" s="108">
+        <v>1.5</v>
+      </c>
+      <c r="E156" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="F156" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="G156" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="105">
+        <v>46090</v>
+      </c>
+      <c r="B157" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D157" s="108">
+        <v>1</v>
+      </c>
+      <c r="E157" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="F157" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="G157" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" s="106">
+        <v>46090</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D158" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E158" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="F158" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="G158" s="20" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" s="106">
+        <v>46090</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D159" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="E159" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="F159" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="G159" s="20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="106">
+        <v>46090</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D160" s="4">
+        <v>1</v>
+      </c>
+      <c r="E160" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="F160" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="G160" s="20" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="106">
+        <v>46090</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D161" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E161" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="F161" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="G161" s="20" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" s="106">
+        <v>46090</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D162" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="E162" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="F162" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="G162" s="20" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="107">
+        <v>46090</v>
+      </c>
+      <c r="B163" s="104" t="s">
+        <v>383</v>
+      </c>
+      <c r="C163" s="104" t="s">
+        <v>43</v>
+      </c>
+      <c r="D163" s="110">
+        <v>0.25</v>
+      </c>
+      <c r="E163" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="F163" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="G163" s="20" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="107">
+        <v>46090</v>
+      </c>
+      <c r="B164" s="104" t="s">
+        <v>383</v>
+      </c>
+      <c r="C164" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="D164" s="110">
+        <v>0.75</v>
+      </c>
+      <c r="E164" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F164" s="17"/>
+      <c r="G164" s="20" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="B148" s="94"/>
-      <c r="C148" s="94"/>
-      <c r="D148" s="95"/>
-      <c r="E148" s="74">
-        <f>SUM(D6:D147)</f>
-        <v>101.85</v>
-      </c>
-      <c r="F148" s="19"/>
-      <c r="G148" s="22"/>
+      <c r="B165" s="89"/>
+      <c r="C165" s="89"/>
+      <c r="D165" s="90"/>
+      <c r="E165" s="73">
+        <f>SUM(D6:D164)</f>
+        <v>119.85</v>
+      </c>
+      <c r="F165" s="18"/>
+      <c r="G165" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A148:D148"/>
+    <mergeCell ref="A165:D165"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E200">
+  <conditionalFormatting sqref="E6:E217">
     <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"0: Environment Setup"</formula>
     </cfRule>
@@ -5671,9 +6212,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Category" error="Please select a category from the dropdown list." xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>Categories!$A$4:$A$24</xm:f>
+            <xm:f>Categories!$A$4:$A$25</xm:f>
           </x14:formula1>
-          <xm:sqref>E6:E200</xm:sqref>
+          <xm:sqref>E6:E217</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5683,7 +6224,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -5691,998 +6232,1007 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="103" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
     </row>
     <row r="3" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="100" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="33" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="35">
+      <c r="A5" s="34">
         <v>0</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="36">
         <v>5</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="37">
         <f>B46</f>
         <v>11.85</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="38">
         <f t="shared" ref="E5:E11" si="0">IF(C5=0,0,MIN(D5/C5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="40">
+      <c r="A6" s="39">
         <v>1</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="36">
         <v>15</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="37">
         <f>SUM(B47:B51)</f>
         <v>14.26</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="38">
         <f t="shared" si="0"/>
         <v>0.95066666666666666</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="42">
+      <c r="A7" s="41">
         <v>2</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="42" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="36">
         <v>25</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="37">
         <f>SUM(B52:B55)</f>
         <v>29.990000000000002</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="38">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="44">
+      <c r="A8" s="43">
         <v>3</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="36">
         <v>20</v>
       </c>
-      <c r="D8" s="38">
-        <f>SUM(B56:B59)</f>
-        <v>6.75</v>
-      </c>
-      <c r="E8" s="39">
+      <c r="D8" s="37">
+        <f>SUM(B56:B60)</f>
+        <v>26.5</v>
+      </c>
+      <c r="E8" s="38">
         <f t="shared" si="0"/>
-        <v>0.33750000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="46">
+      <c r="A9" s="45">
         <v>4</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="36">
         <v>20</v>
       </c>
-      <c r="D9" s="38">
-        <f>SUM(B60:B61)</f>
+      <c r="D9" s="37">
+        <f>SUM(B61:B62)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="48">
+      <c r="A10" s="47">
         <v>5</v>
       </c>
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="36">
         <v>15</v>
       </c>
-      <c r="D10" s="38">
-        <f>SUM(B62:B63)</f>
+      <c r="D10" s="37">
+        <f>SUM(B63:B64)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="39">
+      <c r="E10" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="50">
+      <c r="A11" s="49">
         <v>6</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="36">
         <v>18</v>
       </c>
-      <c r="D11" s="38">
-        <f>SUM(B64)</f>
-        <v>13.25</v>
-      </c>
-      <c r="E11" s="39">
+      <c r="D11" s="37">
+        <f>SUM(B65)</f>
+        <v>14</v>
+      </c>
+      <c r="E11" s="38">
         <f t="shared" si="0"/>
-        <v>0.73611111111111116</v>
+        <v>0.77777777777777779</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="54">
+      <c r="B12" s="52"/>
+      <c r="C12" s="53">
         <f>SUM(C5:C11)</f>
         <v>118</v>
       </c>
-      <c r="D12" s="55">
+      <c r="D12" s="54">
         <f>SUM(D5:D11)</f>
-        <v>76.099999999999994</v>
-      </c>
-      <c r="E12" s="56">
+        <v>96.6</v>
+      </c>
+      <c r="E12" s="55">
         <f>IF(C12=0,0,D12/C12)</f>
-        <v>0.64491525423728813</v>
+        <v>0.81864406779661014</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="90" t="s">
+      <c r="A14" s="101" t="s">
         <v>152</v>
       </c>
-      <c r="B14" s="91"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="91"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="91"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="91"/>
-      <c r="N14" s="91"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="102"/>
+      <c r="N14" s="102"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="G15" s="34" t="s">
+      <c r="G15" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="H15" s="34" t="s">
+      <c r="H15" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="I15" s="34" t="s">
+      <c r="I15" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="J15" s="34" t="s">
+      <c r="J15" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="K15" s="34" t="s">
+      <c r="K15" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="L15" s="34" t="s">
+      <c r="L15" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="M15" s="34" t="s">
+      <c r="M15" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="N15" s="34" t="s">
+      <c r="N15" s="33" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57" t="s">
+      <c r="A16" s="56"/>
+      <c r="B16" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="56" t="s">
         <v>168</v>
       </c>
-      <c r="D16" s="57" t="s">
+      <c r="D16" s="56" t="s">
         <v>169</v>
       </c>
-      <c r="E16" s="57" t="s">
+      <c r="E16" s="56" t="s">
         <v>170</v>
       </c>
-      <c r="F16" s="57" t="s">
+      <c r="F16" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="G16" s="57" t="s">
+      <c r="G16" s="56" t="s">
         <v>172</v>
       </c>
-      <c r="H16" s="57" t="s">
+      <c r="H16" s="56" t="s">
         <v>173</v>
       </c>
-      <c r="I16" s="57" t="s">
+      <c r="I16" s="56" t="s">
         <v>174</v>
       </c>
-      <c r="J16" s="57" t="s">
+      <c r="J16" s="56" t="s">
         <v>175</v>
       </c>
-      <c r="K16" s="57" t="s">
+      <c r="K16" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="L16" s="57" t="s">
+      <c r="L16" s="56" t="s">
         <v>177</v>
       </c>
-      <c r="M16" s="57" t="s">
+      <c r="M16" s="56" t="s">
         <v>178</v>
       </c>
-      <c r="N16" s="57" t="s">
+      <c r="N16" s="56" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="53"/>
-      <c r="N17" s="53"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="B18" s="59"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="53"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="81" t="s">
+      <c r="A19" s="80" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="53"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-      <c r="N19" s="53"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="52"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="80" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="53"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
+      <c r="K20" s="52"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="52"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="81" t="s">
+      <c r="A21" s="80" t="s">
         <v>184</v>
       </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="52"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="81" t="s">
+      <c r="A22" s="80" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="53"/>
-      <c r="N22" s="53"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="52"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="81" t="s">
+      <c r="A23" s="80" t="s">
         <v>186</v>
       </c>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="52"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="51" t="s">
         <v>187</v>
       </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="52"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="81" t="s">
+      <c r="A25" s="80" t="s">
         <v>188</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="53"/>
-      <c r="N25" s="53"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="52"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="81" t="s">
+      <c r="A26" s="80" t="s">
         <v>189</v>
       </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="53"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="52"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="81" t="s">
+      <c r="A27" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="B27" s="53"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="52"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="81" t="s">
+      <c r="A28" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="52"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="52" t="s">
+      <c r="A29" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="B29" s="53"/>
-      <c r="C29" s="53"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="53"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="53"/>
-      <c r="N29" s="53"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="52"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="52"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="81" t="s">
+      <c r="A30" s="80" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="53"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="53"/>
-      <c r="N30" s="53"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="52"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="81" t="s">
+      <c r="A31" s="80" t="s">
         <v>194</v>
       </c>
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="63"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="53"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="53"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="52"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="81" t="s">
+      <c r="A32" s="80" t="s">
         <v>195</v>
       </c>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="63"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="53"/>
-      <c r="N32" s="53"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="52"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="81" t="s">
+      <c r="A33" s="80" t="s">
         <v>196</v>
       </c>
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="63"/>
-      <c r="K33" s="63"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="62"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="52"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="81" t="s">
+      <c r="A34" s="80" t="s">
         <v>381</v>
       </c>
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="63"/>
-      <c r="K34" s="63"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="53"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="52"/>
+      <c r="M34" s="52"/>
+      <c r="N34" s="52"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="52" t="s">
+      <c r="A35" s="51" t="s">
         <v>197</v>
       </c>
-      <c r="B35" s="53"/>
-      <c r="C35" s="53"/>
-      <c r="D35" s="53"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="63"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="53"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="81" t="s">
+      <c r="A36" s="80" t="s">
         <v>198</v>
       </c>
-      <c r="B36" s="53"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="64" t="s">
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="63" t="s">
         <v>199</v>
       </c>
-      <c r="G36" s="53"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="53"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="53"/>
-      <c r="N36" s="53"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="52"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="52"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="81" t="s">
+      <c r="A37" s="80" t="s">
         <v>200</v>
       </c>
-      <c r="B37" s="53"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="47"/>
-      <c r="J37" s="47"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="53"/>
-      <c r="N37" s="64" t="s">
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="52"/>
+      <c r="N37" s="63" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="52" t="s">
+      <c r="A38" s="51" t="s">
         <v>201</v>
       </c>
-      <c r="B38" s="53"/>
-      <c r="C38" s="53"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="53"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="53"/>
-      <c r="I38" s="53"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="53"/>
-      <c r="N38" s="53"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="48"/>
+      <c r="K38" s="48"/>
+      <c r="L38" s="48"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="81" t="s">
+      <c r="A39" s="80" t="s">
         <v>202</v>
       </c>
-      <c r="B39" s="53"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="53"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53"/>
-      <c r="H39" s="53"/>
-      <c r="I39" s="53"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="53"/>
-      <c r="N39" s="53"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52"/>
+      <c r="N39" s="52"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="81" t="s">
+      <c r="A40" s="80" t="s">
         <v>203</v>
       </c>
-      <c r="B40" s="53"/>
-      <c r="C40" s="53"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="53"/>
-      <c r="G40" s="53"/>
-      <c r="H40" s="53"/>
-      <c r="I40" s="53"/>
-      <c r="J40" s="53"/>
-      <c r="K40" s="49"/>
-      <c r="L40" s="49"/>
-      <c r="M40" s="53"/>
-      <c r="N40" s="53"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="48"/>
+      <c r="L40" s="48"/>
+      <c r="M40" s="52"/>
+      <c r="N40" s="52"/>
     </row>
     <row r="41" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="52" t="s">
+      <c r="A41" s="51" t="s">
         <v>204</v>
       </c>
-      <c r="B41" s="53"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="53"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="53"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="53"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="51"/>
-      <c r="M41" s="51"/>
-      <c r="N41" s="51"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="52"/>
+      <c r="K41" s="52"/>
+      <c r="L41" s="50"/>
+      <c r="M41" s="50"/>
+      <c r="N41" s="50"/>
     </row>
     <row r="42" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="80"/>
+      <c r="A42" s="79"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="75"/>
+      <c r="C43" s="74"/>
     </row>
     <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="65" t="s">
+      <c r="A44" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="3"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="34" t="s">
+      <c r="A45" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B45" s="66" t="s">
+      <c r="B45" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="C45" s="4"/>
+      <c r="C45" s="3"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="38">
+      <c r="B46" s="37">
         <f>SUMIF('Work Log'!E:E,"0: Environment Setup",'Work Log'!D:D)</f>
         <v>11.85</v>
       </c>
-      <c r="C46" s="4"/>
+      <c r="C46" s="3"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="41" t="s">
+      <c r="A47" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="38">
+      <c r="B47" s="37">
         <f>SUMIF('Work Log'!E:E,"1A: UI Mockups",'Work Log'!D:D)</f>
         <v>2.81</v>
       </c>
-      <c r="C47" s="4"/>
+      <c r="C47" s="3"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="41" t="s">
+      <c r="A48" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="B48" s="38">
+      <c r="B48" s="37">
         <f>SUMIF('Work Log'!E:E,"1B: Project Structure",'Work Log'!D:D)</f>
         <v>0.67</v>
       </c>
-      <c r="C48" s="4"/>
+      <c r="C48" s="3"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="41" t="s">
+      <c r="A49" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="38">
+      <c r="B49" s="37">
         <f>SUMIF('Work Log'!E:E,"1C: Database Setup",'Work Log'!D:D)</f>
         <v>3.18</v>
       </c>
-      <c r="C49" s="4"/>
+      <c r="C49" s="3"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="41" t="s">
+      <c r="A50" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="B50" s="38">
+      <c r="B50" s="37">
         <f>SUMIF('Work Log'!E:E,"1D: Authentication Feature",'Work Log'!D:D)</f>
         <v>6</v>
       </c>
-      <c r="C50" s="4"/>
+      <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="41" t="s">
+      <c r="A51" s="40" t="s">
         <v>207</v>
       </c>
-      <c r="B51" s="38">
+      <c r="B51" s="37">
         <f>SUMIF('Work Log'!E:E,"1E: Basic Navigation",'Work Log'!D:D)</f>
         <v>1.5999999999999999</v>
       </c>
-      <c r="C51" s="4"/>
+      <c r="C51" s="3"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="43" t="s">
+      <c r="A52" s="42" t="s">
         <v>208</v>
       </c>
-      <c r="B52" s="38">
+      <c r="B52" s="37">
         <f>SUMIF('Work Log'!E:E,"2A: Open AI Integration",'Work Log'!D:D)</f>
         <v>2.08</v>
       </c>
-      <c r="C52" s="4"/>
+      <c r="C52" s="3"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="43" t="s">
+      <c r="A53" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="38">
+      <c r="B53" s="37">
         <f>SUMIF('Work Log'!E:E,"2B: Safety Layer - CTAS Rules",'Work Log'!D:D)</f>
         <v>2.75</v>
       </c>
-      <c r="C53" s="4"/>
+      <c r="C53" s="3"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="43" t="s">
+      <c r="A54" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="B54" s="38">
+      <c r="B54" s="37">
         <f>SUMIF('Work Log'!E:E,"2C: ML Model Training",'Work Log'!D:D)</f>
         <v>9</v>
       </c>
-      <c r="C54" s="4"/>
+      <c r="C54" s="3"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="43" t="s">
+      <c r="A55" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="B55" s="38">
+      <c r="B55" s="37">
         <f>SUMIF('Work Log'!E:E,"2D: Chatbot UI + Integration",'Work Log'!D:D)</f>
         <v>16.16</v>
       </c>
-      <c r="C55" s="4"/>
+      <c r="C55" s="3"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="45" t="s">
+      <c r="A56" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="B56" s="38">
+      <c r="B56" s="37">
         <f>SUMIF('Work Log'!E:E,"3A: Home Dashboard",'Work Log'!D:D)</f>
         <v>6.75</v>
       </c>
-      <c r="C56" s="4"/>
+      <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="45" t="s">
+      <c r="A57" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="B57" s="38">
-        <f>SUMIF('Work Log'!E:E,"3B: My Dashboard - Personal Analytics",'Work Log'!D:D)</f>
-        <v>0</v>
-      </c>
-      <c r="C57" s="4"/>
+      <c r="B57" s="37">
+        <f>SUMIF('Work Log'!E:E,"3B: My Dashboard - Personal Analytics ",'Work Log'!D:D)</f>
+        <v>11.5</v>
+      </c>
+      <c r="C57" s="3"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="45" t="s">
+      <c r="A58" s="44" t="s">
         <v>214</v>
       </c>
-      <c r="B58" s="38">
+      <c r="B58" s="37">
         <f>SUMIF('Work Log'!E:E,"3C: Facility Finder",'Work Log'!D:D)</f>
-        <v>0</v>
-      </c>
-      <c r="C58" s="4"/>
+        <v>3.5</v>
+      </c>
+      <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="45" t="s">
+      <c r="A59" s="44" t="s">
         <v>215</v>
       </c>
-      <c r="B59" s="38">
+      <c r="B59" s="37">
         <f>SUMIF('Work Log'!E:E,"3D: Health Education Library",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
-      <c r="C59" s="4"/>
+      <c r="C59" s="3"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="47" t="s">
+      <c r="A60" s="44" t="s">
+        <v>413</v>
+      </c>
+      <c r="B60" s="37">
+        <f>SUMIF('Work Log'!E:E,"3E: Multi-Turn Chatbot Enhancement",'Work Log'!D:D)</f>
+        <v>4.75</v>
+      </c>
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="B60" s="38">
+      <c r="B61" s="37">
         <f>SUMIF('Work Log'!E:E,"4A: System Analytics Data",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
-      <c r="C60" s="4"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="47" t="s">
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="46" t="s">
         <v>217</v>
       </c>
-      <c r="B61" s="38">
+      <c r="B62" s="37">
         <f>SUMIF('Work Log'!E:E,"4B: System Analytics Dashboard",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
-      <c r="C61" s="4"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="49" t="s">
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="48" t="s">
         <v>218</v>
       </c>
-      <c r="B62" s="38">
+      <c r="B63" s="37">
         <f>SUMIF('Work Log'!E:E,"5A: Deployment",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="49" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="48" t="s">
         <v>219</v>
       </c>
-      <c r="B63" s="38">
+      <c r="B64" s="37">
         <f>SUMIF('Work Log'!E:E,"5B: Testing",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="51" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="B64" s="38">
+      <c r="B65" s="37">
         <f>SUMIF('Work Log'!E:E,"6: Documentation + Submission",'Work Log'!D:D)</f>
-        <v>13.25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="67" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="B65" s="38">
+      <c r="B66" s="37">
         <f>SUMIF('Work Log'!E:E,"Learning &amp; Research",'Work Log'!D:D)</f>
-        <v>17.75</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="68" t="s">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="67" t="s">
         <v>220</v>
       </c>
-      <c r="B66" s="38">
+      <c r="B67" s="54">
         <f>SUMIF('Work Log'!E:E,"Proof of Concept",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="52" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="B67" s="55">
-        <f>SUM(B46:B66)</f>
-        <v>93.850000000000009</v>
+      <c r="B68" s="109">
+        <f>SUM(B46:B67)</f>
+        <v>119.85000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6697,7 +7247,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.109375" bestFit="1" customWidth="1"/>
@@ -6706,26 +7256,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>0</v>
       </c>
       <c r="C4" t="s">
@@ -6733,10 +7283,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>1</v>
       </c>
       <c r="C5" t="s">
@@ -6744,10 +7294,10 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -6755,10 +7305,10 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>1</v>
       </c>
       <c r="C7" t="s">
@@ -6766,10 +7316,10 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
@@ -6777,10 +7327,10 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>1</v>
       </c>
       <c r="C9" t="s">
@@ -6788,10 +7338,10 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>2</v>
       </c>
       <c r="C10" t="s">
@@ -6799,10 +7349,10 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>2</v>
       </c>
       <c r="C11" t="s">
@@ -6810,10 +7360,10 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>2</v>
       </c>
       <c r="C12" t="s">
@@ -6821,10 +7371,10 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>2</v>
       </c>
       <c r="C13" t="s">
@@ -6832,10 +7382,10 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>3</v>
       </c>
       <c r="C14" t="s">
@@ -6843,18 +7393,18 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="8">
         <v>3</v>
       </c>
       <c r="C16" t="s">
@@ -6862,10 +7412,10 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="8">
         <v>3</v>
       </c>
       <c r="C17" t="s">
@@ -6873,79 +7423,90 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="B18" s="8">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B19" s="8">
         <v>4</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B20" s="8">
         <v>4</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B21" s="8">
         <v>5</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B22" s="8">
         <v>5</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="33" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B23" s="8">
         <v>6</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B25" t="s">
         <v>242</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>244</v>
       </c>
     </row>

--- a/DocumentsAndReports/worklog/WorkLog_DesmondChua_W26_4495_S2.xlsx
+++ b/DocumentsAndReports/worklog/WorkLog_DesmondChua_W26_4495_S2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4f25ae689476683/Desmond_New/BC-Health-Platform/DocumentsAndReports/worklog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="8_{08655895-4010-492B-B73A-F5D36A9F8AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47B02F83-99C8-4CB2-8FB6-80065E4D42CC}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="8_{08655895-4010-492B-B73A-F5D36A9F8AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBECE850-859A-40A1-B437-F926111F1D88}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="466">
   <si>
     <t>CSIS 4495 - Applied Research Project</t>
   </si>
@@ -1355,6 +1355,84 @@
   </si>
   <si>
     <t>Prepared Progress Report 3; updated commit history, work log entries, and Gantt chart for PR3 reporting period (Mar 3–9)</t>
+  </si>
+  <si>
+    <t>Sprint 3D Research: Reviewed HealthLinkBC content categories and identified 8 topic areas for the Health Library (Pain &amp; Injury, Cold &amp; Flu, Medications, Prevention &amp; Wellness, Mental Health, Heart Health, Child Health, Emergency Care)</t>
+  </si>
+  <si>
+    <t>Sprint 3D Research: Designed JSON schema for health_articles.json — identified required fields: id, title, category, summary, content, tags, read_time, source_url, banner_color; mapped 18 article topics across 8 categories</t>
+  </si>
+  <si>
+    <t>1 hr 15 min</t>
+  </si>
+  <si>
+    <t>Sprint 3D: Drafted prompt for Claude Code to generate health_articles.json with 18 BC-specific health articles and Health Library page with full page structure matching mockup; reviewed and committed first draft</t>
+  </si>
+  <si>
+    <t>Sprint 3D: Tested initial Health Library page — identified and documented UI bugs: duplicate category grid rendering, search section layout issues, incorrect section header styling; planned targeted fix approach</t>
+  </si>
+  <si>
+    <t>Sprint 3D Fix: Corrected Health Library UI — removed duplicate st.button() row above category icon cards, replaced teal section_header() on Browse by Category with plain st.markdown(), redesigned search card layout</t>
+  </si>
+  <si>
+    <t>Sprint 3D Fix: Resolved ghost input box appearing between page subtitle and search card — root cause identified as orphaned HTML div wrappers auto-closing before Streamlit widgets rendered; replaced with CSS :has() marker injection pattern</t>
+  </si>
+  <si>
+    <t>Sprint 3D: Implemented search logic — keyword filtering against article title, category, tags, and summary fields using session_state (hl_search_query); results grid with 3-column card layout, Clear Search button, no-results fallback message</t>
+  </si>
+  <si>
+    <t>Sprint 3D: Wired Browse by Category Select buttons to filter articles — hl_selected_category session state, 3-column filtered results grid, mutual exclusivity with search filter; tested all 8 categories</t>
+  </si>
+  <si>
+    <t>Sprint 3D: Verified Popular Topics section — 4 coloured banner cards (blue/green/purple/red), expandable full article content, Visit Source external links; confirmed all expanders and links functional</t>
+  </si>
+  <si>
+    <t>Sprint 3D: Implemented UX improvement — wrapped All Articles section in collapsed st.expander() to reduce cognitive overload from 18 article cards; applied teal CSS :has() styling to match platform section header design system</t>
+  </si>
+  <si>
+    <t>Sprint 3D: Standardized font weight across all teal section headers (700 weight, 16px, 0.01em letter-spacing); confirmed Official BC Health Resources section (HealthLinkBC, BCCDC, BC Health Services cards) rendering correctly</t>
+  </si>
+  <si>
+    <t>Sprint 3D: Final review and testing of complete Health Library — search, category filter, popular topics, all articles expander, BC health resources, footer disclaimer; committed all Sprint 3D work to GitHub</t>
+  </si>
+  <si>
+    <t>Sprint 4</t>
+  </si>
+  <si>
+    <t>Sprint 4A Research: Designed synthetic data model for System Analytics — defined 3 patient engagement tiers (Healthy/Occasional, Moderate Users, High-Frequency/Chronic) with realistic assessment frequency and urgency distributions; drafted data generation requirements</t>
+  </si>
+  <si>
+    <t>Sprint 4A: Developed generate_synthetic_data.py — 200 patients across 3 tiers, 5,000 assessment records with tier-weighted urgency distributions, flu season patterns (Nov–Feb spike), chronic symptom elevation for Tier 3; post-generation Emergency cap at ≤5%</t>
+  </si>
+  <si>
+    <t>Sprint 4A: Validated synthetic_assessments.csv output — confirmed 5,000 records, Emergency at exactly 5.0% (250 records), age distributions match tier specifications, top symptoms reflect chronic condition elevation for Tier 3 patients; committed to GitHub</t>
+  </si>
+  <si>
+    <t>Sprint 4B: Built System Analytics Dashboard page — page header with Export Report placeholder and date range filter dropdown (All Time default), CSV data loading with os.path relative resolution, @st.cache_data, 4 KPI cards with teal headers (Total Users, Active This Week, Total Assessments, Avg Assessment Time)</t>
+  </si>
+  <si>
+    <t>1 hr 45 min</t>
+  </si>
+  <si>
+    <t>Sprint 4B: Added 4 Plotly charts — horizontal bar chart (top 10 symptoms with clinical severity colour coding: red=Serious/Chronic, amber=Infectious, blue=General), Urgency Distribution donut, Usage by BC Health Authority donut (5 health authority regions mapped from cities), Assessment Trends line chart with numpy.polyfit orange trendline</t>
+  </si>
+  <si>
+    <t>Sprint 4B: Implemented K-Means unsupervised clustering — per-patient aggregation (age, assessment count, urgent ratio, chronic ratio), StandardScaler normalization, KMeans(n_clusters=3), automatic cluster naming by combined severity score; scatter plot visualization with bubble size = age; 3 cluster summary cards</t>
+  </si>
+  <si>
+    <t>Sprint 4B: Final verification and testing — date range filter wiring confirmed across all KPI cards and charts, K-Means cluster separation validated (Chronic/Elderly avg age 73, High-Risk avg age 47, Healthy/Occasional avg age 29); committed all Sprint 4A and 4B work to GitHub</t>
+  </si>
+  <si>
+    <t>3D</t>
+  </si>
+  <si>
+    <t>4A</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>Prepared Progress Report 4; updated commit history, work log entries, and timeline for PR4 reporting period (Mar 10–16); added screenshots and submitted to Blackboard</t>
   </si>
 </sst>
 </file>
@@ -1918,6 +1996,25 @@
     <xf numFmtId="0" fontId="4" fillId="25" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1950,25 +2047,6 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2155,6 +2233,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2442,7 +2524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2451,41 +2533,41 @@
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="34.21875" style="68" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="19" customWidth="1"/>
-    <col min="7" max="7" width="209.77734375" style="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="255.77734375" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="98"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="105"/>
     </row>
     <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="98"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="105"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="91" t="s">
+      <c r="A3" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="94"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="101"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F4" s="16"/>
@@ -5631,7 +5713,7 @@
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" s="105">
+      <c r="A143" s="89">
         <v>46084</v>
       </c>
       <c r="B143" s="23" t="s">
@@ -5640,7 +5722,7 @@
       <c r="C143" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D143" s="108">
+      <c r="D143" s="92">
         <v>1</v>
       </c>
       <c r="E143" s="24" t="s">
@@ -5652,7 +5734,7 @@
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" s="105">
+      <c r="A144" s="89">
         <v>46084</v>
       </c>
       <c r="B144" s="23" t="s">
@@ -5661,7 +5743,7 @@
       <c r="C144" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D144" s="108">
+      <c r="D144" s="92">
         <v>0.75</v>
       </c>
       <c r="E144" s="24" t="s">
@@ -5673,7 +5755,7 @@
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" s="105">
+      <c r="A145" s="89">
         <v>46085</v>
       </c>
       <c r="B145" s="23" t="s">
@@ -5682,7 +5764,7 @@
       <c r="C145" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D145" s="108">
+      <c r="D145" s="92">
         <v>1</v>
       </c>
       <c r="E145" s="24" t="s">
@@ -5694,7 +5776,7 @@
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146" s="105">
+      <c r="A146" s="89">
         <v>46085</v>
       </c>
       <c r="B146" s="23" t="s">
@@ -5703,7 +5785,7 @@
       <c r="C146" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D146" s="108">
+      <c r="D146" s="92">
         <v>0.75</v>
       </c>
       <c r="E146" s="24" t="s">
@@ -5715,7 +5797,7 @@
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="105">
+      <c r="A147" s="89">
         <v>46086</v>
       </c>
       <c r="B147" s="23" t="s">
@@ -5724,7 +5806,7 @@
       <c r="C147" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D147" s="108">
+      <c r="D147" s="92">
         <v>1</v>
       </c>
       <c r="E147" s="24" t="s">
@@ -5736,7 +5818,7 @@
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148" s="105">
+      <c r="A148" s="89">
         <v>46086</v>
       </c>
       <c r="B148" s="23" t="s">
@@ -5745,7 +5827,7 @@
       <c r="C148" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D148" s="108">
+      <c r="D148" s="92">
         <v>0.5</v>
       </c>
       <c r="E148" s="24" t="s">
@@ -5757,7 +5839,7 @@
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149" s="105">
+      <c r="A149" s="89">
         <v>46087</v>
       </c>
       <c r="B149" s="23" t="s">
@@ -5766,7 +5848,7 @@
       <c r="C149" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D149" s="108">
+      <c r="D149" s="92">
         <v>0.5</v>
       </c>
       <c r="E149" s="24" t="s">
@@ -5778,7 +5860,7 @@
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150" s="105">
+      <c r="A150" s="89">
         <v>46088</v>
       </c>
       <c r="B150" s="23" t="s">
@@ -5787,7 +5869,7 @@
       <c r="C150" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D150" s="108">
+      <c r="D150" s="92">
         <v>1</v>
       </c>
       <c r="E150" s="24" t="s">
@@ -5801,7 +5883,7 @@
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151" s="105">
+      <c r="A151" s="89">
         <v>46088</v>
       </c>
       <c r="B151" s="23" t="s">
@@ -5810,7 +5892,7 @@
       <c r="C151" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D151" s="108">
+      <c r="D151" s="92">
         <v>0.75</v>
       </c>
       <c r="E151" s="24" t="s">
@@ -5824,7 +5906,7 @@
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152" s="105">
+      <c r="A152" s="89">
         <v>46089</v>
       </c>
       <c r="B152" s="23" t="s">
@@ -5833,7 +5915,7 @@
       <c r="C152" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D152" s="108">
+      <c r="D152" s="92">
         <v>0.75</v>
       </c>
       <c r="E152" s="24" t="s">
@@ -5847,7 +5929,7 @@
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A153" s="105">
+      <c r="A153" s="89">
         <v>46089</v>
       </c>
       <c r="B153" s="23" t="s">
@@ -5856,7 +5938,7 @@
       <c r="C153" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D153" s="108">
+      <c r="D153" s="92">
         <v>0.5</v>
       </c>
       <c r="E153" s="24" t="s">
@@ -5870,7 +5952,7 @@
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A154" s="105">
+      <c r="A154" s="89">
         <v>46089</v>
       </c>
       <c r="B154" s="23" t="s">
@@ -5879,7 +5961,7 @@
       <c r="C154" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D154" s="108">
+      <c r="D154" s="92">
         <v>0.5</v>
       </c>
       <c r="E154" s="24" t="s">
@@ -5893,7 +5975,7 @@
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A155" s="105">
+      <c r="A155" s="89">
         <v>46089</v>
       </c>
       <c r="B155" s="23" t="s">
@@ -5902,7 +5984,7 @@
       <c r="C155" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D155" s="108">
+      <c r="D155" s="92">
         <v>1.5</v>
       </c>
       <c r="E155" s="24" t="s">
@@ -5916,7 +5998,7 @@
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A156" s="105">
+      <c r="A156" s="89">
         <v>46090</v>
       </c>
       <c r="B156" s="23" t="s">
@@ -5925,7 +6007,7 @@
       <c r="C156" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D156" s="108">
+      <c r="D156" s="92">
         <v>1.5</v>
       </c>
       <c r="E156" s="24" t="s">
@@ -5939,7 +6021,7 @@
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A157" s="105">
+      <c r="A157" s="89">
         <v>46090</v>
       </c>
       <c r="B157" s="23" t="s">
@@ -5948,7 +6030,7 @@
       <c r="C157" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D157" s="108">
+      <c r="D157" s="92">
         <v>1</v>
       </c>
       <c r="E157" s="24" t="s">
@@ -5962,7 +6044,7 @@
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A158" s="106">
+      <c r="A158" s="90">
         <v>46090</v>
       </c>
       <c r="B158" s="1" t="s">
@@ -5985,7 +6067,7 @@
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A159" s="106">
+      <c r="A159" s="90">
         <v>46090</v>
       </c>
       <c r="B159" s="1" t="s">
@@ -6008,7 +6090,7 @@
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A160" s="106">
+      <c r="A160" s="90">
         <v>46090</v>
       </c>
       <c r="B160" s="1" t="s">
@@ -6031,7 +6113,7 @@
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A161" s="106">
+      <c r="A161" s="90">
         <v>46090</v>
       </c>
       <c r="B161" s="1" t="s">
@@ -6054,7 +6136,7 @@
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A162" s="106">
+      <c r="A162" s="90">
         <v>46090</v>
       </c>
       <c r="B162" s="1" t="s">
@@ -6077,16 +6159,16 @@
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A163" s="107">
+      <c r="A163" s="91">
         <v>46090</v>
       </c>
-      <c r="B163" s="104" t="s">
+      <c r="B163" s="88" t="s">
         <v>383</v>
       </c>
-      <c r="C163" s="104" t="s">
+      <c r="C163" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="D163" s="110">
+      <c r="D163" s="94">
         <v>0.25</v>
       </c>
       <c r="E163" s="24" t="s">
@@ -6100,16 +6182,16 @@
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A164" s="107">
+      <c r="A164" s="91">
         <v>46090</v>
       </c>
-      <c r="B164" s="104" t="s">
+      <c r="B164" s="88" t="s">
         <v>383</v>
       </c>
-      <c r="C164" s="104" t="s">
+      <c r="C164" s="88" t="s">
         <v>128</v>
       </c>
-      <c r="D164" s="110">
+      <c r="D164" s="94">
         <v>0.75</v>
       </c>
       <c r="E164" s="24" t="s">
@@ -6121,27 +6203,485 @@
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A165" s="88" t="s">
+      <c r="A165" s="91">
+        <v>46092</v>
+      </c>
+      <c r="B165" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C165" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="D165" s="94">
+        <v>1</v>
+      </c>
+      <c r="E165" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F165" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G165" s="20" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" s="91">
+        <v>46092</v>
+      </c>
+      <c r="B166" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C166" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D166" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E166" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F166" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G166" s="20" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="91">
+        <v>46092</v>
+      </c>
+      <c r="B167" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C167" s="88" t="s">
+        <v>442</v>
+      </c>
+      <c r="D167" s="94">
+        <v>1.25</v>
+      </c>
+      <c r="E167" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F167" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G167" s="20" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="91">
+        <v>46092</v>
+      </c>
+      <c r="B168" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C168" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="D168" s="94">
+        <v>1</v>
+      </c>
+      <c r="E168" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F168" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G168" s="20" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" s="91">
+        <v>46094</v>
+      </c>
+      <c r="B169" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C169" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D169" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E169" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F169" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G169" s="20" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="91">
+        <v>46094</v>
+      </c>
+      <c r="B170" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C170" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="D170" s="94">
+        <v>1</v>
+      </c>
+      <c r="E170" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F170" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G170" s="20" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" s="91">
+        <v>46094</v>
+      </c>
+      <c r="B171" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C171" s="88" t="s">
+        <v>442</v>
+      </c>
+      <c r="D171" s="94">
+        <v>1.25</v>
+      </c>
+      <c r="E171" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F171" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G171" s="20" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="91">
+        <v>46094</v>
+      </c>
+      <c r="B172" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C172" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D172" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E172" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F172" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G172" s="20" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="91">
+        <v>46096</v>
+      </c>
+      <c r="B173" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C173" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D173" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E173" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F173" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G173" s="20" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" s="91">
+        <v>46096</v>
+      </c>
+      <c r="B174" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C174" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="D174" s="94">
+        <v>0.5</v>
+      </c>
+      <c r="E174" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F174" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G174" s="20" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" s="91">
+        <v>46096</v>
+      </c>
+      <c r="B175" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C175" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D175" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E175" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F175" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G175" s="20" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" s="91">
+        <v>46096</v>
+      </c>
+      <c r="B176" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C176" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="D176" s="94">
+        <v>0.5</v>
+      </c>
+      <c r="E176" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F176" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="G176" s="20" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="91">
+        <v>46097</v>
+      </c>
+      <c r="B177" s="88" t="s">
+        <v>453</v>
+      </c>
+      <c r="C177" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="D177" s="94">
+        <v>1</v>
+      </c>
+      <c r="E177" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="F177" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="G177" s="20" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="91">
+        <v>46097</v>
+      </c>
+      <c r="B178" s="88" t="s">
+        <v>453</v>
+      </c>
+      <c r="C178" s="88" t="s">
+        <v>442</v>
+      </c>
+      <c r="D178" s="94">
+        <v>1.25</v>
+      </c>
+      <c r="E178" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="F178" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="G178" s="20" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="91">
+        <v>46097</v>
+      </c>
+      <c r="B179" s="88" t="s">
+        <v>453</v>
+      </c>
+      <c r="C179" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="D179" s="94">
+        <v>0.5</v>
+      </c>
+      <c r="E179" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="F179" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="G179" s="20" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="91">
+        <v>46097</v>
+      </c>
+      <c r="B180" s="88" t="s">
+        <v>453</v>
+      </c>
+      <c r="C180" s="88" t="s">
+        <v>427</v>
+      </c>
+      <c r="D180" s="94">
+        <v>1.5</v>
+      </c>
+      <c r="E180" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="F180" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="G180" s="20" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" s="91">
+        <v>46097</v>
+      </c>
+      <c r="B181" s="88" t="s">
+        <v>453</v>
+      </c>
+      <c r="C181" s="88" t="s">
+        <v>458</v>
+      </c>
+      <c r="D181" s="94">
+        <v>1.75</v>
+      </c>
+      <c r="E181" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="F181" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="G181" s="20" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" s="91">
+        <v>46097</v>
+      </c>
+      <c r="B182" s="88" t="s">
+        <v>453</v>
+      </c>
+      <c r="C182" s="88" t="s">
+        <v>427</v>
+      </c>
+      <c r="D182" s="94">
+        <v>1.5</v>
+      </c>
+      <c r="E182" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="F182" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="G182" s="20" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" s="91">
+        <v>46097</v>
+      </c>
+      <c r="B183" s="88" t="s">
+        <v>453</v>
+      </c>
+      <c r="C183" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="D183" s="94">
+        <v>0.5</v>
+      </c>
+      <c r="E183" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="F183" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="G183" s="20" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" s="91">
+        <v>46097</v>
+      </c>
+      <c r="B184" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="C184" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D184" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E184" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F184" s="17"/>
+      <c r="G184" s="20" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" s="95" t="s">
         <v>137</v>
       </c>
-      <c r="B165" s="89"/>
-      <c r="C165" s="89"/>
-      <c r="D165" s="90"/>
-      <c r="E165" s="73">
-        <f>SUM(D6:D164)</f>
-        <v>119.85</v>
-      </c>
-      <c r="F165" s="18"/>
-      <c r="G165" s="21"/>
+      <c r="B185" s="96"/>
+      <c r="C185" s="96"/>
+      <c r="D185" s="97"/>
+      <c r="E185" s="73">
+        <f>SUM(D6:D184)</f>
+        <v>138.85</v>
+      </c>
+      <c r="F185" s="18"/>
+      <c r="G185" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A165:D165"/>
+    <mergeCell ref="A185:D185"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E217">
+  <conditionalFormatting sqref="E6:E237">
     <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"0: Environment Setup"</formula>
     </cfRule>
@@ -6214,7 +6754,7 @@
           <x14:formula1>
             <xm:f>Categories!$A$4:$A$25</xm:f>
           </x14:formula1>
-          <xm:sqref>E6:E217</xm:sqref>
+          <xm:sqref>E6:E237</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6232,31 +6772,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="110" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
     </row>
     <row r="3" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="107" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
@@ -6344,7 +6884,7 @@
       </c>
       <c r="D8" s="37">
         <f>SUM(B56:B60)</f>
-        <v>26.5</v>
+        <v>36.75</v>
       </c>
       <c r="E8" s="38">
         <f t="shared" si="0"/>
@@ -6363,11 +6903,11 @@
       </c>
       <c r="D9" s="37">
         <f>SUM(B61:B62)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E9" s="38">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -6401,11 +6941,11 @@
       </c>
       <c r="D11" s="37">
         <f>SUM(B65)</f>
-        <v>14</v>
+        <v>14.75</v>
       </c>
       <c r="E11" s="38">
         <f t="shared" si="0"/>
-        <v>0.77777777777777779</v>
+        <v>0.81944444444444442</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -6419,30 +6959,30 @@
       </c>
       <c r="D12" s="54">
         <f>SUM(D5:D11)</f>
-        <v>96.6</v>
+        <v>115.6</v>
       </c>
       <c r="E12" s="55">
         <f>IF(C12=0,0,D12/C12)</f>
-        <v>0.81864406779661014</v>
+        <v>0.97966101694915253</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="101" t="s">
+      <c r="A14" s="108" t="s">
         <v>152</v>
       </c>
-      <c r="B14" s="102"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="102"/>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="102"/>
-      <c r="H14" s="102"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="102"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="102"/>
-      <c r="M14" s="102"/>
-      <c r="N14" s="102"/>
+      <c r="B14" s="109"/>
+      <c r="C14" s="109"/>
+      <c r="D14" s="109"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="109"/>
+      <c r="I14" s="109"/>
+      <c r="J14" s="109"/>
+      <c r="K14" s="109"/>
+      <c r="L14" s="109"/>
+      <c r="M14" s="109"/>
+      <c r="N14" s="109"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
@@ -7148,7 +7688,7 @@
       </c>
       <c r="B59" s="37">
         <f>SUMIF('Work Log'!E:E,"3D: Health Education Library",'Work Log'!D:D)</f>
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="C59" s="3"/>
     </row>
@@ -7168,7 +7708,7 @@
       </c>
       <c r="B61" s="37">
         <f>SUMIF('Work Log'!E:E,"4A: System Analytics Data",'Work Log'!D:D)</f>
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="C61" s="3"/>
     </row>
@@ -7178,7 +7718,7 @@
       </c>
       <c r="B62" s="37">
         <f>SUMIF('Work Log'!E:E,"4B: System Analytics Dashboard",'Work Log'!D:D)</f>
-        <v>0</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -7205,7 +7745,7 @@
       </c>
       <c r="B65" s="37">
         <f>SUMIF('Work Log'!E:E,"6: Documentation + Submission",'Work Log'!D:D)</f>
-        <v>14</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -7230,9 +7770,9 @@
       <c r="A68" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="B68" s="109">
+      <c r="B68" s="93">
         <f>SUM(B46:B67)</f>
-        <v>119.85000000000001</v>
+        <v>138.85000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/DocumentsAndReports/worklog/WorkLog_DesmondChua_W26_4495_S2.xlsx
+++ b/DocumentsAndReports/worklog/WorkLog_DesmondChua_W26_4495_S2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4f25ae689476683/Desmond_New/BC-Health-Platform/DocumentsAndReports/worklog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="8_{08655895-4010-492B-B73A-F5D36A9F8AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBECE850-859A-40A1-B437-F926111F1D88}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="8_{08655895-4010-492B-B73A-F5D36A9F8AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8130E292-2780-4531-992B-4C84406774B9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="502">
   <si>
     <t>CSIS 4495 - Applied Research Project</t>
   </si>
@@ -1433,6 +1433,114 @@
   </si>
   <si>
     <t>Prepared Progress Report 4; updated commit history, work log entries, and timeline for PR4 reporting period (Mar 10–16); added screenshots and submitted to Blackboard</t>
+  </si>
+  <si>
+    <t>Sprint 5</t>
+  </si>
+  <si>
+    <t>5A: Automated Testing Suite</t>
+  </si>
+  <si>
+    <t>5A.1</t>
+  </si>
+  <si>
+    <t>Sprint 5A scope planning: Decided to drop Community Pulse (web scraping) feature and focus on automated testing suite. Drafted scope decision rationale and sent email to Prof. Priya explaining the scope change and requesting absence from class for job interview</t>
+  </si>
+  <si>
+    <t>Sprint 5A.1: Designed tests/ folder architecture — unit/, integration/, ui/, property/ sub-packages. Created all init.py files, conftest.py with test_db (in-memory SQLite fixture with yield teardown) and test_user fixtures, TEST_REGISTER.md with table header</t>
+  </si>
+  <si>
+    <t>Sprint 5A.1 cleanup: Identified and removed old ad-hoc test scripts (test_openai.py, test_predict.py, test_rules.py) from Implementation/tests/ — superseded by new proper pytest suite at root tests/ folder</t>
+  </si>
+  <si>
+    <t>5A.2</t>
+  </si>
+  <si>
+    <t>Sprint 5A.2: Read auth.py source code to understand exact function signatures (hash_password, verify_password, validate_password_strength, validate_email, require_authentication). Designed 10 test cases across 4 logical groups: Registration, Login, Security, Session</t>
+  </si>
+  <si>
+    <t>Sprint 5A.2: Wrote test_auth.py — 10 unit tests for authentication module. Used conftest.py test_db fixture for all database operations, unittest.mock for Streamlit session_state and st.switch_page. Verified all 10 tests pass: 10/10 passed in 4.38s</t>
+  </si>
+  <si>
+    <t>5A.3</t>
+  </si>
+  <si>
+    <t>Sprint 5A.3 analysis: Read rules.py to confirm check_critical_symptoms() signature, return dict structure, 14-rule count, match types (any vs all), case-insensitive matching behaviour before writing tests</t>
+  </si>
+  <si>
+    <t>Sprint 5A.3: Wrote test_ctas_rules.py — 23 unit tests across 3 groups: 14 parametrized positive detection tests (one per CTAS rule), 5 negative pass-through tests, 4 edge case tests (mixed case, None input, large lists, single keyword). All 23 passing</t>
+  </si>
+  <si>
+    <t>5A.4</t>
+  </si>
+  <si>
+    <t>Sprint 5A.4 analysis: Read database.py (690 lines) — confirmed all CRUD function signatures, return types, table schema, and connection pattern (get_connection() called internally — requires unittest.mock.patch to redirect to test DB)</t>
+  </si>
+  <si>
+    <t>Sprint 5A.4: Wrote test_database.py — 12 unit tests across 3 groups: 5 User CRUD tests, 5 Assessment CRUD tests, 2 Data Integrity tests. Patched get_connection() with test DB factory. Verified user isolation (TC-DB-11) and correct FK constraint handling. All 12 passing</t>
+  </si>
+  <si>
+    <t>5A.5</t>
+  </si>
+  <si>
+    <t>Sprint 5A.5 analysis: Confirmed ML layer lives in chatbot.py (not ml_model.py). Read model.pkl and model_metadata.json directly — identified feature vector building logic, 70% confidence threshold location, predict_proba() call pattern</t>
+  </si>
+  <si>
+    <t>Sprint 5A.5: Wrote test_ml_model.py — 12 unit tests across 4 groups: model loading (2), confidence threshold (3), input handling (4), output validation (3). Loaded real model.pkl directly without Streamlit. UTI symptoms achieved 100% confidence. All 12 passing</t>
+  </si>
+  <si>
+    <t>5A.6</t>
+  </si>
+  <si>
+    <t>Sprint 5A.6 analysis: Read chatbot.py — confirmed run_assessment() layer sequence (OpenAI → CTAS → ML), all 4 return statuses and their dict keys, patch target (components.chatbot.extract_symptoms — patch where used not where defined)</t>
+  </si>
+  <si>
+    <t>Sprint 5A.6: Wrote test_pipeline.py — 6 integration tests. Mocked both extract_symptoms() and get_openai_fallback_guidance(). Tested emergency circuit breaker, ML prediction path, OpenAI fallback path, safety invariants. All 6 passing in 3.74s</t>
+  </si>
+  <si>
+    <t>5A.7</t>
+  </si>
+  <si>
+    <t>Sprint 5A.7 analysis: Confirmed extract_symptoms() return dict key is 'symptoms' (not 'extracted_symptoms'). Confirmed all mock return structures for 6 clinical scenarios before writing tests</t>
+  </si>
+  <si>
+    <t>Sprint 5A.7: Wrote test_chatbot_scenarios.py — 6 integration tests covering cardiac emergency, stroke emergency, UTI ML prediction, vague symptom fallback, emergency override safety, minimal input edge case. All 6 passing on first run</t>
+  </si>
+  <si>
+    <t>5A.8</t>
+  </si>
+  <si>
+    <t>Sprint 5A.8 analysis: Read 3_My_Dashboard.py — confirmed session_state keys, data source (get_user_assessments via components.database), 4 stat cards as custom HTML st.markdown (not st.metric), 2 selectboxes, CWD dependency for assets/logo.png</t>
+  </si>
+  <si>
+    <t>Sprint 5A.8: Wrote test_dashboard_apptest.py — 8 headless UI tests using Streamlit AppTest. Implemented _run_dashboard() helper with os.chdir(SRC_DIR) pattern. Verified stat card headers, selectbox options (All Time, Last 3 Months, All Urgency Levels), user data isolation. All 8 passing</t>
+  </si>
+  <si>
+    <t>5A.9</t>
+  </si>
+  <si>
+    <t>Sprint 5A.9 analysis: Read 2_Symptom_Assessment.py — confirmed session_state keys, process_multiturn_message() as primary function to mock (not run_assessment()), AppTest chat input syntax (at.chat_input[0].set_value().run()), _submit_chat() helper pattern needed</t>
+  </si>
+  <si>
+    <t>Sprint 5A.9: Wrote test_chatbot_apptest.py — 8 headless UI tests. Implemented _run_chatbot() and _submit_chat() helpers with patch re-application on rerun. Tested warning banner, welcome message personalisation, ML response, emergency response, auth guard. All 8 passing</t>
+  </si>
+  <si>
+    <t>5A.10</t>
+  </si>
+  <si>
+    <t>Sprint 5A.10 analysis: Confirmed Hypothesis installed (6.151.9). Read auth.py and rules.py to verify exact validation rules — password requires letter + digit (not uppercase + lowercase separately). Corrected strategy before writing</t>
+  </si>
+  <si>
+    <t>Sprint 5A.10: Wrote test_fuzz_hypothesis.py — 10 property-based tests using Hypothesis. 1,000 total fuzz inputs (100 per test). Covered password fuzzing (3 tests), email fuzzing (3 tests), CTAS rules fuzzing (3 tests), database fuzzing (1 test). All 10 passing</t>
+  </si>
+  <si>
+    <t>5A.11</t>
+  </si>
+  <si>
+    <t>Sprint 5A.11: Ran full test suite from project root — 79 tests across unit, integration, property folders all passing in 20.89s. UI tests confirmed passing individually (16 tests). Took screenshots for progress report documentation</t>
+  </si>
+  <si>
+    <t>Git commits: All Sprint 5A tasks committed with granular messages (5A.1 through 5A.11) and pushed to GitHub main branch</t>
   </si>
 </sst>
 </file>
@@ -1574,7 +1682,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1703,6 +1811,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E4CF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -1809,7 +1923,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2048,6 +2162,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2524,7 +2641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -6644,7 +6761,7 @@
         <v>46097</v>
       </c>
       <c r="B184" s="88" t="s">
-        <v>383</v>
+        <v>453</v>
       </c>
       <c r="C184" s="88" t="s">
         <v>128</v>
@@ -6661,27 +6778,556 @@
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A185" s="95" t="s">
+      <c r="A185" s="91">
+        <v>46098</v>
+      </c>
+      <c r="B185" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C185" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="D185" s="94">
+        <v>1</v>
+      </c>
+      <c r="E185" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F185" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="G185" s="20" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" s="91">
+        <v>46098</v>
+      </c>
+      <c r="B186" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C186" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D186" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E186" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F186" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="G186" s="20" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" s="91">
+        <v>46098</v>
+      </c>
+      <c r="B187" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C187" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="D187" s="94">
+        <v>0.5</v>
+      </c>
+      <c r="E187" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F187" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="G187" s="20" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" s="91">
+        <v>46100</v>
+      </c>
+      <c r="B188" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C188" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="D188" s="94">
+        <v>1</v>
+      </c>
+      <c r="E188" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F188" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="G188" s="20" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" s="91">
+        <v>46100</v>
+      </c>
+      <c r="B189" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C189" s="88" t="s">
+        <v>442</v>
+      </c>
+      <c r="D189" s="94">
+        <v>1.25</v>
+      </c>
+      <c r="E189" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F189" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="G189" s="20" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" s="91">
+        <v>46100</v>
+      </c>
+      <c r="B190" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C190" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="D190" s="94">
+        <v>0.5</v>
+      </c>
+      <c r="E190" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F190" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="G190" s="20" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191" s="91">
+        <v>46102</v>
+      </c>
+      <c r="B191" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C191" s="88" t="s">
+        <v>427</v>
+      </c>
+      <c r="D191" s="94">
+        <v>1.5</v>
+      </c>
+      <c r="E191" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F191" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="G191" s="20" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192" s="91">
+        <v>46102</v>
+      </c>
+      <c r="B192" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C192" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D192" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E192" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F192" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="G192" s="20" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A193" s="91">
+        <v>46102</v>
+      </c>
+      <c r="B193" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C193" s="88" t="s">
+        <v>442</v>
+      </c>
+      <c r="D193" s="94">
+        <v>1.25</v>
+      </c>
+      <c r="E193" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F193" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="G193" s="20" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A194" s="91">
+        <v>46102</v>
+      </c>
+      <c r="B194" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C194" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D194" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E194" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F194" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="G194" s="20" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A195" s="91">
+        <v>46102</v>
+      </c>
+      <c r="B195" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C195" s="88" t="s">
+        <v>442</v>
+      </c>
+      <c r="D195" s="94">
+        <v>1.25</v>
+      </c>
+      <c r="E195" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F195" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="G195" s="20" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A196" s="91">
+        <v>46103</v>
+      </c>
+      <c r="B196" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C196" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D196" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E196" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F196" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="G196" s="20" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A197" s="91">
+        <v>46103</v>
+      </c>
+      <c r="B197" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C197" s="88" t="s">
+        <v>442</v>
+      </c>
+      <c r="D197" s="94">
+        <v>1.25</v>
+      </c>
+      <c r="E197" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F197" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="G197" s="20" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A198" s="91">
+        <v>46104</v>
+      </c>
+      <c r="B198" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C198" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D198" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E198" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F198" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="G198" s="20" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A199" s="91">
+        <v>46104</v>
+      </c>
+      <c r="B199" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C199" s="88" t="s">
+        <v>442</v>
+      </c>
+      <c r="D199" s="94">
+        <v>1.25</v>
+      </c>
+      <c r="E199" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F199" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="G199" s="20" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A200" s="91">
+        <v>46104</v>
+      </c>
+      <c r="B200" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C200" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D200" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E200" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F200" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="G200" s="20" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A201" s="91">
+        <v>46104</v>
+      </c>
+      <c r="B201" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C201" s="88" t="s">
+        <v>427</v>
+      </c>
+      <c r="D201" s="94">
+        <v>1.5</v>
+      </c>
+      <c r="E201" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F201" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="G201" s="20" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A202" s="91">
+        <v>46104</v>
+      </c>
+      <c r="B202" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C202" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D202" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E202" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F202" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="G202" s="20" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A203" s="91">
+        <v>46104</v>
+      </c>
+      <c r="B203" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C203" s="88" t="s">
+        <v>427</v>
+      </c>
+      <c r="D203" s="94">
+        <v>1.5</v>
+      </c>
+      <c r="E203" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F203" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="G203" s="20" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A204" s="91">
+        <v>46104</v>
+      </c>
+      <c r="B204" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C204" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="D204" s="94">
+        <v>0.75</v>
+      </c>
+      <c r="E204" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F204" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="G204" s="20" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A205" s="91">
+        <v>46104</v>
+      </c>
+      <c r="B205" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C205" s="88" t="s">
+        <v>442</v>
+      </c>
+      <c r="D205" s="94">
+        <v>1.25</v>
+      </c>
+      <c r="E205" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F205" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="G205" s="20" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A206" s="91">
+        <v>46104</v>
+      </c>
+      <c r="B206" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C206" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="D206" s="94">
+        <v>0.5</v>
+      </c>
+      <c r="E206" s="111" t="s">
+        <v>467</v>
+      </c>
+      <c r="F206" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="G206" s="20" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A207" s="91">
+        <v>46104</v>
+      </c>
+      <c r="B207" s="88" t="s">
+        <v>466</v>
+      </c>
+      <c r="C207" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="D207" s="94">
+        <v>0.25</v>
+      </c>
+      <c r="E207" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="F207" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="G207" s="20" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A208" s="95" t="s">
         <v>137</v>
       </c>
-      <c r="B185" s="96"/>
-      <c r="C185" s="96"/>
-      <c r="D185" s="97"/>
-      <c r="E185" s="73">
-        <f>SUM(D6:D184)</f>
-        <v>138.85</v>
-      </c>
-      <c r="F185" s="18"/>
-      <c r="G185" s="21"/>
+      <c r="B208" s="96"/>
+      <c r="C208" s="96"/>
+      <c r="D208" s="97"/>
+      <c r="E208" s="73">
+        <f>SUM(D6:D207)</f>
+        <v>160.6</v>
+      </c>
+      <c r="F208" s="18"/>
+      <c r="G208" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A185:D185"/>
+    <mergeCell ref="A208:D208"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E237">
+  <conditionalFormatting sqref="E6:E260">
     <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"0: Environment Setup"</formula>
     </cfRule>
@@ -6754,7 +7400,7 @@
           <x14:formula1>
             <xm:f>Categories!$A$4:$A$25</xm:f>
           </x14:formula1>
-          <xm:sqref>E6:E237</xm:sqref>
+          <xm:sqref>E6:E260</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6941,11 +7587,11 @@
       </c>
       <c r="D11" s="37">
         <f>SUM(B65)</f>
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="E11" s="38">
         <f t="shared" si="0"/>
-        <v>0.81944444444444442</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -6959,11 +7605,11 @@
       </c>
       <c r="D12" s="54">
         <f>SUM(D5:D11)</f>
-        <v>115.6</v>
+        <v>115.85</v>
       </c>
       <c r="E12" s="55">
         <f>IF(C12=0,0,D12/C12)</f>
-        <v>0.97966101694915253</v>
+        <v>0.98177966101694913</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -7745,7 +8391,7 @@
       </c>
       <c r="B65" s="37">
         <f>SUMIF('Work Log'!E:E,"6: Documentation + Submission",'Work Log'!D:D)</f>
-        <v>14.75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -7772,7 +8418,7 @@
       </c>
       <c r="B68" s="93">
         <f>SUM(B46:B67)</f>
-        <v>138.85000000000002</v>
+        <v>139.10000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/DocumentsAndReports/worklog/WorkLog_DesmondChua_W26_4495_S2.xlsx
+++ b/DocumentsAndReports/worklog/WorkLog_DesmondChua_W26_4495_S2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4f25ae689476683/Desmond_New/BC-Health-Platform/DocumentsAndReports/worklog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="189" documentId="8_{08655895-4010-492B-B73A-F5D36A9F8AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8130E292-2780-4531-992B-4C84406774B9}"/>
+  <xr:revisionPtr revIDLastSave="1074" documentId="8_{08655895-4010-492B-B73A-F5D36A9F8AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3E214E2-00D8-4A74-9FEB-F97952A5FCDE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work Log" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="548">
   <si>
     <t>CSIS 4495 - Applied Research Project</t>
   </si>
@@ -1541,6 +1541,144 @@
   </si>
   <si>
     <t>Git commits: All Sprint 5A tasks committed with granular messages (5A.1 through 5A.11) and pushed to GitHub main branch</t>
+  </si>
+  <si>
+    <t>5B: CI/CD Pipeline</t>
+  </si>
+  <si>
+    <t>5B.1</t>
+  </si>
+  <si>
+    <t>Sprint 5B: Created .github/workflows/ci.yml — GitHub Actions CI/CD pipeline to run 79-test suite on every push to main. Fixed PAT workflow scope permission error</t>
+  </si>
+  <si>
+    <t>5B.2</t>
+  </si>
+  <si>
+    <t>Sprint 5B: Debugged CI failures — requirements.txt path fix, pytest command not found (python -m pytest), streamlit.testing module conflict. Excluded UI AppTests from CI with --ignore=../../tests/ui</t>
+  </si>
+  <si>
+    <t>5B.3</t>
+  </si>
+  <si>
+    <t>Sprint 5B: Committed model.pkl to repo (removed from .gitignore) to resolve CI model file not found errors. Final CI run: 79/79 tests passed in 13.72s</t>
+  </si>
+  <si>
+    <t>5C: Deploy + UI Polish</t>
+  </si>
+  <si>
+    <t>5C.1</t>
+  </si>
+  <si>
+    <t>UI redesign: Implemented white topbar with CedarCare two-tone wordmark and cedar tree logo. Standardised page headers across all 6 pages with custom SVG icons per page</t>
+  </si>
+  <si>
+    <t>5C.2</t>
+  </si>
+  <si>
+    <t>UI redesign: Renamed BC Health Platform to CedarCare everywhere in code, page titles, sidebar, header component. Updated CSS for dark teal sidebar (#006271)</t>
+  </si>
+  <si>
+    <t>5C.3</t>
+  </si>
+  <si>
+    <t>UI redesign: Dashboard KPI fix — replaced Total checks since registration and Registrations this month with Most Recent Urgency Level and Days Since Last Assessment. Added consistent footer across all 6 pages</t>
+  </si>
+  <si>
+    <t>5C.4</t>
+  </si>
+  <si>
+    <t>UI redesign: Home page clean welcome header with SVG quick action icons for Check Symptoms, Find Facility, Health Library. Facility Finder emergency contacts redesigned as styled cards</t>
+  </si>
+  <si>
+    <t>5C.5</t>
+  </si>
+  <si>
+    <t>UI redesign: System Analytics trendline graceful fallback for missing data. Login button updated to teal filled to match CedarCare brand palette</t>
+  </si>
+  <si>
+    <t>5C.6</t>
+  </si>
+  <si>
+    <t>Sprint 5C prep: Created seed_db.py — auto-seeds test@test.com / Password123 on fresh deployment so Streamlit Cloud starts with a usable test account</t>
+  </si>
+  <si>
+    <t>5C.7</t>
+  </si>
+  <si>
+    <t>Sprint 5C: Deployed CedarCare to Streamlit Cloud at cedarcare.streamlit.app. Configured repo, branch (main), entry point (Implementation/src/app.py), Python 3.11, OPENAI_API_KEY secret</t>
+  </si>
+  <si>
+    <t>5C.8</t>
+  </si>
+  <si>
+    <t>Bug fix: Chips appearing on non-medical redirect. Implemented _show_chips session state flag — chips only shown when bot has genuinely collected symptoms. Added two-tier redirect logic: gentle redirect turn 1, hard end turn 2+</t>
+  </si>
+  <si>
+    <t>5C.9</t>
+  </si>
+  <si>
+    <t>Bug fix: Turn count reset on first symptom extraction — users who open with vague input get full 3-turn chip flow once real symptoms identified. Fixed chip handler to set _show_chips=True on follow_up with collected_symptoms</t>
+  </si>
+  <si>
+    <t>5C.10</t>
+  </si>
+  <si>
+    <t>Bug fix: Chip result rendering fix — result card not showing after final chip selection. Added _show_chips=False in chip handler for final assessment statuses. Removed redundant st.caption(hint) above chips</t>
+  </si>
+  <si>
+    <t>5C.11</t>
+  </si>
+  <si>
+    <t>Landing page: Built cedarcare_landing_v3_vch.html — custom HTML/CSS landing page via st.components.v1.html(). Hero section, chatbot mockup demo, statistics bar, trust indicators (CTAS-aligned triage, HealthLink BC, GPT-4o-mini powered)</t>
+  </si>
+  <si>
+    <t>5C.12</t>
+  </si>
+  <si>
+    <t>User testing: Set up CedarCare User Evaluation Survey on Google Forms (6 questions, Likert scales + open-ended). Distributed to 12 testers. Collected and captured all response charts for final report</t>
+  </si>
+  <si>
+    <t>5C.13</t>
+  </si>
+  <si>
+    <t>End-to-end smoke test of live deployment — verified all 6 pages load, chatbot pipeline works, emergency detection fires, seed data present, and user testing form accessible</t>
+  </si>
+  <si>
+    <t>Sprint 6</t>
+  </si>
+  <si>
+    <t>Sprint 6: Final Report — Wrote Sections 1-4 (Introduction, Project Summary, Changes to Proposal, Project Completion Timeline). Generated Gantt chart PNG using matplotlib and Playwright</t>
+  </si>
+  <si>
+    <t>Sprint 6: Final Report — Wrote Section 5 (Technical Implementation): Three-Layer Pipeline, CTAS rules, ML architecture, database design, dual ML architecture, OpenAI integration with system prompt engineering</t>
+  </si>
+  <si>
+    <t>Sprint 6: Generated architecture diagram and tech stack diagram using Google Gemini image generation with detailed prompts. Generated algorithm benchmarking bar chart (RF vs SVM vs KNN) using matplotlib</t>
+  </si>
+  <si>
+    <t>Sprint 6: Generated dark-theme Monokai code snippet PNGs for rules.py, chatbot.py (_ml_predict), database.py, auth.py, openai_utils.py, and 6___System_Analytics.py (K-Means pipeline) using Pygments ImageFormatter</t>
+  </si>
+  <si>
+    <t>Sprint 6: Final Report — Wrote Sections 6-11 (Implemented Features 1-6): Secure Authentication, Symptom Assessment Chatbot, Personal Health Dashboard, BC Facility Finder, Health Education Library, System Analytics Dashboard</t>
+  </si>
+  <si>
+    <t>Sprint 6: Captured all platform screenshots for report across all 6 features. Named and inserted all figures with captions. Documented chatbot flows including emergency, ML prediction, OpenAI fallback, and multi-turn chip flow</t>
+  </si>
+  <si>
+    <t>Sprint 6: Final Report — Wrote Section 12 (Evaluation Techniques): pytest suite table (95 tests, 9 files), CI/CD pipeline section, user evaluation survey results (12 responses, Q1-Q5 analysis), implementation changes in response to feedback</t>
+  </si>
+  <si>
+    <t>Sprint 6: Final Report — Wrote remaining sections: Competitive Analysis, Perceptual Map, Limitations and Constraints, Future Work, Conclusion, References, Appendix A (Installation Guide) and Appendix B (User Guide with screenshots)</t>
+  </si>
+  <si>
+    <t>Sprint 6: Updated work log Excel with all Sprint 5B, 5C, and Sprint 6 entries (Apr 2-6). Compiled all potential demo Q&amp;A pairs for presentation preparation (13 questions with model answers)</t>
+  </si>
+  <si>
+    <t>Sprint 6: Final GitHub check-in — pushed final report PDF, presentation slides, updated README with installation instructions, and user guide PDF to ReportsAndDocuments folder on main branch</t>
+  </si>
+  <si>
+    <t>Sprint 6: Submitted final report PDF on Blackboard. Confirmed all checklist items complete: GitHub check-in, slides, user guide, README, Blackboard submission</t>
   </si>
 </sst>
 </file>
@@ -1682,7 +1820,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1817,8 +1955,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1919,11 +2063,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1956,14 +2162,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2077,9 +2279,6 @@
     <xf numFmtId="0" fontId="4" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2129,14 +2328,8 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2163,8 +2356,61 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2639,2708 +2885,2730 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{212A1D3F-E799-4313-91D0-DBAA38962652}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;a0cf2915-0d4f-4d29-aae8-96935cfab218&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="34.21875" style="68" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="19" customWidth="1"/>
-    <col min="7" max="7" width="255.77734375" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.21875" style="66" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="18" customWidth="1"/>
+    <col min="7" max="7" width="255.77734375" style="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="105"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="100"/>
     </row>
     <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="105"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="100"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="101"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="96"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="25" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="21">
         <v>0</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="26">
         <v>2</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="30" t="s">
+      <c r="F6" s="27"/>
+      <c r="G6" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="21">
         <v>0</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="26">
         <v>1.5</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="30" t="s">
+      <c r="F7" s="27"/>
+      <c r="G7" s="28" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="21">
         <v>0</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="26">
         <v>2</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="30" t="s">
+      <c r="F8" s="27"/>
+      <c r="G8" s="28" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="21">
         <v>0</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="26">
         <v>1</v>
       </c>
-      <c r="E9" s="69" t="s">
+      <c r="E9" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="30" t="s">
+      <c r="F9" s="27"/>
+      <c r="G9" s="28" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="21">
         <v>0</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="26">
         <v>2.5</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="30" t="s">
+      <c r="F10" s="27"/>
+      <c r="G10" s="28" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="21">
         <v>0</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="26">
         <v>2</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="E11" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="29"/>
-      <c r="G11" s="30" t="s">
+      <c r="F11" s="27"/>
+      <c r="G11" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="21">
         <v>0</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="26">
         <v>3</v>
       </c>
-      <c r="E12" s="70" t="s">
+      <c r="E12" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="30" t="s">
+      <c r="F12" s="27"/>
+      <c r="G12" s="28" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="21">
         <v>0</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="26">
         <v>2.5</v>
       </c>
-      <c r="E13" s="69" t="s">
+      <c r="E13" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="29"/>
-      <c r="G13" s="30" t="s">
+      <c r="F13" s="27"/>
+      <c r="G13" s="28" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="21">
         <v>0</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="26">
         <v>3</v>
       </c>
-      <c r="E14" s="70" t="s">
+      <c r="E14" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="30" t="s">
+      <c r="F14" s="27"/>
+      <c r="G14" s="28" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="21">
         <v>0</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="26">
         <v>2.5</v>
       </c>
-      <c r="E15" s="70" t="s">
+      <c r="E15" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="29"/>
-      <c r="G15" s="30" t="s">
+      <c r="F15" s="27"/>
+      <c r="G15" s="28" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="21">
         <v>0</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="26">
         <v>3</v>
       </c>
-      <c r="E16" s="71" t="s">
+      <c r="E16" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="29"/>
-      <c r="G16" s="30" t="s">
+      <c r="F16" s="27"/>
+      <c r="G16" s="28" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="21">
         <v>0</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="26">
         <v>3.5</v>
       </c>
-      <c r="E17" s="71" t="s">
+      <c r="E17" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="29"/>
-      <c r="G17" s="30" t="s">
+      <c r="F17" s="27"/>
+      <c r="G17" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="21">
         <v>0</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="26">
         <v>0.25</v>
       </c>
-      <c r="E18" s="69" t="s">
+      <c r="E18" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="29" t="s">
+      <c r="F18" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="G18" s="28" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="21">
         <v>0</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="26">
         <v>0.25</v>
       </c>
-      <c r="E19" s="69" t="s">
+      <c r="E19" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="30" t="s">
+      <c r="G19" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="21">
         <v>0</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="26">
         <v>0.25</v>
       </c>
-      <c r="E20" s="69" t="s">
+      <c r="E20" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="29" t="s">
+      <c r="F20" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G20" s="28" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="21">
         <v>0</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="26">
         <v>0.25</v>
       </c>
-      <c r="E21" s="69" t="s">
+      <c r="E21" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="G21" s="30" t="s">
+      <c r="G21" s="28" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B22" s="21">
         <v>0</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="26">
         <v>0.1</v>
       </c>
-      <c r="E22" s="69" t="s">
+      <c r="E22" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="G22" s="30" t="s">
+      <c r="G22" s="28" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="21">
         <v>0</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="26">
         <v>1</v>
       </c>
-      <c r="E23" s="69" t="s">
+      <c r="E23" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="29"/>
-      <c r="G23" s="30" t="s">
+      <c r="F23" s="27"/>
+      <c r="G23" s="28" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="21">
         <v>0</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="26">
         <v>0.17</v>
       </c>
-      <c r="E24" s="69" t="s">
+      <c r="E24" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="G24" s="30" t="s">
+      <c r="G24" s="28" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B25" s="21">
         <v>0</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="26">
         <v>0.08</v>
       </c>
-      <c r="E25" s="69" t="s">
+      <c r="E25" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="30" t="s">
+      <c r="G25" s="28" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B26" s="21">
         <v>0</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="26">
         <v>0.25</v>
       </c>
-      <c r="E26" s="69" t="s">
+      <c r="E26" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="29" t="s">
+      <c r="F26" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="G26" s="30" t="s">
+      <c r="G26" s="28" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="21">
         <v>0</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="26">
         <v>0.08</v>
       </c>
-      <c r="E27" s="69" t="s">
+      <c r="E27" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="G27" s="30" t="s">
+      <c r="G27" s="28" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B28" s="21">
         <v>0</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="26">
         <v>0.17</v>
       </c>
-      <c r="E28" s="69" t="s">
+      <c r="E28" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G28" s="28" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="21">
         <v>1</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="29">
         <v>0.42</v>
       </c>
-      <c r="E29" s="70" t="s">
+      <c r="E29" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="F29" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="22" t="s">
+      <c r="G29" s="20" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B30" s="21">
         <v>1</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="29">
         <v>0.57999999999999996</v>
       </c>
-      <c r="E30" s="70" t="s">
+      <c r="E30" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F30" s="25" t="s">
+      <c r="F30" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="20" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="21">
         <v>1</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D31" s="31">
+      <c r="D31" s="29">
         <v>0.5</v>
       </c>
-      <c r="E31" s="70" t="s">
+      <c r="E31" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F31" s="25" t="s">
+      <c r="F31" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="G31" s="22" t="s">
+      <c r="G31" s="20" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B32" s="21">
         <v>1</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="31">
+      <c r="D32" s="29">
         <v>0.25</v>
       </c>
-      <c r="E32" s="70" t="s">
+      <c r="E32" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F32" s="25" t="s">
+      <c r="F32" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="22" t="s">
+      <c r="G32" s="20" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B33" s="21">
         <v>1</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D33" s="31">
+      <c r="D33" s="29">
         <v>0.33</v>
       </c>
-      <c r="E33" s="70" t="s">
+      <c r="E33" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F33" s="25" t="s">
+      <c r="F33" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="G33" s="20" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="21">
         <v>1</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D34" s="31">
+      <c r="D34" s="29">
         <v>0.33</v>
       </c>
-      <c r="E34" s="70" t="s">
+      <c r="E34" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F34" s="25" t="s">
+      <c r="F34" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="20" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B35" s="21">
         <v>1</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C35" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="31">
+      <c r="D35" s="29">
         <v>0.42</v>
       </c>
-      <c r="E35" s="70" t="s">
+      <c r="E35" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F35" s="25" t="s">
+      <c r="F35" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="G35" s="22" t="s">
+      <c r="G35" s="20" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B36" s="21">
         <v>1</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="31">
+      <c r="D36" s="29">
         <v>0.25</v>
       </c>
-      <c r="E36" s="70" t="s">
+      <c r="E36" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F36" s="25" t="s">
+      <c r="F36" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="22" t="s">
+      <c r="G36" s="20" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B37" s="21">
         <v>1</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="31">
+      <c r="D37" s="29">
         <v>0.25</v>
       </c>
-      <c r="E37" s="70" t="s">
+      <c r="E37" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F37" s="25" t="s">
+      <c r="F37" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="G37" s="22" t="s">
+      <c r="G37" s="20" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="21">
         <v>1</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="29">
         <v>0.67</v>
       </c>
-      <c r="E38" s="70" t="s">
+      <c r="E38" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="F38" s="25" t="s">
+      <c r="F38" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="20" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="B39" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="29">
         <v>0.33</v>
       </c>
-      <c r="E39" s="72" t="s">
+      <c r="E39" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F39" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="20" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B40" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="31">
+      <c r="D40" s="29">
         <v>0.33</v>
       </c>
-      <c r="E40" s="72" t="s">
+      <c r="E40" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="F40" s="25" t="s">
+      <c r="F40" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="G40" s="22" t="s">
+      <c r="G40" s="20" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="29">
         <v>0.33</v>
       </c>
-      <c r="E41" s="72" t="s">
+      <c r="E41" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="F41" s="25" t="s">
+      <c r="F41" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="G41" s="22" t="s">
+      <c r="G41" s="20" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="29">
         <v>0.33</v>
       </c>
-      <c r="E42" s="72" t="s">
+      <c r="E42" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="F42" s="25" t="s">
+      <c r="F42" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="G42" s="22" t="s">
+      <c r="G42" s="20" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="23" t="s">
+      <c r="A43" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C43" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="29">
         <v>0.33</v>
       </c>
-      <c r="E43" s="72" t="s">
+      <c r="E43" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="25" t="s">
+      <c r="F43" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="G43" s="22" t="s">
+      <c r="G43" s="20" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="29">
         <v>0.33</v>
       </c>
-      <c r="E44" s="72" t="s">
+      <c r="E44" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="F44" s="25" t="s">
+      <c r="F44" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="G44" s="22" t="s">
+      <c r="G44" s="20" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="29">
         <v>0.33</v>
       </c>
-      <c r="E45" s="72" t="s">
+      <c r="E45" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="F45" s="25" t="s">
+      <c r="F45" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="G45" s="22" t="s">
+      <c r="G45" s="20" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="29">
         <v>0.33</v>
       </c>
-      <c r="E46" s="72" t="s">
+      <c r="E46" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="F46" s="25" t="s">
+      <c r="F46" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="G46" s="22" t="s">
+      <c r="G46" s="20" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="B47" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="29">
         <v>0.17</v>
       </c>
-      <c r="E47" s="72" t="s">
+      <c r="E47" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="F47" s="25" t="s">
+      <c r="F47" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="G47" s="22" t="s">
+      <c r="G47" s="20" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="29">
         <v>0.25</v>
       </c>
-      <c r="E48" s="72" t="s">
+      <c r="E48" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="F48" s="25" t="s">
+      <c r="F48" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="G48" s="22" t="s">
+      <c r="G48" s="20" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="B49" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="C49" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D49" s="31">
+      <c r="D49" s="29">
         <v>0.17</v>
       </c>
-      <c r="E49" s="72" t="s">
+      <c r="E49" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="F49" s="25" t="s">
+      <c r="F49" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="G49" s="22" t="s">
+      <c r="G49" s="20" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="23" t="s">
+      <c r="A50" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B50" s="23" t="s">
+      <c r="B50" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="29">
         <v>0.25</v>
       </c>
-      <c r="E50" s="72" t="s">
+      <c r="E50" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="F50" s="25" t="s">
+      <c r="F50" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="G50" s="22" t="s">
+      <c r="G50" s="20" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="31">
+      <c r="D51" s="29">
         <v>0.5</v>
       </c>
-      <c r="E51" s="72" t="s">
+      <c r="E51" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="F51" s="25" t="s">
+      <c r="F51" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="G51" s="22" t="s">
+      <c r="G51" s="20" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="23" t="s">
+      <c r="A52" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B52" s="23" t="s">
+      <c r="B52" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="D52" s="31">
+      <c r="D52" s="29">
         <v>0.5</v>
       </c>
-      <c r="E52" s="72" t="s">
+      <c r="E52" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="F52" s="25" t="s">
+      <c r="F52" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="G52" s="22" t="s">
+      <c r="G52" s="20" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="23" t="s">
+      <c r="A53" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="29">
         <v>0.5</v>
       </c>
-      <c r="E53" s="72" t="s">
+      <c r="E53" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="F53" s="25" t="s">
+      <c r="F53" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="G53" s="22" t="s">
+      <c r="G53" s="20" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="25" t="s">
+      <c r="B54" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="D54" s="31">
+      <c r="D54" s="29">
         <v>0.75</v>
       </c>
-      <c r="E54" s="72" t="s">
+      <c r="E54" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="F54" s="25" t="s">
+      <c r="F54" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="G54" s="22" t="s">
+      <c r="G54" s="20" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B55" s="25" t="s">
+      <c r="B55" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="31">
+      <c r="D55" s="29">
         <v>0.5</v>
       </c>
-      <c r="E55" s="72" t="s">
+      <c r="E55" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="F55" s="25" t="s">
+      <c r="F55" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="G55" s="22" t="s">
+      <c r="G55" s="20" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B56" s="25" t="s">
+      <c r="B56" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="29">
         <v>0.33</v>
       </c>
-      <c r="E56" s="72" t="s">
+      <c r="E56" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="F56" s="25" t="s">
+      <c r="F56" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="G56" s="22" t="s">
+      <c r="G56" s="20" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="25" t="s">
+      <c r="A57" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D57" s="28">
+      <c r="D57" s="26">
         <v>0.1</v>
       </c>
-      <c r="E57" s="72" t="s">
+      <c r="E57" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="F57" s="25" t="s">
+      <c r="F57" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="G57" s="22" t="s">
+      <c r="G57" s="20" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="77" t="s">
+      <c r="A58" s="74" t="s">
         <v>245</v>
       </c>
-      <c r="B58" s="77" t="s">
+      <c r="B58" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="77" t="s">
+      <c r="C58" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="D58" s="77">
+      <c r="D58" s="74">
         <v>0.75</v>
       </c>
-      <c r="E58" s="75" t="s">
+      <c r="E58" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="F58" s="77" t="s">
+      <c r="F58" s="74" t="s">
         <v>246</v>
       </c>
-      <c r="G58" s="78" t="s">
+      <c r="G58" s="75" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="77" t="s">
+      <c r="A59" s="74" t="s">
         <v>245</v>
       </c>
-      <c r="B59" s="77" t="s">
+      <c r="B59" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C59" s="77" t="s">
+      <c r="C59" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="D59" s="77">
+      <c r="D59" s="74">
         <v>1</v>
       </c>
-      <c r="E59" s="75" t="s">
+      <c r="E59" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="F59" s="77" t="s">
+      <c r="F59" s="74" t="s">
         <v>248</v>
       </c>
-      <c r="G59" s="78" t="s">
+      <c r="G59" s="75" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="77" t="s">
+      <c r="A60" s="74" t="s">
         <v>245</v>
       </c>
-      <c r="B60" s="77" t="s">
+      <c r="B60" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C60" s="77" t="s">
+      <c r="C60" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="D60" s="77">
+      <c r="D60" s="74">
         <v>1.5</v>
       </c>
-      <c r="E60" s="75" t="s">
+      <c r="E60" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="F60" s="77" t="s">
+      <c r="F60" s="74" t="s">
         <v>250</v>
       </c>
-      <c r="G60" s="78" t="s">
+      <c r="G60" s="75" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="77" t="s">
+      <c r="A61" s="74" t="s">
         <v>245</v>
       </c>
-      <c r="B61" s="77" t="s">
+      <c r="B61" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C61" s="77" t="s">
+      <c r="C61" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="D61" s="77">
+      <c r="D61" s="74">
         <v>0.75</v>
       </c>
-      <c r="E61" s="75" t="s">
+      <c r="E61" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="F61" s="77" t="s">
+      <c r="F61" s="74" t="s">
         <v>252</v>
       </c>
-      <c r="G61" s="78" t="s">
+      <c r="G61" s="75" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="77" t="s">
+      <c r="A62" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="B62" s="77" t="s">
+      <c r="B62" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C62" s="77" t="s">
+      <c r="C62" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="D62" s="77">
+      <c r="D62" s="74">
         <v>0.75</v>
       </c>
-      <c r="E62" s="75" t="s">
+      <c r="E62" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="F62" s="77" t="s">
+      <c r="F62" s="74" t="s">
         <v>255</v>
       </c>
-      <c r="G62" s="78" t="s">
+      <c r="G62" s="75" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="77" t="s">
+      <c r="A63" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="B63" s="77" t="s">
+      <c r="B63" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C63" s="77" t="s">
+      <c r="C63" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="D63" s="77">
+      <c r="D63" s="74">
         <v>0.25</v>
       </c>
-      <c r="E63" s="75" t="s">
+      <c r="E63" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="F63" s="77" t="s">
+      <c r="F63" s="74" t="s">
         <v>257</v>
       </c>
-      <c r="G63" s="78" t="s">
+      <c r="G63" s="75" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="77" t="s">
+      <c r="A64" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="B64" s="77" t="s">
+      <c r="B64" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C64" s="77" t="s">
+      <c r="C64" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="D64" s="77">
+      <c r="D64" s="74">
         <v>0.5</v>
       </c>
-      <c r="E64" s="75" t="s">
+      <c r="E64" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="F64" s="77" t="s">
+      <c r="F64" s="74" t="s">
         <v>259</v>
       </c>
-      <c r="G64" s="78" t="s">
+      <c r="G64" s="75" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="77" t="s">
+      <c r="A65" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="B65" s="77" t="s">
+      <c r="B65" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C65" s="77" t="s">
+      <c r="C65" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="D65" s="77">
+      <c r="D65" s="74">
         <v>0.5</v>
       </c>
-      <c r="E65" s="75" t="s">
+      <c r="E65" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="F65" s="77" t="s">
+      <c r="F65" s="74" t="s">
         <v>261</v>
       </c>
-      <c r="G65" s="78" t="s">
+      <c r="G65" s="75" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="77" t="s">
+      <c r="A66" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="B66" s="77" t="s">
+      <c r="B66" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C66" s="77" t="s">
+      <c r="C66" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="77">
+      <c r="D66" s="74">
         <v>0.5</v>
       </c>
-      <c r="E66" s="76" t="s">
+      <c r="E66" s="73" t="s">
         <v>207</v>
       </c>
-      <c r="F66" s="77" t="s">
+      <c r="F66" s="74" t="s">
         <v>263</v>
       </c>
-      <c r="G66" s="78" t="s">
+      <c r="G66" s="75" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="77" t="s">
+      <c r="A67" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="B67" s="77" t="s">
+      <c r="B67" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C67" s="77" t="s">
+      <c r="C67" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="D67" s="77">
+      <c r="D67" s="74">
         <v>0.17</v>
       </c>
-      <c r="E67" s="76" t="s">
+      <c r="E67" s="73" t="s">
         <v>207</v>
       </c>
-      <c r="F67" s="77" t="s">
+      <c r="F67" s="74" t="s">
         <v>265</v>
       </c>
-      <c r="G67" s="78" t="s">
+      <c r="G67" s="75" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="77" t="s">
+      <c r="A68" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="B68" s="77" t="s">
+      <c r="B68" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C68" s="77" t="s">
+      <c r="C68" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="D68" s="77">
+      <c r="D68" s="74">
         <v>0.17</v>
       </c>
-      <c r="E68" s="76" t="s">
+      <c r="E68" s="73" t="s">
         <v>207</v>
       </c>
-      <c r="F68" s="77" t="s">
+      <c r="F68" s="74" t="s">
         <v>267</v>
       </c>
-      <c r="G68" s="78" t="s">
+      <c r="G68" s="75" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="77" t="s">
+      <c r="A69" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="B69" s="77" t="s">
+      <c r="B69" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C69" s="77" t="s">
+      <c r="C69" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="77">
+      <c r="D69" s="74">
         <v>0.17</v>
       </c>
-      <c r="E69" s="76" t="s">
+      <c r="E69" s="73" t="s">
         <v>207</v>
       </c>
-      <c r="F69" s="77" t="s">
+      <c r="F69" s="74" t="s">
         <v>269</v>
       </c>
-      <c r="G69" s="78" t="s">
+      <c r="G69" s="75" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="77" t="s">
+      <c r="A70" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="B70" s="77" t="s">
+      <c r="B70" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C70" s="77" t="s">
+      <c r="C70" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="D70" s="77">
+      <c r="D70" s="74">
         <v>0.17</v>
       </c>
-      <c r="E70" s="76" t="s">
+      <c r="E70" s="73" t="s">
         <v>207</v>
       </c>
-      <c r="F70" s="77" t="s">
+      <c r="F70" s="74" t="s">
         <v>271</v>
       </c>
-      <c r="G70" s="78" t="s">
+      <c r="G70" s="75" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="77" t="s">
+      <c r="A71" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="B71" s="77" t="s">
+      <c r="B71" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C71" s="77" t="s">
+      <c r="C71" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="D71" s="77">
+      <c r="D71" s="74">
         <v>0.17</v>
       </c>
-      <c r="E71" s="76" t="s">
+      <c r="E71" s="73" t="s">
         <v>207</v>
       </c>
-      <c r="F71" s="77" t="s">
+      <c r="F71" s="74" t="s">
         <v>273</v>
       </c>
-      <c r="G71" s="78" t="s">
+      <c r="G71" s="75" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="77" t="s">
+      <c r="A72" s="74" t="s">
         <v>254</v>
       </c>
-      <c r="B72" s="77" t="s">
+      <c r="B72" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="C72" s="77" t="s">
+      <c r="C72" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="D72" s="77">
+      <c r="D72" s="74">
         <v>0.25</v>
       </c>
-      <c r="E72" s="76" t="s">
+      <c r="E72" s="73" t="s">
         <v>207</v>
       </c>
-      <c r="F72" s="77" t="s">
+      <c r="F72" s="74" t="s">
         <v>275</v>
       </c>
-      <c r="G72" s="78" t="s">
+      <c r="G72" s="75" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="23" t="s">
+      <c r="A73" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="B73" s="23" t="s">
+      <c r="B73" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D73" s="23">
+      <c r="D73" s="21">
         <v>0.17</v>
       </c>
-      <c r="E73" s="82" t="s">
+      <c r="E73" s="79" t="s">
         <v>208</v>
       </c>
-      <c r="F73" s="23" t="s">
+      <c r="F73" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="G73" s="81" t="s">
+      <c r="G73" s="78" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="23" t="s">
+      <c r="A74" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="B74" s="23" t="s">
+      <c r="B74" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D74" s="23">
+      <c r="D74" s="21">
         <v>0.08</v>
       </c>
-      <c r="E74" s="82" t="s">
+      <c r="E74" s="79" t="s">
         <v>208</v>
       </c>
-      <c r="F74" s="23" t="s">
+      <c r="F74" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="G74" s="81" t="s">
+      <c r="G74" s="78" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="23" t="s">
+      <c r="A75" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="B75" s="23" t="s">
+      <c r="B75" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="23">
+      <c r="D75" s="21">
         <v>0.5</v>
       </c>
-      <c r="E75" s="82" t="s">
+      <c r="E75" s="79" t="s">
         <v>208</v>
       </c>
-      <c r="F75" s="23" t="s">
+      <c r="F75" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="G75" s="81" t="s">
+      <c r="G75" s="78" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="23" t="s">
+      <c r="A76" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="B76" s="23" t="s">
+      <c r="B76" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D76" s="23">
+      <c r="D76" s="21">
         <v>1</v>
       </c>
-      <c r="E76" s="82" t="s">
+      <c r="E76" s="79" t="s">
         <v>208</v>
       </c>
-      <c r="F76" s="23" t="s">
+      <c r="F76" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="G76" s="81" t="s">
+      <c r="G76" s="78" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="23" t="s">
+      <c r="A77" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="B77" s="23" t="s">
+      <c r="B77" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D77" s="23">
+      <c r="D77" s="21">
         <v>0.33</v>
       </c>
-      <c r="E77" s="82" t="s">
+      <c r="E77" s="79" t="s">
         <v>208</v>
       </c>
-      <c r="F77" s="23" t="s">
+      <c r="F77" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="G77" s="81" t="s">
+      <c r="G77" s="78" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="23" t="s">
+      <c r="A78" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="B78" s="23" t="s">
+      <c r="B78" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D78" s="23">
+      <c r="D78" s="21">
         <v>0.5</v>
       </c>
-      <c r="E78" s="82" t="s">
+      <c r="E78" s="79" t="s">
         <v>209</v>
       </c>
-      <c r="F78" s="23" t="s">
+      <c r="F78" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="G78" s="81" t="s">
+      <c r="G78" s="78" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="23" t="s">
+      <c r="A79" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="B79" s="23" t="s">
+      <c r="B79" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C79" s="23" t="s">
+      <c r="C79" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D79" s="23">
+      <c r="D79" s="21">
         <v>1</v>
       </c>
-      <c r="E79" s="82" t="s">
+      <c r="E79" s="79" t="s">
         <v>209</v>
       </c>
-      <c r="F79" s="23" t="s">
+      <c r="F79" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="G79" s="81" t="s">
+      <c r="G79" s="78" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="23" t="s">
+      <c r="A80" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="B80" s="23" t="s">
+      <c r="B80" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C80" s="23" t="s">
+      <c r="C80" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D80" s="23">
+      <c r="D80" s="21">
         <v>0.75</v>
       </c>
-      <c r="E80" s="82" t="s">
+      <c r="E80" s="79" t="s">
         <v>209</v>
       </c>
-      <c r="F80" s="23" t="s">
+      <c r="F80" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="G80" s="81" t="s">
+      <c r="G80" s="78" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="23" t="s">
+      <c r="A81" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="B81" s="23" t="s">
+      <c r="B81" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C81" s="23" t="s">
+      <c r="C81" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D81" s="23">
+      <c r="D81" s="21">
         <v>0.5</v>
       </c>
-      <c r="E81" s="82" t="s">
+      <c r="E81" s="79" t="s">
         <v>209</v>
       </c>
-      <c r="F81" s="23" t="s">
+      <c r="F81" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="G81" s="81" t="s">
+      <c r="G81" s="78" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="23" t="s">
+      <c r="A82" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="B82" s="23" t="s">
+      <c r="B82" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C82" s="23" t="s">
+      <c r="C82" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="23">
+      <c r="D82" s="21">
         <v>2</v>
       </c>
-      <c r="E82" s="82" t="s">
+      <c r="E82" s="79" t="s">
         <v>210</v>
       </c>
-      <c r="F82" s="23" t="s">
+      <c r="F82" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="G82" s="81" t="s">
+      <c r="G82" s="78" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="23" t="s">
+      <c r="A83" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="B83" s="23" t="s">
+      <c r="B83" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C83" s="23" t="s">
+      <c r="C83" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D83" s="23">
+      <c r="D83" s="21">
         <v>0.5</v>
       </c>
-      <c r="E83" s="82" t="s">
+      <c r="E83" s="79" t="s">
         <v>210</v>
       </c>
-      <c r="F83" s="23" t="s">
+      <c r="F83" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="G83" s="81" t="s">
+      <c r="G83" s="78" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="23" t="s">
+      <c r="A84" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="B84" s="23" t="s">
+      <c r="B84" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C84" s="23" t="s">
+      <c r="C84" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D84" s="23">
+      <c r="D84" s="21">
         <v>0.75</v>
       </c>
-      <c r="E84" s="82" t="s">
+      <c r="E84" s="79" t="s">
         <v>210</v>
       </c>
-      <c r="F84" s="23" t="s">
+      <c r="F84" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="G84" s="81" t="s">
+      <c r="G84" s="78" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="23" t="s">
+      <c r="A85" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="B85" s="23" t="s">
+      <c r="B85" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C85" s="23" t="s">
+      <c r="C85" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D85" s="23">
+      <c r="D85" s="21">
         <v>1</v>
       </c>
-      <c r="E85" s="82" t="s">
+      <c r="E85" s="79" t="s">
         <v>210</v>
       </c>
-      <c r="F85" s="23" t="s">
+      <c r="F85" s="21" t="s">
         <v>307</v>
       </c>
-      <c r="G85" s="81" t="s">
+      <c r="G85" s="78" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="23" t="s">
+      <c r="A86" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="B86" s="23" t="s">
+      <c r="B86" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C86" s="23" t="s">
+      <c r="C86" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D86" s="23">
+      <c r="D86" s="21">
         <v>1</v>
       </c>
-      <c r="E86" s="82" t="s">
+      <c r="E86" s="79" t="s">
         <v>210</v>
       </c>
-      <c r="F86" s="23" t="s">
+      <c r="F86" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="G86" s="81" t="s">
+      <c r="G86" s="78" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="23" t="s">
+      <c r="A87" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="B87" s="23" t="s">
+      <c r="B87" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C87" s="23" t="s">
+      <c r="C87" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D87" s="23">
+      <c r="D87" s="21">
         <v>1</v>
       </c>
-      <c r="E87" s="82" t="s">
+      <c r="E87" s="79" t="s">
         <v>210</v>
       </c>
-      <c r="F87" s="23" t="s">
+      <c r="F87" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="G87" s="81" t="s">
+      <c r="G87" s="78" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="23" t="s">
+      <c r="A88" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="B88" s="23" t="s">
+      <c r="B88" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C88" s="23" t="s">
+      <c r="C88" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D88" s="23">
+      <c r="D88" s="21">
         <v>2</v>
       </c>
-      <c r="E88" s="82" t="s">
+      <c r="E88" s="79" t="s">
         <v>210</v>
       </c>
-      <c r="F88" s="23" t="s">
+      <c r="F88" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="G88" s="81" t="s">
+      <c r="G88" s="78" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="23" t="s">
+      <c r="A89" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="B89" s="23" t="s">
+      <c r="B89" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C89" s="23" t="s">
+      <c r="C89" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D89" s="23">
+      <c r="D89" s="21">
         <v>0.5</v>
       </c>
-      <c r="E89" s="82" t="s">
+      <c r="E89" s="79" t="s">
         <v>210</v>
       </c>
-      <c r="F89" s="23" t="s">
+      <c r="F89" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="G89" s="81" t="s">
+      <c r="G89" s="78" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="23" t="s">
+      <c r="A90" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="B90" s="23" t="s">
+      <c r="B90" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C90" s="23" t="s">
+      <c r="C90" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D90" s="23">
+      <c r="D90" s="21">
         <v>0.25</v>
       </c>
-      <c r="E90" s="82" t="s">
+      <c r="E90" s="79" t="s">
         <v>210</v>
       </c>
-      <c r="F90" s="23" t="s">
+      <c r="F90" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="G90" s="81" t="s">
+      <c r="G90" s="78" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="23" t="s">
+      <c r="A91" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B91" s="23" t="s">
+      <c r="B91" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C91" s="23" t="s">
+      <c r="C91" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D91" s="23">
+      <c r="D91" s="21">
         <v>1</v>
       </c>
-      <c r="E91" s="82" t="s">
+      <c r="E91" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F91" s="23" t="s">
+      <c r="F91" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="G91" s="81" t="s">
+      <c r="G91" s="78" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="23" t="s">
+      <c r="A92" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B92" s="23" t="s">
+      <c r="B92" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C92" s="23" t="s">
+      <c r="C92" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D92" s="23">
+      <c r="D92" s="21">
         <v>1.5</v>
       </c>
-      <c r="E92" s="82" t="s">
+      <c r="E92" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F92" s="23" t="s">
+      <c r="F92" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="G92" s="81" t="s">
+      <c r="G92" s="78" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="23" t="s">
+      <c r="A93" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B93" s="23" t="s">
+      <c r="B93" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C93" s="23" t="s">
+      <c r="C93" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D93" s="23">
+      <c r="D93" s="21">
         <v>0.33</v>
       </c>
-      <c r="E93" s="82" t="s">
+      <c r="E93" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F93" s="23" t="s">
+      <c r="F93" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="G93" s="81" t="s">
+      <c r="G93" s="78" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" s="23" t="s">
+      <c r="A94" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B94" s="23" t="s">
+      <c r="B94" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C94" s="23" t="s">
+      <c r="C94" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D94" s="23">
+      <c r="D94" s="21">
         <v>0.75</v>
       </c>
-      <c r="E94" s="82" t="s">
+      <c r="E94" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F94" s="23" t="s">
+      <c r="F94" s="21" t="s">
         <v>328</v>
       </c>
-      <c r="G94" s="81" t="s">
+      <c r="G94" s="78" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="23" t="s">
+      <c r="A95" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B95" s="23" t="s">
+      <c r="B95" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C95" s="23" t="s">
+      <c r="C95" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D95" s="23">
+      <c r="D95" s="21">
         <v>2</v>
       </c>
-      <c r="E95" s="82" t="s">
+      <c r="E95" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F95" s="23" t="s">
+      <c r="F95" s="21" t="s">
         <v>330</v>
       </c>
-      <c r="G95" s="81" t="s">
+      <c r="G95" s="78" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="23" t="s">
+      <c r="A96" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B96" s="23" t="s">
+      <c r="B96" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C96" s="23" t="s">
+      <c r="C96" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D96" s="23">
+      <c r="D96" s="21">
         <v>1</v>
       </c>
-      <c r="E96" s="82" t="s">
+      <c r="E96" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F96" s="23" t="s">
+      <c r="F96" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="G96" s="81" t="s">
+      <c r="G96" s="78" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="23" t="s">
+      <c r="A97" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B97" s="23" t="s">
+      <c r="B97" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C97" s="23" t="s">
+      <c r="C97" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D97" s="23">
+      <c r="D97" s="21">
         <v>0.75</v>
       </c>
-      <c r="E97" s="82" t="s">
+      <c r="E97" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F97" s="23" t="s">
+      <c r="F97" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="G97" s="81" t="s">
+      <c r="G97" s="78" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="23" t="s">
+      <c r="A98" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B98" s="23" t="s">
+      <c r="B98" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C98" s="23" t="s">
+      <c r="C98" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D98" s="23">
+      <c r="D98" s="21">
         <v>0.5</v>
       </c>
-      <c r="E98" s="82" t="s">
+      <c r="E98" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F98" s="23" t="s">
+      <c r="F98" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="G98" s="81" t="s">
+      <c r="G98" s="78" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="23" t="s">
+      <c r="A99" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B99" s="23" t="s">
+      <c r="B99" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C99" s="23" t="s">
+      <c r="C99" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D99" s="23">
+      <c r="D99" s="21">
         <v>0.75</v>
       </c>
-      <c r="E99" s="82" t="s">
+      <c r="E99" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F99" s="23" t="s">
+      <c r="F99" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="G99" s="81" t="s">
+      <c r="G99" s="78" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="23" t="s">
+      <c r="A100" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B100" s="23" t="s">
+      <c r="B100" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C100" s="23" t="s">
+      <c r="C100" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D100" s="23">
+      <c r="D100" s="21">
         <v>0.25</v>
       </c>
-      <c r="E100" s="82" t="s">
+      <c r="E100" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F100" s="23" t="s">
+      <c r="F100" s="21" t="s">
         <v>339</v>
       </c>
-      <c r="G100" s="81" t="s">
+      <c r="G100" s="78" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="23" t="s">
+      <c r="A101" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B101" s="23" t="s">
+      <c r="B101" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C101" s="23" t="s">
+      <c r="C101" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D101" s="23">
+      <c r="D101" s="21">
         <v>0.25</v>
       </c>
-      <c r="E101" s="82" t="s">
+      <c r="E101" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F101" s="23" t="s">
+      <c r="F101" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="G101" s="81" t="s">
+      <c r="G101" s="78" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="23" t="s">
+      <c r="A102" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B102" s="23" t="s">
+      <c r="B102" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C102" s="23" t="s">
+      <c r="C102" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D102" s="23">
+      <c r="D102" s="21">
         <v>0.25</v>
       </c>
-      <c r="E102" s="82" t="s">
+      <c r="E102" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F102" s="23" t="s">
+      <c r="F102" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="G102" s="81" t="s">
+      <c r="G102" s="78" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="23" t="s">
+      <c r="A103" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B103" s="23" t="s">
+      <c r="B103" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C103" s="23" t="s">
+      <c r="C103" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D103" s="23">
+      <c r="D103" s="21">
         <v>0.5</v>
       </c>
-      <c r="E103" s="82" t="s">
+      <c r="E103" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F103" s="23" t="s">
+      <c r="F103" s="21" t="s">
         <v>343</v>
       </c>
-      <c r="G103" s="81" t="s">
+      <c r="G103" s="78" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="23" t="s">
+      <c r="A104" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B104" s="23" t="s">
+      <c r="B104" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C104" s="23" t="s">
+      <c r="C104" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D104" s="23">
+      <c r="D104" s="21">
         <v>0.33</v>
       </c>
-      <c r="E104" s="82" t="s">
+      <c r="E104" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F104" s="23" t="s">
+      <c r="F104" s="21" t="s">
         <v>345</v>
       </c>
-      <c r="G104" s="81" t="s">
+      <c r="G104" s="78" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" s="23" t="s">
+      <c r="A105" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B105" s="23" t="s">
+      <c r="B105" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C105" s="23" t="s">
+      <c r="C105" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D105" s="23">
+      <c r="D105" s="21">
         <v>0.25</v>
       </c>
-      <c r="E105" s="82" t="s">
+      <c r="E105" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F105" s="23" t="s">
+      <c r="F105" s="21" t="s">
         <v>346</v>
       </c>
-      <c r="G105" s="81" t="s">
+      <c r="G105" s="78" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" s="23" t="s">
+      <c r="A106" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B106" s="23" t="s">
+      <c r="B106" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C106" s="23" t="s">
+      <c r="C106" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D106" s="23">
+      <c r="D106" s="21">
         <v>0.33</v>
       </c>
-      <c r="E106" s="82" t="s">
+      <c r="E106" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F106" s="23" t="s">
+      <c r="F106" s="21" t="s">
         <v>347</v>
       </c>
-      <c r="G106" s="81" t="s">
+      <c r="G106" s="78" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" s="23" t="s">
+      <c r="A107" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B107" s="23" t="s">
+      <c r="B107" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C107" s="23" t="s">
+      <c r="C107" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D107" s="23">
+      <c r="D107" s="21">
         <v>0.5</v>
       </c>
-      <c r="E107" s="82" t="s">
+      <c r="E107" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F107" s="23" t="s">
+      <c r="F107" s="21" t="s">
         <v>349</v>
       </c>
-      <c r="G107" s="81" t="s">
+      <c r="G107" s="78" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="23" t="s">
+      <c r="A108" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B108" s="23" t="s">
+      <c r="B108" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C108" s="23" t="s">
+      <c r="C108" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D108" s="23">
+      <c r="D108" s="21">
         <v>0.17</v>
       </c>
-      <c r="E108" s="82" t="s">
+      <c r="E108" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F108" s="23" t="s">
+      <c r="F108" s="21" t="s">
         <v>350</v>
       </c>
-      <c r="G108" s="81" t="s">
+      <c r="G108" s="78" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="23" t="s">
+      <c r="A109" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B109" s="23" t="s">
+      <c r="B109" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C109" s="23" t="s">
+      <c r="C109" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D109" s="23">
+      <c r="D109" s="21">
         <v>0.17</v>
       </c>
-      <c r="E109" s="82" t="s">
+      <c r="E109" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F109" s="23" t="s">
+      <c r="F109" s="21" t="s">
         <v>351</v>
       </c>
-      <c r="G109" s="81" t="s">
+      <c r="G109" s="78" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="23" t="s">
+      <c r="A110" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="B110" s="23" t="s">
+      <c r="B110" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C110" s="23" t="s">
+      <c r="C110" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D110" s="23">
+      <c r="D110" s="21">
         <v>0.5</v>
       </c>
-      <c r="E110" s="82" t="s">
+      <c r="E110" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F110" s="23" t="s">
+      <c r="F110" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="G110" s="81" t="s">
+      <c r="G110" s="78" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="23" t="s">
+      <c r="A111" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="B111" s="23" t="s">
+      <c r="B111" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C111" s="23" t="s">
+      <c r="C111" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D111" s="23">
+      <c r="D111" s="21">
         <v>0.25</v>
       </c>
-      <c r="E111" s="82" t="s">
+      <c r="E111" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F111" s="23" t="s">
+      <c r="F111" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="G111" s="81" t="s">
+      <c r="G111" s="78" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="23" t="s">
+      <c r="A112" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="B112" s="23" t="s">
+      <c r="B112" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C112" s="23" t="s">
+      <c r="C112" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D112" s="23">
+      <c r="D112" s="21">
         <v>1</v>
       </c>
-      <c r="E112" s="82" t="s">
+      <c r="E112" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F112" s="23" t="s">
+      <c r="F112" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="G112" s="81" t="s">
+      <c r="G112" s="78" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" s="23" t="s">
+      <c r="A113" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="B113" s="23" t="s">
+      <c r="B113" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C113" s="23" t="s">
+      <c r="C113" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D113" s="23">
+      <c r="D113" s="21">
         <v>0.5</v>
       </c>
-      <c r="E113" s="82" t="s">
+      <c r="E113" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F113" s="23" t="s">
+      <c r="F113" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="G113" s="81" t="s">
+      <c r="G113" s="78" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="23" t="s">
+      <c r="A114" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="B114" s="23" t="s">
+      <c r="B114" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="23" t="s">
+      <c r="C114" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="D114" s="23">
+      <c r="D114" s="21">
         <v>0.75</v>
       </c>
-      <c r="E114" s="82" t="s">
+      <c r="E114" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F114" s="23" t="s">
+      <c r="F114" s="21" t="s">
         <v>361</v>
       </c>
-      <c r="G114" s="81" t="s">
+      <c r="G114" s="78" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="23" t="s">
+      <c r="A115" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="B115" s="23" t="s">
+      <c r="B115" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C115" s="23" t="s">
+      <c r="C115" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D115" s="23">
+      <c r="D115" s="21">
         <v>0.5</v>
       </c>
-      <c r="E115" s="82" t="s">
+      <c r="E115" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F115" s="23" t="s">
+      <c r="F115" s="21" t="s">
         <v>363</v>
       </c>
-      <c r="G115" s="81" t="s">
+      <c r="G115" s="78" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="23" t="s">
+      <c r="A116" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="B116" s="23" t="s">
+      <c r="B116" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C116" s="23" t="s">
+      <c r="C116" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D116" s="23">
+      <c r="D116" s="21">
         <v>0.5</v>
       </c>
-      <c r="E116" s="82" t="s">
+      <c r="E116" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F116" s="23" t="s">
+      <c r="F116" s="21" t="s">
         <v>365</v>
       </c>
-      <c r="G116" s="81" t="s">
+      <c r="G116" s="78" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="23" t="s">
+      <c r="A117" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="B117" s="23" t="s">
+      <c r="B117" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C117" s="23" t="s">
+      <c r="C117" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D117" s="23">
+      <c r="D117" s="21">
         <v>0.33</v>
       </c>
-      <c r="E117" s="82" t="s">
+      <c r="E117" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F117" s="23" t="s">
+      <c r="F117" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="G117" s="81" t="s">
+      <c r="G117" s="78" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="23" t="s">
+      <c r="A118" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="B118" s="23" t="s">
+      <c r="B118" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="C118" s="23" t="s">
+      <c r="C118" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D118" s="23">
+      <c r="D118" s="21">
         <v>0.25</v>
       </c>
-      <c r="E118" s="82" t="s">
+      <c r="E118" s="79" t="s">
         <v>211</v>
       </c>
-      <c r="F118" s="23" t="s">
+      <c r="F118" s="21" t="s">
         <v>369</v>
       </c>
-      <c r="G118" s="81" t="s">
+      <c r="G118" s="78" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="83">
+      <c r="A119" s="80">
         <v>46066</v>
       </c>
-      <c r="B119" s="23" t="s">
+      <c r="B119" s="21" t="s">
         <v>279</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D119" s="84">
+      <c r="D119" s="81">
         <v>4</v>
       </c>
-      <c r="E119" s="82" t="s">
+      <c r="E119" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="F119" s="86"/>
-      <c r="G119" s="20" t="s">
+      <c r="F119" s="83"/>
+      <c r="G119" s="19" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="83">
+      <c r="A120" s="80">
         <v>46066</v>
       </c>
-      <c r="B120" s="23" t="s">
+      <c r="B120" s="21" t="s">
         <v>279</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D120" s="85">
+      <c r="D120" s="82">
         <v>2</v>
       </c>
-      <c r="E120" s="82" t="s">
+      <c r="E120" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="F120" s="86"/>
-      <c r="G120" s="20" t="s">
+      <c r="F120" s="83"/>
+      <c r="G120" s="19" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="83" t="s">
+      <c r="A121" s="80" t="s">
         <v>382</v>
       </c>
-      <c r="B121" s="23" t="s">
+      <c r="B121" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D121" s="85">
+      <c r="D121" s="82">
         <v>1</v>
       </c>
-      <c r="E121" s="26" t="s">
+      <c r="E121" s="24" t="s">
         <v>212</v>
       </c>
       <c r="F121" s="17" t="s">
@@ -5351,19 +5619,19 @@
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="83" t="s">
+      <c r="A122" s="80" t="s">
         <v>382</v>
       </c>
-      <c r="B122" s="23" t="s">
+      <c r="B122" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D122" s="85">
+      <c r="D122" s="82">
         <v>0.5</v>
       </c>
-      <c r="E122" s="26" t="s">
+      <c r="E122" s="24" t="s">
         <v>212</v>
       </c>
       <c r="F122" s="17" t="s">
@@ -5374,19 +5642,19 @@
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="83" t="s">
+      <c r="A123" s="80" t="s">
         <v>382</v>
       </c>
-      <c r="B123" s="23" t="s">
+      <c r="B123" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D123" s="85">
+      <c r="D123" s="82">
         <v>1</v>
       </c>
-      <c r="E123" s="26" t="s">
+      <c r="E123" s="24" t="s">
         <v>212</v>
       </c>
       <c r="F123" s="17" t="s">
@@ -5397,19 +5665,19 @@
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="83" t="s">
+      <c r="A124" s="80" t="s">
         <v>384</v>
       </c>
-      <c r="B124" s="23" t="s">
+      <c r="B124" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D124" s="85">
+      <c r="D124" s="82">
         <v>0.75</v>
       </c>
-      <c r="E124" s="26" t="s">
+      <c r="E124" s="24" t="s">
         <v>212</v>
       </c>
       <c r="F124" s="17" t="s">
@@ -5420,19 +5688,19 @@
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="83" t="s">
+      <c r="A125" s="80" t="s">
         <v>384</v>
       </c>
-      <c r="B125" s="23" t="s">
+      <c r="B125" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D125" s="85">
+      <c r="D125" s="82">
         <v>1</v>
       </c>
-      <c r="E125" s="26" t="s">
+      <c r="E125" s="24" t="s">
         <v>212</v>
       </c>
       <c r="F125" s="17" t="s">
@@ -5443,19 +5711,19 @@
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="83" t="s">
+      <c r="A126" s="80" t="s">
         <v>384</v>
       </c>
-      <c r="B126" s="23" t="s">
+      <c r="B126" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D126" s="85">
+      <c r="D126" s="82">
         <v>0.75</v>
       </c>
-      <c r="E126" s="26" t="s">
+      <c r="E126" s="24" t="s">
         <v>212</v>
       </c>
       <c r="F126" s="17" t="s">
@@ -5466,19 +5734,19 @@
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="83" t="s">
+      <c r="A127" s="80" t="s">
         <v>385</v>
       </c>
-      <c r="B127" s="23" t="s">
+      <c r="B127" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D127" s="85">
+      <c r="D127" s="82">
         <v>0.5</v>
       </c>
-      <c r="E127" s="26" t="s">
+      <c r="E127" s="24" t="s">
         <v>212</v>
       </c>
       <c r="F127" s="17" t="s">
@@ -5489,19 +5757,19 @@
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="83" t="s">
+      <c r="A128" s="80" t="s">
         <v>385</v>
       </c>
-      <c r="B128" s="23" t="s">
+      <c r="B128" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D128" s="85">
+      <c r="D128" s="82">
         <v>0.5</v>
       </c>
-      <c r="E128" s="26" t="s">
+      <c r="E128" s="24" t="s">
         <v>212</v>
       </c>
       <c r="F128" s="17" t="s">
@@ -5512,19 +5780,19 @@
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="83" t="s">
+      <c r="A129" s="80" t="s">
         <v>385</v>
       </c>
-      <c r="B129" s="23" t="s">
+      <c r="B129" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D129" s="85">
+      <c r="D129" s="82">
         <v>0.5</v>
       </c>
-      <c r="E129" s="26" t="s">
+      <c r="E129" s="24" t="s">
         <v>212</v>
       </c>
       <c r="F129" s="17" t="s">
@@ -5535,19 +5803,19 @@
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="83" t="s">
+      <c r="A130" s="80" t="s">
         <v>385</v>
       </c>
-      <c r="B130" s="23" t="s">
+      <c r="B130" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D130" s="85">
+      <c r="D130" s="82">
         <v>0.25</v>
       </c>
-      <c r="E130" s="26" t="s">
+      <c r="E130" s="24" t="s">
         <v>212</v>
       </c>
       <c r="F130" s="17" t="s">
@@ -5558,19 +5826,19 @@
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="83" t="s">
+      <c r="A131" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="B131" s="23" t="s">
+      <c r="B131" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D131" s="85">
+      <c r="D131" s="82">
         <v>0.5</v>
       </c>
-      <c r="E131" s="87" t="s">
+      <c r="E131" s="84" t="s">
         <v>234</v>
       </c>
       <c r="F131" s="17" t="s">
@@ -5581,19 +5849,19 @@
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="83" t="s">
+      <c r="A132" s="80" t="s">
         <v>386</v>
       </c>
-      <c r="B132" s="23" t="s">
+      <c r="B132" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D132" s="85">
+      <c r="D132" s="82">
         <v>1.5</v>
       </c>
-      <c r="E132" s="87" t="s">
+      <c r="E132" s="84" t="s">
         <v>234</v>
       </c>
       <c r="F132" s="17" t="s">
@@ -5604,19 +5872,19 @@
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="83" t="s">
+      <c r="A133" s="80" t="s">
         <v>387</v>
       </c>
-      <c r="B133" s="23" t="s">
+      <c r="B133" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D133" s="85">
+      <c r="D133" s="82">
         <v>1.5</v>
       </c>
-      <c r="E133" s="87" t="s">
+      <c r="E133" s="84" t="s">
         <v>234</v>
       </c>
       <c r="F133" s="17" t="s">
@@ -5627,19 +5895,19 @@
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" s="83" t="s">
+      <c r="A134" s="80" t="s">
         <v>387</v>
       </c>
-      <c r="B134" s="23" t="s">
+      <c r="B134" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D134" s="85">
+      <c r="D134" s="82">
         <v>1</v>
       </c>
-      <c r="E134" s="87" t="s">
+      <c r="E134" s="84" t="s">
         <v>234</v>
       </c>
       <c r="F134" s="17" t="s">
@@ -5650,19 +5918,19 @@
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="83" t="s">
+      <c r="A135" s="80" t="s">
         <v>387</v>
       </c>
-      <c r="B135" s="23" t="s">
+      <c r="B135" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D135" s="85">
+      <c r="D135" s="82">
         <v>1</v>
       </c>
-      <c r="E135" s="87" t="s">
+      <c r="E135" s="84" t="s">
         <v>234</v>
       </c>
       <c r="F135" s="17" t="s">
@@ -5673,19 +5941,19 @@
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" s="83" t="s">
+      <c r="A136" s="80" t="s">
         <v>388</v>
       </c>
-      <c r="B136" s="23" t="s">
+      <c r="B136" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D136" s="85">
+      <c r="D136" s="82">
         <v>0.75</v>
       </c>
-      <c r="E136" s="87" t="s">
+      <c r="E136" s="84" t="s">
         <v>234</v>
       </c>
       <c r="F136" s="17" t="s">
@@ -5696,19 +5964,19 @@
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="83" t="s">
+      <c r="A137" s="80" t="s">
         <v>388</v>
       </c>
-      <c r="B137" s="23" t="s">
+      <c r="B137" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D137" s="85">
+      <c r="D137" s="82">
         <v>0.75</v>
       </c>
-      <c r="E137" s="87" t="s">
+      <c r="E137" s="84" t="s">
         <v>234</v>
       </c>
       <c r="F137" s="17" t="s">
@@ -5719,19 +5987,19 @@
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="83" t="s">
+      <c r="A138" s="80" t="s">
         <v>388</v>
       </c>
-      <c r="B138" s="23" t="s">
+      <c r="B138" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D138" s="85">
+      <c r="D138" s="82">
         <v>0.5</v>
       </c>
-      <c r="E138" s="87" t="s">
+      <c r="E138" s="84" t="s">
         <v>234</v>
       </c>
       <c r="F138" s="17" t="s">
@@ -5742,19 +6010,19 @@
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="83" t="s">
+      <c r="A139" s="80" t="s">
         <v>388</v>
       </c>
-      <c r="B139" s="23" t="s">
+      <c r="B139" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D139" s="85">
+      <c r="D139" s="82">
         <v>0.25</v>
       </c>
-      <c r="E139" s="87" t="s">
+      <c r="E139" s="84" t="s">
         <v>234</v>
       </c>
       <c r="F139" s="17" t="s">
@@ -5765,19 +6033,19 @@
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" s="83" t="s">
+      <c r="A140" s="80" t="s">
         <v>388</v>
       </c>
-      <c r="B140" s="23" t="s">
+      <c r="B140" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D140" s="85">
+      <c r="D140" s="82">
         <v>0.25</v>
       </c>
-      <c r="E140" s="87" t="s">
+      <c r="E140" s="84" t="s">
         <v>234</v>
       </c>
       <c r="F140" s="17" t="s">
@@ -5788,19 +6056,19 @@
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141" s="83" t="s">
+      <c r="A141" s="80" t="s">
         <v>388</v>
       </c>
-      <c r="B141" s="23" t="s">
+      <c r="B141" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D141" s="85">
+      <c r="D141" s="82">
         <v>0.75</v>
       </c>
-      <c r="E141" s="24" t="s">
+      <c r="E141" s="22" t="s">
         <v>17</v>
       </c>
       <c r="F141" s="17"/>
@@ -5809,19 +6077,19 @@
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" s="83" t="s">
+      <c r="A142" s="80" t="s">
         <v>388</v>
       </c>
-      <c r="B142" s="23" t="s">
+      <c r="B142" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D142" s="85">
+      <c r="D142" s="82">
         <v>0.75</v>
       </c>
-      <c r="E142" s="24" t="s">
+      <c r="E142" s="22" t="s">
         <v>37</v>
       </c>
       <c r="F142" s="17"/>
@@ -5830,19 +6098,19 @@
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" s="89">
+      <c r="A143" s="86">
         <v>46084</v>
       </c>
-      <c r="B143" s="23" t="s">
+      <c r="B143" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D143" s="92">
+      <c r="D143" s="89">
         <v>1</v>
       </c>
-      <c r="E143" s="24" t="s">
+      <c r="E143" s="22" t="s">
         <v>17</v>
       </c>
       <c r="F143" s="17"/>
@@ -5851,19 +6119,19 @@
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" s="89">
+      <c r="A144" s="86">
         <v>46084</v>
       </c>
-      <c r="B144" s="23" t="s">
+      <c r="B144" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D144" s="92">
+      <c r="D144" s="89">
         <v>0.75</v>
       </c>
-      <c r="E144" s="24" t="s">
+      <c r="E144" s="22" t="s">
         <v>17</v>
       </c>
       <c r="F144" s="17"/>
@@ -5872,19 +6140,19 @@
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" s="89">
+      <c r="A145" s="86">
         <v>46085</v>
       </c>
-      <c r="B145" s="23" t="s">
+      <c r="B145" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D145" s="92">
+      <c r="D145" s="89">
         <v>1</v>
       </c>
-      <c r="E145" s="24" t="s">
+      <c r="E145" s="22" t="s">
         <v>17</v>
       </c>
       <c r="F145" s="17"/>
@@ -5893,19 +6161,19 @@
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146" s="89">
+      <c r="A146" s="86">
         <v>46085</v>
       </c>
-      <c r="B146" s="23" t="s">
+      <c r="B146" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D146" s="92">
+      <c r="D146" s="89">
         <v>0.75</v>
       </c>
-      <c r="E146" s="24" t="s">
+      <c r="E146" s="22" t="s">
         <v>17</v>
       </c>
       <c r="F146" s="17"/>
@@ -5914,19 +6182,19 @@
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="89">
+      <c r="A147" s="86">
         <v>46086</v>
       </c>
-      <c r="B147" s="23" t="s">
+      <c r="B147" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D147" s="92">
+      <c r="D147" s="89">
         <v>1</v>
       </c>
-      <c r="E147" s="24" t="s">
+      <c r="E147" s="22" t="s">
         <v>17</v>
       </c>
       <c r="F147" s="17"/>
@@ -5935,19 +6203,19 @@
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148" s="89">
+      <c r="A148" s="86">
         <v>46086</v>
       </c>
-      <c r="B148" s="23" t="s">
+      <c r="B148" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D148" s="92">
+      <c r="D148" s="89">
         <v>0.5</v>
       </c>
-      <c r="E148" s="24" t="s">
+      <c r="E148" s="22" t="s">
         <v>17</v>
       </c>
       <c r="F148" s="17"/>
@@ -5956,19 +6224,19 @@
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149" s="89">
+      <c r="A149" s="86">
         <v>46087</v>
       </c>
-      <c r="B149" s="23" t="s">
+      <c r="B149" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D149" s="92">
+      <c r="D149" s="89">
         <v>0.5</v>
       </c>
-      <c r="E149" s="24" t="s">
+      <c r="E149" s="22" t="s">
         <v>17</v>
       </c>
       <c r="F149" s="17"/>
@@ -5977,19 +6245,19 @@
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150" s="89">
+      <c r="A150" s="86">
         <v>46088</v>
       </c>
-      <c r="B150" s="23" t="s">
+      <c r="B150" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D150" s="92">
+      <c r="D150" s="89">
         <v>1</v>
       </c>
-      <c r="E150" s="24" t="s">
+      <c r="E150" s="22" t="s">
         <v>234</v>
       </c>
       <c r="F150" s="17" t="s">
@@ -6000,19 +6268,19 @@
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151" s="89">
+      <c r="A151" s="86">
         <v>46088</v>
       </c>
-      <c r="B151" s="23" t="s">
+      <c r="B151" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D151" s="92">
+      <c r="D151" s="89">
         <v>0.75</v>
       </c>
-      <c r="E151" s="24" t="s">
+      <c r="E151" s="22" t="s">
         <v>234</v>
       </c>
       <c r="F151" s="17" t="s">
@@ -6023,19 +6291,19 @@
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152" s="89">
+      <c r="A152" s="86">
         <v>46089</v>
       </c>
-      <c r="B152" s="23" t="s">
+      <c r="B152" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D152" s="92">
+      <c r="D152" s="89">
         <v>0.75</v>
       </c>
-      <c r="E152" s="24" t="s">
+      <c r="E152" s="22" t="s">
         <v>234</v>
       </c>
       <c r="F152" s="17" t="s">
@@ -6046,19 +6314,19 @@
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A153" s="89">
+      <c r="A153" s="86">
         <v>46089</v>
       </c>
-      <c r="B153" s="23" t="s">
+      <c r="B153" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D153" s="92">
+      <c r="D153" s="89">
         <v>0.5</v>
       </c>
-      <c r="E153" s="24" t="s">
+      <c r="E153" s="22" t="s">
         <v>234</v>
       </c>
       <c r="F153" s="17" t="s">
@@ -6069,19 +6337,19 @@
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A154" s="89">
+      <c r="A154" s="86">
         <v>46089</v>
       </c>
-      <c r="B154" s="23" t="s">
+      <c r="B154" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D154" s="92">
+      <c r="D154" s="89">
         <v>0.5</v>
       </c>
-      <c r="E154" s="24" t="s">
+      <c r="E154" s="22" t="s">
         <v>234</v>
       </c>
       <c r="F154" s="17" t="s">
@@ -6092,19 +6360,19 @@
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A155" s="89">
+      <c r="A155" s="86">
         <v>46089</v>
       </c>
-      <c r="B155" s="23" t="s">
+      <c r="B155" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D155" s="92">
+      <c r="D155" s="89">
         <v>1.5</v>
       </c>
-      <c r="E155" s="24" t="s">
+      <c r="E155" s="22" t="s">
         <v>413</v>
       </c>
       <c r="F155" s="17" t="s">
@@ -6115,19 +6383,19 @@
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A156" s="89">
+      <c r="A156" s="86">
         <v>46090</v>
       </c>
-      <c r="B156" s="23" t="s">
+      <c r="B156" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D156" s="92">
+      <c r="D156" s="89">
         <v>1.5</v>
       </c>
-      <c r="E156" s="24" t="s">
+      <c r="E156" s="22" t="s">
         <v>413</v>
       </c>
       <c r="F156" s="17" t="s">
@@ -6138,19 +6406,19 @@
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A157" s="89">
+      <c r="A157" s="86">
         <v>46090</v>
       </c>
-      <c r="B157" s="23" t="s">
+      <c r="B157" s="21" t="s">
         <v>383</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D157" s="92">
+      <c r="D157" s="89">
         <v>1</v>
       </c>
-      <c r="E157" s="24" t="s">
+      <c r="E157" s="22" t="s">
         <v>413</v>
       </c>
       <c r="F157" s="17" t="s">
@@ -6161,7 +6429,7 @@
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A158" s="90">
+      <c r="A158" s="87">
         <v>46090</v>
       </c>
       <c r="B158" s="1" t="s">
@@ -6173,18 +6441,18 @@
       <c r="D158" s="4">
         <v>0.5</v>
       </c>
-      <c r="E158" s="24" t="s">
+      <c r="E158" s="22" t="s">
         <v>413</v>
       </c>
       <c r="F158" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="G158" s="20" t="s">
+      <c r="G158" s="19" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A159" s="90">
+      <c r="A159" s="87">
         <v>46090</v>
       </c>
       <c r="B159" s="1" t="s">
@@ -6196,18 +6464,18 @@
       <c r="D159" s="4">
         <v>0.25</v>
       </c>
-      <c r="E159" s="24" t="s">
+      <c r="E159" s="22" t="s">
         <v>413</v>
       </c>
       <c r="F159" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="G159" s="20" t="s">
+      <c r="G159" s="19" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A160" s="90">
+      <c r="A160" s="87">
         <v>46090</v>
       </c>
       <c r="B160" s="1" t="s">
@@ -6219,18 +6487,18 @@
       <c r="D160" s="4">
         <v>1</v>
       </c>
-      <c r="E160" s="24" t="s">
+      <c r="E160" s="22" t="s">
         <v>214</v>
       </c>
       <c r="F160" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="G160" s="20" t="s">
+      <c r="G160" s="19" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A161" s="90">
+      <c r="A161" s="87">
         <v>46090</v>
       </c>
       <c r="B161" s="1" t="s">
@@ -6242,18 +6510,18 @@
       <c r="D161" s="4">
         <v>1.5</v>
       </c>
-      <c r="E161" s="24" t="s">
+      <c r="E161" s="22" t="s">
         <v>214</v>
       </c>
       <c r="F161" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="G161" s="20" t="s">
+      <c r="G161" s="19" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A162" s="90">
+      <c r="A162" s="87">
         <v>46090</v>
       </c>
       <c r="B162" s="1" t="s">
@@ -6265,1069 +6533,1690 @@
       <c r="D162" s="4">
         <v>0.75</v>
       </c>
-      <c r="E162" s="24" t="s">
+      <c r="E162" s="22" t="s">
         <v>214</v>
       </c>
       <c r="F162" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="G162" s="20" t="s">
+      <c r="G162" s="19" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A163" s="91">
+      <c r="A163" s="88">
         <v>46090</v>
       </c>
-      <c r="B163" s="88" t="s">
+      <c r="B163" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C163" s="88" t="s">
+      <c r="C163" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="D163" s="94">
+      <c r="D163" s="91">
         <v>0.25</v>
       </c>
-      <c r="E163" s="24" t="s">
+      <c r="E163" s="22" t="s">
         <v>214</v>
       </c>
       <c r="F163" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="G163" s="20" t="s">
+      <c r="G163" s="19" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A164" s="91">
+      <c r="A164" s="88">
         <v>46090</v>
       </c>
-      <c r="B164" s="88" t="s">
+      <c r="B164" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C164" s="88" t="s">
+      <c r="C164" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D164" s="94">
+      <c r="D164" s="91">
         <v>0.75</v>
       </c>
-      <c r="E164" s="24" t="s">
+      <c r="E164" s="22" t="s">
         <v>37</v>
       </c>
       <c r="F164" s="17"/>
-      <c r="G164" s="20" t="s">
+      <c r="G164" s="19" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A165" s="91">
+      <c r="A165" s="88">
         <v>46092</v>
       </c>
-      <c r="B165" s="88" t="s">
+      <c r="B165" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C165" s="88" t="s">
+      <c r="C165" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="D165" s="94">
+      <c r="D165" s="91">
         <v>1</v>
       </c>
-      <c r="E165" s="24" t="s">
+      <c r="E165" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F165" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G165" s="20" t="s">
+      <c r="G165" s="19" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A166" s="91">
+      <c r="A166" s="88">
         <v>46092</v>
       </c>
-      <c r="B166" s="88" t="s">
+      <c r="B166" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C166" s="88" t="s">
+      <c r="C166" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D166" s="94">
+      <c r="D166" s="91">
         <v>0.75</v>
       </c>
-      <c r="E166" s="24" t="s">
+      <c r="E166" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F166" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G166" s="20" t="s">
+      <c r="G166" s="19" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A167" s="91">
+      <c r="A167" s="88">
         <v>46092</v>
       </c>
-      <c r="B167" s="88" t="s">
+      <c r="B167" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C167" s="88" t="s">
+      <c r="C167" s="85" t="s">
         <v>442</v>
       </c>
-      <c r="D167" s="94">
+      <c r="D167" s="91">
         <v>1.25</v>
       </c>
-      <c r="E167" s="24" t="s">
+      <c r="E167" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F167" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G167" s="20" t="s">
+      <c r="G167" s="19" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A168" s="91">
+      <c r="A168" s="88">
         <v>46092</v>
       </c>
-      <c r="B168" s="88" t="s">
+      <c r="B168" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C168" s="88" t="s">
+      <c r="C168" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="D168" s="94">
+      <c r="D168" s="91">
         <v>1</v>
       </c>
-      <c r="E168" s="24" t="s">
+      <c r="E168" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F168" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G168" s="20" t="s">
+      <c r="G168" s="19" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A169" s="91">
+      <c r="A169" s="88">
         <v>46094</v>
       </c>
-      <c r="B169" s="88" t="s">
+      <c r="B169" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C169" s="88" t="s">
+      <c r="C169" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D169" s="94">
+      <c r="D169" s="91">
         <v>0.75</v>
       </c>
-      <c r="E169" s="24" t="s">
+      <c r="E169" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F169" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G169" s="20" t="s">
+      <c r="G169" s="19" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A170" s="91">
+      <c r="A170" s="88">
         <v>46094</v>
       </c>
-      <c r="B170" s="88" t="s">
+      <c r="B170" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C170" s="88" t="s">
+      <c r="C170" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="D170" s="94">
+      <c r="D170" s="91">
         <v>1</v>
       </c>
-      <c r="E170" s="24" t="s">
+      <c r="E170" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F170" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G170" s="20" t="s">
+      <c r="G170" s="19" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A171" s="91">
+      <c r="A171" s="88">
         <v>46094</v>
       </c>
-      <c r="B171" s="88" t="s">
+      <c r="B171" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C171" s="88" t="s">
+      <c r="C171" s="85" t="s">
         <v>442</v>
       </c>
-      <c r="D171" s="94">
+      <c r="D171" s="91">
         <v>1.25</v>
       </c>
-      <c r="E171" s="24" t="s">
+      <c r="E171" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F171" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G171" s="20" t="s">
+      <c r="G171" s="19" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A172" s="91">
+      <c r="A172" s="88">
         <v>46094</v>
       </c>
-      <c r="B172" s="88" t="s">
+      <c r="B172" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C172" s="88" t="s">
+      <c r="C172" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D172" s="94">
+      <c r="D172" s="91">
         <v>0.75</v>
       </c>
-      <c r="E172" s="24" t="s">
+      <c r="E172" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F172" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G172" s="20" t="s">
+      <c r="G172" s="19" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A173" s="91">
+      <c r="A173" s="88">
         <v>46096</v>
       </c>
-      <c r="B173" s="88" t="s">
+      <c r="B173" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C173" s="88" t="s">
+      <c r="C173" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D173" s="94">
+      <c r="D173" s="91">
         <v>0.75</v>
       </c>
-      <c r="E173" s="24" t="s">
+      <c r="E173" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F173" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G173" s="20" t="s">
+      <c r="G173" s="19" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A174" s="91">
+      <c r="A174" s="88">
         <v>46096</v>
       </c>
-      <c r="B174" s="88" t="s">
+      <c r="B174" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C174" s="88" t="s">
+      <c r="C174" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D174" s="94">
+      <c r="D174" s="91">
         <v>0.5</v>
       </c>
-      <c r="E174" s="24" t="s">
+      <c r="E174" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F174" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G174" s="20" t="s">
+      <c r="G174" s="19" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A175" s="91">
+      <c r="A175" s="88">
         <v>46096</v>
       </c>
-      <c r="B175" s="88" t="s">
+      <c r="B175" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C175" s="88" t="s">
+      <c r="C175" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D175" s="94">
+      <c r="D175" s="91">
         <v>0.75</v>
       </c>
-      <c r="E175" s="24" t="s">
+      <c r="E175" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F175" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G175" s="20" t="s">
+      <c r="G175" s="19" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A176" s="91">
+      <c r="A176" s="88">
         <v>46096</v>
       </c>
-      <c r="B176" s="88" t="s">
+      <c r="B176" s="85" t="s">
         <v>383</v>
       </c>
-      <c r="C176" s="88" t="s">
+      <c r="C176" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D176" s="94">
+      <c r="D176" s="91">
         <v>0.5</v>
       </c>
-      <c r="E176" s="24" t="s">
+      <c r="E176" s="22" t="s">
         <v>215</v>
       </c>
       <c r="F176" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="G176" s="20" t="s">
+      <c r="G176" s="19" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A177" s="91">
+      <c r="A177" s="88">
         <v>46097</v>
       </c>
-      <c r="B177" s="88" t="s">
+      <c r="B177" s="85" t="s">
         <v>453</v>
       </c>
-      <c r="C177" s="88" t="s">
+      <c r="C177" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="D177" s="94">
+      <c r="D177" s="91">
         <v>1</v>
       </c>
-      <c r="E177" s="24" t="s">
+      <c r="E177" s="22" t="s">
         <v>216</v>
       </c>
       <c r="F177" s="17" t="s">
         <v>463</v>
       </c>
-      <c r="G177" s="20" t="s">
+      <c r="G177" s="19" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" s="91">
+      <c r="A178" s="88">
         <v>46097</v>
       </c>
-      <c r="B178" s="88" t="s">
+      <c r="B178" s="85" t="s">
         <v>453</v>
       </c>
-      <c r="C178" s="88" t="s">
+      <c r="C178" s="85" t="s">
         <v>442</v>
       </c>
-      <c r="D178" s="94">
+      <c r="D178" s="91">
         <v>1.25</v>
       </c>
-      <c r="E178" s="24" t="s">
+      <c r="E178" s="22" t="s">
         <v>216</v>
       </c>
       <c r="F178" s="17" t="s">
         <v>463</v>
       </c>
-      <c r="G178" s="20" t="s">
+      <c r="G178" s="19" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A179" s="91">
+      <c r="A179" s="88">
         <v>46097</v>
       </c>
-      <c r="B179" s="88" t="s">
+      <c r="B179" s="85" t="s">
         <v>453</v>
       </c>
-      <c r="C179" s="88" t="s">
+      <c r="C179" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D179" s="94">
+      <c r="D179" s="91">
         <v>0.5</v>
       </c>
-      <c r="E179" s="24" t="s">
+      <c r="E179" s="22" t="s">
         <v>216</v>
       </c>
       <c r="F179" s="17" t="s">
         <v>463</v>
       </c>
-      <c r="G179" s="20" t="s">
+      <c r="G179" s="19" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" s="91">
+      <c r="A180" s="88">
         <v>46097</v>
       </c>
-      <c r="B180" s="88" t="s">
+      <c r="B180" s="85" t="s">
         <v>453</v>
       </c>
-      <c r="C180" s="88" t="s">
+      <c r="C180" s="85" t="s">
         <v>427</v>
       </c>
-      <c r="D180" s="94">
+      <c r="D180" s="91">
         <v>1.5</v>
       </c>
-      <c r="E180" s="24" t="s">
+      <c r="E180" s="22" t="s">
         <v>217</v>
       </c>
       <c r="F180" s="17" t="s">
         <v>464</v>
       </c>
-      <c r="G180" s="20" t="s">
+      <c r="G180" s="19" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A181" s="91">
+      <c r="A181" s="88">
         <v>46097</v>
       </c>
-      <c r="B181" s="88" t="s">
+      <c r="B181" s="85" t="s">
         <v>453</v>
       </c>
-      <c r="C181" s="88" t="s">
+      <c r="C181" s="85" t="s">
         <v>458</v>
       </c>
-      <c r="D181" s="94">
+      <c r="D181" s="91">
         <v>1.75</v>
       </c>
-      <c r="E181" s="24" t="s">
+      <c r="E181" s="22" t="s">
         <v>217</v>
       </c>
       <c r="F181" s="17" t="s">
         <v>464</v>
       </c>
-      <c r="G181" s="20" t="s">
+      <c r="G181" s="19" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A182" s="91">
+      <c r="A182" s="88">
         <v>46097</v>
       </c>
-      <c r="B182" s="88" t="s">
+      <c r="B182" s="85" t="s">
         <v>453</v>
       </c>
-      <c r="C182" s="88" t="s">
+      <c r="C182" s="85" t="s">
         <v>427</v>
       </c>
-      <c r="D182" s="94">
+      <c r="D182" s="91">
         <v>1.5</v>
       </c>
-      <c r="E182" s="24" t="s">
+      <c r="E182" s="22" t="s">
         <v>217</v>
       </c>
       <c r="F182" s="17" t="s">
         <v>464</v>
       </c>
-      <c r="G182" s="20" t="s">
+      <c r="G182" s="19" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A183" s="91">
+      <c r="A183" s="88">
         <v>46097</v>
       </c>
-      <c r="B183" s="88" t="s">
+      <c r="B183" s="85" t="s">
         <v>453</v>
       </c>
-      <c r="C183" s="88" t="s">
+      <c r="C183" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D183" s="94">
+      <c r="D183" s="91">
         <v>0.5</v>
       </c>
-      <c r="E183" s="24" t="s">
+      <c r="E183" s="22" t="s">
         <v>217</v>
       </c>
       <c r="F183" s="17" t="s">
         <v>464</v>
       </c>
-      <c r="G183" s="20" t="s">
+      <c r="G183" s="19" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A184" s="91">
+      <c r="A184" s="88">
         <v>46097</v>
       </c>
-      <c r="B184" s="88" t="s">
+      <c r="B184" s="85" t="s">
         <v>453</v>
       </c>
-      <c r="C184" s="88" t="s">
+      <c r="C184" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D184" s="94">
+      <c r="D184" s="91">
         <v>0.75</v>
       </c>
-      <c r="E184" s="24" t="s">
+      <c r="E184" s="22" t="s">
         <v>37</v>
       </c>
       <c r="F184" s="17"/>
-      <c r="G184" s="20" t="s">
+      <c r="G184" s="19" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A185" s="91">
+      <c r="A185" s="88">
         <v>46098</v>
       </c>
-      <c r="B185" s="88" t="s">
+      <c r="B185" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C185" s="88" t="s">
+      <c r="C185" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="D185" s="94">
+      <c r="D185" s="91">
         <v>1</v>
       </c>
-      <c r="E185" s="111" t="s">
+      <c r="E185" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F185" s="17" t="s">
         <v>468</v>
       </c>
-      <c r="G185" s="20" t="s">
+      <c r="G185" s="19" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A186" s="91">
+      <c r="A186" s="88">
         <v>46098</v>
       </c>
-      <c r="B186" s="88" t="s">
+      <c r="B186" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C186" s="88" t="s">
+      <c r="C186" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D186" s="94">
+      <c r="D186" s="91">
         <v>0.75</v>
       </c>
-      <c r="E186" s="111" t="s">
+      <c r="E186" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F186" s="17" t="s">
         <v>468</v>
       </c>
-      <c r="G186" s="20" t="s">
+      <c r="G186" s="19" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A187" s="91">
+      <c r="A187" s="88">
         <v>46098</v>
       </c>
-      <c r="B187" s="88" t="s">
+      <c r="B187" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C187" s="88" t="s">
+      <c r="C187" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D187" s="94">
+      <c r="D187" s="91">
         <v>0.5</v>
       </c>
-      <c r="E187" s="111" t="s">
+      <c r="E187" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F187" s="17" t="s">
         <v>468</v>
       </c>
-      <c r="G187" s="20" t="s">
+      <c r="G187" s="19" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A188" s="91">
+      <c r="A188" s="88">
         <v>46100</v>
       </c>
-      <c r="B188" s="88" t="s">
+      <c r="B188" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C188" s="88" t="s">
+      <c r="C188" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="D188" s="94">
+      <c r="D188" s="91">
         <v>1</v>
       </c>
-      <c r="E188" s="111" t="s">
+      <c r="E188" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F188" s="17" t="s">
         <v>472</v>
       </c>
-      <c r="G188" s="20" t="s">
+      <c r="G188" s="19" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A189" s="91">
+      <c r="A189" s="88">
         <v>46100</v>
       </c>
-      <c r="B189" s="88" t="s">
+      <c r="B189" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C189" s="88" t="s">
+      <c r="C189" s="85" t="s">
         <v>442</v>
       </c>
-      <c r="D189" s="94">
+      <c r="D189" s="91">
         <v>1.25</v>
       </c>
-      <c r="E189" s="111" t="s">
+      <c r="E189" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F189" s="17" t="s">
         <v>472</v>
       </c>
-      <c r="G189" s="20" t="s">
+      <c r="G189" s="19" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A190" s="91">
+      <c r="A190" s="88">
         <v>46100</v>
       </c>
-      <c r="B190" s="88" t="s">
+      <c r="B190" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C190" s="88" t="s">
+      <c r="C190" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D190" s="94">
+      <c r="D190" s="91">
         <v>0.5</v>
       </c>
-      <c r="E190" s="111" t="s">
+      <c r="E190" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F190" s="17" t="s">
         <v>475</v>
       </c>
-      <c r="G190" s="20" t="s">
+      <c r="G190" s="19" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A191" s="91">
+      <c r="A191" s="88">
         <v>46102</v>
       </c>
-      <c r="B191" s="88" t="s">
+      <c r="B191" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C191" s="88" t="s">
+      <c r="C191" s="85" t="s">
         <v>427</v>
       </c>
-      <c r="D191" s="94">
+      <c r="D191" s="91">
         <v>1.5</v>
       </c>
-      <c r="E191" s="111" t="s">
+      <c r="E191" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F191" s="17" t="s">
         <v>475</v>
       </c>
-      <c r="G191" s="20" t="s">
+      <c r="G191" s="19" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A192" s="91">
+      <c r="A192" s="88">
         <v>46102</v>
       </c>
-      <c r="B192" s="88" t="s">
+      <c r="B192" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C192" s="88" t="s">
+      <c r="C192" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D192" s="94">
+      <c r="D192" s="91">
         <v>0.75</v>
       </c>
-      <c r="E192" s="111" t="s">
+      <c r="E192" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F192" s="17" t="s">
         <v>478</v>
       </c>
-      <c r="G192" s="20" t="s">
+      <c r="G192" s="19" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A193" s="91">
+      <c r="A193" s="88">
         <v>46102</v>
       </c>
-      <c r="B193" s="88" t="s">
+      <c r="B193" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C193" s="88" t="s">
+      <c r="C193" s="85" t="s">
         <v>442</v>
       </c>
-      <c r="D193" s="94">
+      <c r="D193" s="91">
         <v>1.25</v>
       </c>
-      <c r="E193" s="111" t="s">
+      <c r="E193" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F193" s="17" t="s">
         <v>478</v>
       </c>
-      <c r="G193" s="20" t="s">
+      <c r="G193" s="19" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A194" s="91">
+      <c r="A194" s="88">
         <v>46102</v>
       </c>
-      <c r="B194" s="88" t="s">
+      <c r="B194" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C194" s="88" t="s">
+      <c r="C194" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D194" s="94">
+      <c r="D194" s="91">
         <v>0.75</v>
       </c>
-      <c r="E194" s="111" t="s">
+      <c r="E194" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F194" s="17" t="s">
         <v>481</v>
       </c>
-      <c r="G194" s="20" t="s">
+      <c r="G194" s="19" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A195" s="91">
+      <c r="A195" s="88">
         <v>46102</v>
       </c>
-      <c r="B195" s="88" t="s">
+      <c r="B195" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C195" s="88" t="s">
+      <c r="C195" s="85" t="s">
         <v>442</v>
       </c>
-      <c r="D195" s="94">
+      <c r="D195" s="91">
         <v>1.25</v>
       </c>
-      <c r="E195" s="111" t="s">
+      <c r="E195" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F195" s="17" t="s">
         <v>481</v>
       </c>
-      <c r="G195" s="20" t="s">
+      <c r="G195" s="19" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A196" s="91">
+      <c r="A196" s="88">
         <v>46103</v>
       </c>
-      <c r="B196" s="88" t="s">
+      <c r="B196" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C196" s="88" t="s">
+      <c r="C196" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D196" s="94">
+      <c r="D196" s="91">
         <v>0.75</v>
       </c>
-      <c r="E196" s="111" t="s">
+      <c r="E196" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F196" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="G196" s="20" t="s">
+      <c r="G196" s="19" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A197" s="91">
+      <c r="A197" s="88">
         <v>46103</v>
       </c>
-      <c r="B197" s="88" t="s">
+      <c r="B197" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C197" s="88" t="s">
+      <c r="C197" s="85" t="s">
         <v>442</v>
       </c>
-      <c r="D197" s="94">
+      <c r="D197" s="91">
         <v>1.25</v>
       </c>
-      <c r="E197" s="111" t="s">
+      <c r="E197" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F197" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="G197" s="20" t="s">
+      <c r="G197" s="19" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A198" s="91">
+      <c r="A198" s="88">
         <v>46104</v>
       </c>
-      <c r="B198" s="88" t="s">
+      <c r="B198" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C198" s="88" t="s">
+      <c r="C198" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D198" s="94">
+      <c r="D198" s="91">
         <v>0.75</v>
       </c>
-      <c r="E198" s="111" t="s">
+      <c r="E198" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F198" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="G198" s="20" t="s">
+      <c r="G198" s="19" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A199" s="91">
+      <c r="A199" s="88">
         <v>46104</v>
       </c>
-      <c r="B199" s="88" t="s">
+      <c r="B199" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C199" s="88" t="s">
+      <c r="C199" s="85" t="s">
         <v>442</v>
       </c>
-      <c r="D199" s="94">
+      <c r="D199" s="91">
         <v>1.25</v>
       </c>
-      <c r="E199" s="111" t="s">
+      <c r="E199" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F199" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="G199" s="20" t="s">
+      <c r="G199" s="19" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A200" s="91">
+      <c r="A200" s="88">
         <v>46104</v>
       </c>
-      <c r="B200" s="88" t="s">
+      <c r="B200" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C200" s="88" t="s">
+      <c r="C200" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D200" s="94">
+      <c r="D200" s="91">
         <v>0.75</v>
       </c>
-      <c r="E200" s="111" t="s">
+      <c r="E200" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F200" s="17" t="s">
         <v>490</v>
       </c>
-      <c r="G200" s="20" t="s">
+      <c r="G200" s="19" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A201" s="91">
+      <c r="A201" s="88">
         <v>46104</v>
       </c>
-      <c r="B201" s="88" t="s">
+      <c r="B201" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C201" s="88" t="s">
+      <c r="C201" s="85" t="s">
         <v>427</v>
       </c>
-      <c r="D201" s="94">
+      <c r="D201" s="91">
         <v>1.5</v>
       </c>
-      <c r="E201" s="111" t="s">
+      <c r="E201" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F201" s="17" t="s">
         <v>490</v>
       </c>
-      <c r="G201" s="20" t="s">
+      <c r="G201" s="19" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A202" s="91">
+      <c r="A202" s="88">
         <v>46104</v>
       </c>
-      <c r="B202" s="88" t="s">
+      <c r="B202" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C202" s="88" t="s">
+      <c r="C202" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D202" s="94">
+      <c r="D202" s="91">
         <v>0.75</v>
       </c>
-      <c r="E202" s="111" t="s">
+      <c r="E202" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F202" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="G202" s="20" t="s">
+      <c r="G202" s="19" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A203" s="91">
+      <c r="A203" s="88">
         <v>46104</v>
       </c>
-      <c r="B203" s="88" t="s">
+      <c r="B203" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C203" s="88" t="s">
+      <c r="C203" s="85" t="s">
         <v>427</v>
       </c>
-      <c r="D203" s="94">
+      <c r="D203" s="91">
         <v>1.5</v>
       </c>
-      <c r="E203" s="111" t="s">
+      <c r="E203" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F203" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="G203" s="20" t="s">
+      <c r="G203" s="19" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A204" s="91">
+      <c r="A204" s="88">
         <v>46104</v>
       </c>
-      <c r="B204" s="88" t="s">
+      <c r="B204" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C204" s="88" t="s">
+      <c r="C204" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="D204" s="94">
+      <c r="D204" s="91">
         <v>0.75</v>
       </c>
-      <c r="E204" s="111" t="s">
+      <c r="E204" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F204" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="G204" s="20" t="s">
+      <c r="G204" s="19" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A205" s="91">
+      <c r="A205" s="88">
         <v>46104</v>
       </c>
-      <c r="B205" s="88" t="s">
+      <c r="B205" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C205" s="88" t="s">
+      <c r="C205" s="85" t="s">
         <v>442</v>
       </c>
-      <c r="D205" s="94">
+      <c r="D205" s="91">
         <v>1.25</v>
       </c>
-      <c r="E205" s="111" t="s">
+      <c r="E205" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F205" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="G205" s="20" t="s">
+      <c r="G205" s="19" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A206" s="91">
+      <c r="A206" s="88">
         <v>46104</v>
       </c>
-      <c r="B206" s="88" t="s">
+      <c r="B206" s="85" t="s">
         <v>466</v>
       </c>
-      <c r="C206" s="88" t="s">
+      <c r="C206" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D206" s="94">
+      <c r="D206" s="91">
         <v>0.5</v>
       </c>
-      <c r="E206" s="111" t="s">
+      <c r="E206" s="92" t="s">
         <v>467</v>
       </c>
       <c r="F206" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="G206" s="20" t="s">
+      <c r="G206" s="19" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A207" s="91">
+      <c r="A207" s="108">
         <v>46104</v>
       </c>
-      <c r="B207" s="88" t="s">
+      <c r="B207" s="109" t="s">
         <v>466</v>
       </c>
-      <c r="C207" s="88" t="s">
+      <c r="C207" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="D207" s="94">
+      <c r="D207" s="110">
         <v>0.25</v>
       </c>
-      <c r="E207" s="24" t="s">
+      <c r="E207" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="F207" s="17" t="s">
+      <c r="F207" s="120" t="s">
         <v>499</v>
       </c>
-      <c r="G207" s="20" t="s">
+      <c r="G207" s="121" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A208" s="95" t="s">
+      <c r="A208" s="88">
+        <v>46114</v>
+      </c>
+      <c r="B208" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C208" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="D208" s="116">
+        <v>1</v>
+      </c>
+      <c r="E208" s="92" t="s">
+        <v>502</v>
+      </c>
+      <c r="F208" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="G208" s="106" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A209" s="114">
+        <v>46114</v>
+      </c>
+      <c r="B209" s="115" t="s">
+        <v>466</v>
+      </c>
+      <c r="C209" s="115" t="s">
+        <v>128</v>
+      </c>
+      <c r="D209" s="117">
+        <v>0.75</v>
+      </c>
+      <c r="E209" s="92" t="s">
+        <v>502</v>
+      </c>
+      <c r="F209" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="G209" s="106" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A210" s="88">
+        <v>46114</v>
+      </c>
+      <c r="B210" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C210" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="D210" s="116">
+        <v>0.5</v>
+      </c>
+      <c r="E210" s="92" t="s">
+        <v>502</v>
+      </c>
+      <c r="F210" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="G210" s="106" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A211" s="88">
+        <v>46114</v>
+      </c>
+      <c r="B211" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C211" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="D211" s="116">
+        <v>1</v>
+      </c>
+      <c r="E211" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F211" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="G211" s="106" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A212" s="88">
+        <v>46114</v>
+      </c>
+      <c r="B212" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C212" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="D212" s="116">
+        <v>0.75</v>
+      </c>
+      <c r="E212" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F212" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="G212" s="106" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A213" s="88">
+        <v>46114</v>
+      </c>
+      <c r="B213" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C213" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="D213" s="116">
+        <v>0.75</v>
+      </c>
+      <c r="E213" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F213" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="G213" s="106" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A214" s="88">
+        <v>46114</v>
+      </c>
+      <c r="B214" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C214" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="D214" s="116">
+        <v>0.5</v>
+      </c>
+      <c r="E214" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F214" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="G214" s="106" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A215" s="88">
+        <v>46114</v>
+      </c>
+      <c r="B215" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C215" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="D215" s="116">
+        <v>0.5</v>
+      </c>
+      <c r="E215" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F215" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="G215" s="106" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A216" s="88">
+        <v>46114</v>
+      </c>
+      <c r="B216" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C216" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="D216" s="116">
+        <v>0.75</v>
+      </c>
+      <c r="E216" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F216" s="17" t="s">
+        <v>520</v>
+      </c>
+      <c r="G216" s="106" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A217" s="88">
+        <v>46115</v>
+      </c>
+      <c r="B217" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C217" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="D217" s="116">
+        <v>0.5</v>
+      </c>
+      <c r="E217" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F217" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="G217" s="106" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A218" s="88">
+        <v>46115</v>
+      </c>
+      <c r="B218" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C218" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="D218" s="116">
+        <v>1</v>
+      </c>
+      <c r="E218" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F218" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="G218" s="106" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A219" s="88">
+        <v>46115</v>
+      </c>
+      <c r="B219" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C219" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="D219" s="116">
+        <v>0.75</v>
+      </c>
+      <c r="E219" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F219" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="G219" s="106" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A220" s="88">
+        <v>46115</v>
+      </c>
+      <c r="B220" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C220" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="D220" s="116">
+        <v>0.5</v>
+      </c>
+      <c r="E220" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F220" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="G220" s="106" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A221" s="88">
+        <v>46115</v>
+      </c>
+      <c r="B221" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C221" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="D221" s="116">
+        <v>0.75</v>
+      </c>
+      <c r="E221" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F221" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="G221" s="106" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A222" s="88">
+        <v>46115</v>
+      </c>
+      <c r="B222" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C222" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="D222" s="116">
+        <v>0.75</v>
+      </c>
+      <c r="E222" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F222" s="17" t="s">
+        <v>532</v>
+      </c>
+      <c r="G222" s="106" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A223" s="88">
+        <v>46115</v>
+      </c>
+      <c r="B223" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="C223" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="D223" s="116">
+        <v>0.5</v>
+      </c>
+      <c r="E223" s="92" t="s">
+        <v>509</v>
+      </c>
+      <c r="F223" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="G223" s="106" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A224" s="88">
+        <v>46116</v>
+      </c>
+      <c r="B224" s="85" t="s">
+        <v>536</v>
+      </c>
+      <c r="C224" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D224" s="116">
+        <v>2</v>
+      </c>
+      <c r="E224" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F224" s="125">
+        <v>6.1</v>
+      </c>
+      <c r="G224" s="106" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A225" s="88">
+        <v>46116</v>
+      </c>
+      <c r="B225" s="85" t="s">
+        <v>536</v>
+      </c>
+      <c r="C225" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D225" s="116">
+        <v>2</v>
+      </c>
+      <c r="E225" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F225" s="125">
+        <v>6.2</v>
+      </c>
+      <c r="G225" s="106" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A226" s="88">
+        <v>46116</v>
+      </c>
+      <c r="B226" s="85" t="s">
+        <v>536</v>
+      </c>
+      <c r="C226" s="85" t="s">
+        <v>427</v>
+      </c>
+      <c r="D226" s="116">
+        <v>1.5</v>
+      </c>
+      <c r="E226" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F226" s="125">
+        <v>6.3</v>
+      </c>
+      <c r="G226" s="106" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A227" s="88">
+        <v>46116</v>
+      </c>
+      <c r="B227" s="85" t="s">
+        <v>536</v>
+      </c>
+      <c r="C227" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="D227" s="116">
+        <v>1</v>
+      </c>
+      <c r="E227" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F227" s="125">
+        <v>6.4</v>
+      </c>
+      <c r="G227" s="106" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A228" s="88">
+        <v>46117</v>
+      </c>
+      <c r="B228" s="85" t="s">
+        <v>536</v>
+      </c>
+      <c r="C228" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D228" s="116">
+        <v>2</v>
+      </c>
+      <c r="E228" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F228" s="125">
+        <v>6.5</v>
+      </c>
+      <c r="G228" s="106" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A229" s="88">
+        <v>46117</v>
+      </c>
+      <c r="B229" s="85" t="s">
+        <v>536</v>
+      </c>
+      <c r="C229" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="D229" s="116">
+        <v>1</v>
+      </c>
+      <c r="E229" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F229" s="125">
+        <v>6.6</v>
+      </c>
+      <c r="G229" s="106" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A230" s="88">
+        <v>46117</v>
+      </c>
+      <c r="B230" s="85" t="s">
+        <v>536</v>
+      </c>
+      <c r="C230" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="D230" s="116">
+        <v>1</v>
+      </c>
+      <c r="E230" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F230" s="125">
+        <v>6.7</v>
+      </c>
+      <c r="G230" s="106" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A231" s="88">
+        <v>46118</v>
+      </c>
+      <c r="B231" s="85" t="s">
+        <v>536</v>
+      </c>
+      <c r="C231" s="85" t="s">
+        <v>427</v>
+      </c>
+      <c r="D231" s="116">
+        <v>1.5</v>
+      </c>
+      <c r="E231" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F231" s="125">
+        <v>6.8</v>
+      </c>
+      <c r="G231" s="106" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A232" s="88">
+        <v>46118</v>
+      </c>
+      <c r="B232" s="85" t="s">
+        <v>536</v>
+      </c>
+      <c r="C232" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="D232" s="116">
+        <v>0.75</v>
+      </c>
+      <c r="E232" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F232" s="125">
+        <v>6.9</v>
+      </c>
+      <c r="G232" s="106" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A233" s="108">
+        <v>46118</v>
+      </c>
+      <c r="B233" s="109" t="s">
+        <v>536</v>
+      </c>
+      <c r="C233" s="109" t="s">
+        <v>74</v>
+      </c>
+      <c r="D233" s="118">
+        <v>0.5</v>
+      </c>
+      <c r="E233" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F233" s="125">
+        <v>6.1</v>
+      </c>
+      <c r="G233" s="106" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A234" s="88">
+        <v>46118</v>
+      </c>
+      <c r="B234" s="85" t="s">
+        <v>536</v>
+      </c>
+      <c r="C234" s="85" t="s">
+        <v>43</v>
+      </c>
+      <c r="D234" s="116">
+        <v>0.25</v>
+      </c>
+      <c r="E234" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F234" s="125">
+        <v>6.11</v>
+      </c>
+      <c r="G234" s="106" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A235" s="111" t="s">
         <v>137</v>
       </c>
-      <c r="B208" s="96"/>
-      <c r="C208" s="96"/>
-      <c r="D208" s="97"/>
-      <c r="E208" s="73">
-        <f>SUM(D6:D207)</f>
-        <v>160.6</v>
-      </c>
-      <c r="F208" s="18"/>
-      <c r="G208" s="21"/>
+      <c r="B235" s="112"/>
+      <c r="C235" s="112"/>
+      <c r="D235" s="113"/>
+      <c r="E235" s="122">
+        <f>SUM(D6:D234)</f>
+        <v>185.35</v>
+      </c>
+      <c r="F235" s="123"/>
+      <c r="G235" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A208:D208"/>
+    <mergeCell ref="A235:D235"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E260">
+  <conditionalFormatting sqref="E6:E287">
     <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"0: Environment Setup"</formula>
     </cfRule>
@@ -7400,7 +8289,7 @@
           <x14:formula1>
             <xm:f>Categories!$A$4:$A$25</xm:f>
           </x14:formula1>
-          <xm:sqref>E6:E260</xm:sqref>
+          <xm:sqref>E6:E287</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7418,760 +8307,760 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="105" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
     </row>
     <row r="3" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="107" t="s">
+      <c r="A3" s="102" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="31" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="34">
+      <c r="A5" s="32">
         <v>0</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="34">
         <v>5</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="35">
         <f>B46</f>
         <v>11.85</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="36">
         <f t="shared" ref="E5:E11" si="0">IF(C5=0,0,MIN(D5/C5,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="39">
+      <c r="A6" s="37">
         <v>1</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="34">
         <v>15</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="35">
         <f>SUM(B47:B51)</f>
         <v>14.26</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="36">
         <f t="shared" si="0"/>
         <v>0.95066666666666666</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="41">
+      <c r="A7" s="39">
         <v>2</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="34">
         <v>25</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="35">
         <f>SUM(B52:B55)</f>
         <v>29.990000000000002</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="36">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="43">
+      <c r="A8" s="41">
         <v>3</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="42" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="34">
         <v>20</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="35">
         <f>SUM(B56:B60)</f>
         <v>36.75</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="36">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="45">
+      <c r="A9" s="43">
         <v>4</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="34">
         <v>20</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="35">
         <f>SUM(B61:B62)</f>
         <v>8</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="36">
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="47">
+      <c r="A10" s="45">
         <v>5</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="34">
         <v>15</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="35">
         <f>SUM(B63:B64)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="49">
+      <c r="A11" s="47">
         <v>6</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="34">
         <v>18</v>
       </c>
-      <c r="D11" s="37">
+      <c r="D11" s="35">
         <f>SUM(B65)</f>
-        <v>15</v>
-      </c>
-      <c r="E11" s="38">
+        <v>28.5</v>
+      </c>
+      <c r="E11" s="36">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="49" t="s">
         <v>151</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="53">
+      <c r="B12" s="50"/>
+      <c r="C12" s="51">
         <f>SUM(C5:C11)</f>
         <v>118</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="52">
         <f>SUM(D5:D11)</f>
-        <v>115.85</v>
-      </c>
-      <c r="E12" s="55">
+        <v>129.35</v>
+      </c>
+      <c r="E12" s="53">
         <f>IF(C12=0,0,D12/C12)</f>
-        <v>0.98177966101694913</v>
+        <v>1.096186440677966</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="108" t="s">
+      <c r="A14" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="B14" s="109"/>
-      <c r="C14" s="109"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="109"/>
-      <c r="G14" s="109"/>
-      <c r="H14" s="109"/>
-      <c r="I14" s="109"/>
-      <c r="J14" s="109"/>
-      <c r="K14" s="109"/>
-      <c r="L14" s="109"/>
-      <c r="M14" s="109"/>
-      <c r="N14" s="109"/>
+      <c r="B14" s="104"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+      <c r="K14" s="104"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="104"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="F15" s="33" t="s">
+      <c r="F15" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="G15" s="33" t="s">
+      <c r="G15" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="H15" s="33" t="s">
+      <c r="H15" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="I15" s="33" t="s">
+      <c r="I15" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="J15" s="33" t="s">
+      <c r="J15" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="K15" s="33" t="s">
+      <c r="K15" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="L15" s="33" t="s">
+      <c r="L15" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="M15" s="33" t="s">
+      <c r="M15" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="N15" s="33" t="s">
+      <c r="N15" s="31" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="56"/>
-      <c r="B16" s="56" t="s">
+      <c r="A16" s="54"/>
+      <c r="B16" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="54" t="s">
         <v>168</v>
       </c>
-      <c r="D16" s="56" t="s">
+      <c r="D16" s="54" t="s">
         <v>169</v>
       </c>
-      <c r="E16" s="56" t="s">
+      <c r="E16" s="54" t="s">
         <v>170</v>
       </c>
-      <c r="F16" s="56" t="s">
+      <c r="F16" s="54" t="s">
         <v>171</v>
       </c>
-      <c r="G16" s="56" t="s">
+      <c r="G16" s="54" t="s">
         <v>172</v>
       </c>
-      <c r="H16" s="56" t="s">
+      <c r="H16" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="I16" s="56" t="s">
+      <c r="I16" s="54" t="s">
         <v>174</v>
       </c>
-      <c r="J16" s="56" t="s">
+      <c r="J16" s="54" t="s">
         <v>175</v>
       </c>
-      <c r="K16" s="56" t="s">
+      <c r="K16" s="54" t="s">
         <v>176</v>
       </c>
-      <c r="L16" s="56" t="s">
+      <c r="L16" s="54" t="s">
         <v>177</v>
       </c>
-      <c r="M16" s="56" t="s">
+      <c r="M16" s="54" t="s">
         <v>178</v>
       </c>
-      <c r="N16" s="56" t="s">
+      <c r="N16" s="54" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="49" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="50"/>
+      <c r="K17" s="50"/>
+      <c r="L17" s="50"/>
+      <c r="M17" s="50"/>
+      <c r="N17" s="50"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="49" t="s">
         <v>181</v>
       </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="52"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="50"/>
+      <c r="K18" s="50"/>
+      <c r="L18" s="50"/>
+      <c r="M18" s="50"/>
+      <c r="N18" s="50"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="80" t="s">
+      <c r="A19" s="77" t="s">
         <v>182</v>
       </c>
-      <c r="B19" s="52"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="52"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="50"/>
+      <c r="N19" s="50"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="77" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="52"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="52"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="52"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
+      <c r="M20" s="50"/>
+      <c r="N20" s="50"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="77" t="s">
         <v>184</v>
       </c>
-      <c r="B21" s="52"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="52"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="50"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="50"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="80" t="s">
+      <c r="A22" s="77" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="52"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="50"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="50"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="80" t="s">
+      <c r="A23" s="77" t="s">
         <v>186</v>
       </c>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="52"/>
-      <c r="L23" s="52"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="52"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="49" t="s">
         <v>187</v>
       </c>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="52"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="52"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="80" t="s">
+      <c r="A25" s="77" t="s">
         <v>188</v>
       </c>
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="60"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="52"/>
-      <c r="K25" s="52"/>
-      <c r="L25" s="52"/>
-      <c r="M25" s="52"/>
-      <c r="N25" s="52"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="50"/>
+      <c r="M25" s="50"/>
+      <c r="N25" s="50"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="80" t="s">
+      <c r="A26" s="77" t="s">
         <v>189</v>
       </c>
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="52"/>
-      <c r="M26" s="52"/>
-      <c r="N26" s="52"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="50"/>
+      <c r="M26" s="50"/>
+      <c r="N26" s="50"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="80" t="s">
+      <c r="A27" s="77" t="s">
         <v>190</v>
       </c>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="52"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="50"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="50"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="80" t="s">
+      <c r="A28" s="77" t="s">
         <v>191</v>
       </c>
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="52"/>
-      <c r="K28" s="52"/>
-      <c r="L28" s="52"/>
-      <c r="M28" s="52"/>
-      <c r="N28" s="52"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="50"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="50"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="51" t="s">
+      <c r="A29" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="61"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="52"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="52"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="50"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="50"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="80" t="s">
+      <c r="A30" s="77" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="52"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="50"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="50"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="80" t="s">
+      <c r="A31" s="77" t="s">
         <v>194</v>
       </c>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="62"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="52"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="52"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="50"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="50"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="80" t="s">
+      <c r="A32" s="77" t="s">
         <v>195</v>
       </c>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="52"/>
-      <c r="N32" s="52"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="50"/>
+      <c r="M32" s="50"/>
+      <c r="N32" s="50"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="80" t="s">
+      <c r="A33" s="77" t="s">
         <v>196</v>
       </c>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="62"/>
-      <c r="K33" s="62"/>
-      <c r="L33" s="52"/>
-      <c r="M33" s="52"/>
-      <c r="N33" s="52"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="60"/>
+      <c r="K33" s="60"/>
+      <c r="L33" s="50"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="50"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="80" t="s">
+      <c r="A34" s="77" t="s">
         <v>381</v>
       </c>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="62"/>
-      <c r="K34" s="62"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="52"/>
-      <c r="N34" s="52"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="50"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="60"/>
+      <c r="L34" s="50"/>
+      <c r="M34" s="50"/>
+      <c r="N34" s="50"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="51" t="s">
+      <c r="A35" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="62"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="60"/>
+      <c r="L35" s="50"/>
+      <c r="M35" s="50"/>
+      <c r="N35" s="50"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="80" t="s">
+      <c r="A36" s="77" t="s">
         <v>198</v>
       </c>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="63" t="s">
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="61" t="s">
         <v>199</v>
       </c>
-      <c r="G36" s="52"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="50"/>
+      <c r="L36" s="50"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="80" t="s">
+      <c r="A37" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="B37" s="52"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="52"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="52"/>
-      <c r="N37" s="63" t="s">
+      <c r="B37" s="50"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="50"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="50"/>
+      <c r="L37" s="50"/>
+      <c r="M37" s="50"/>
+      <c r="N37" s="61" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="51" t="s">
+      <c r="A38" s="49" t="s">
         <v>201</v>
       </c>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="48"/>
-      <c r="K38" s="48"/>
-      <c r="L38" s="48"/>
-      <c r="M38" s="52"/>
-      <c r="N38" s="52"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="50"/>
+      <c r="J38" s="46"/>
+      <c r="K38" s="46"/>
+      <c r="L38" s="46"/>
+      <c r="M38" s="50"/>
+      <c r="N38" s="50"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="80" t="s">
+      <c r="A39" s="77" t="s">
         <v>202</v>
       </c>
-      <c r="B39" s="52"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
-      <c r="L39" s="52"/>
-      <c r="M39" s="52"/>
-      <c r="N39" s="52"/>
+      <c r="B39" s="50"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="50"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="50"/>
+      <c r="M39" s="50"/>
+      <c r="N39" s="50"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="80" t="s">
+      <c r="A40" s="77" t="s">
         <v>203</v>
       </c>
-      <c r="B40" s="52"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="48"/>
-      <c r="L40" s="48"/>
-      <c r="M40" s="52"/>
-      <c r="N40" s="52"/>
+      <c r="B40" s="50"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="50"/>
+      <c r="I40" s="50"/>
+      <c r="J40" s="50"/>
+      <c r="K40" s="46"/>
+      <c r="L40" s="46"/>
+      <c r="M40" s="50"/>
+      <c r="N40" s="50"/>
     </row>
     <row r="41" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="51" t="s">
+      <c r="A41" s="49" t="s">
         <v>204</v>
       </c>
-      <c r="B41" s="52"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="52"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="52"/>
-      <c r="K41" s="52"/>
-      <c r="L41" s="50"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="50"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="50"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
+      <c r="L41" s="48"/>
+      <c r="M41" s="48"/>
+      <c r="N41" s="48"/>
     </row>
     <row r="42" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="79"/>
+      <c r="A42" s="76"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
@@ -8180,245 +9069,245 @@
       <c r="B43" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="74"/>
+      <c r="C43" s="71"/>
     </row>
     <row r="44" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="64" t="s">
+      <c r="A44" s="62" t="s">
         <v>205</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="3"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="33" t="s">
+      <c r="A45" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="B45" s="65" t="s">
+      <c r="B45" s="63" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="3"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="35" t="s">
+      <c r="A46" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="37">
+      <c r="B46" s="35">
         <f>SUMIF('Work Log'!E:E,"0: Environment Setup",'Work Log'!D:D)</f>
         <v>11.85</v>
       </c>
       <c r="C46" s="3"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="40" t="s">
+      <c r="A47" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="B47" s="37">
+      <c r="B47" s="35">
         <f>SUMIF('Work Log'!E:E,"1A: UI Mockups",'Work Log'!D:D)</f>
         <v>2.81</v>
       </c>
       <c r="C47" s="3"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="40" t="s">
+      <c r="A48" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="B48" s="37">
+      <c r="B48" s="35">
         <f>SUMIF('Work Log'!E:E,"1B: Project Structure",'Work Log'!D:D)</f>
         <v>0.67</v>
       </c>
       <c r="C48" s="3"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="40" t="s">
+      <c r="A49" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="37">
+      <c r="B49" s="35">
         <f>SUMIF('Work Log'!E:E,"1C: Database Setup",'Work Log'!D:D)</f>
         <v>3.18</v>
       </c>
       <c r="C49" s="3"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="40" t="s">
+      <c r="A50" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="B50" s="37">
+      <c r="B50" s="35">
         <f>SUMIF('Work Log'!E:E,"1D: Authentication Feature",'Work Log'!D:D)</f>
         <v>6</v>
       </c>
       <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="40" t="s">
+      <c r="A51" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="B51" s="37">
+      <c r="B51" s="35">
         <f>SUMIF('Work Log'!E:E,"1E: Basic Navigation",'Work Log'!D:D)</f>
         <v>1.5999999999999999</v>
       </c>
       <c r="C51" s="3"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="42" t="s">
+      <c r="A52" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="B52" s="37">
+      <c r="B52" s="35">
         <f>SUMIF('Work Log'!E:E,"2A: Open AI Integration",'Work Log'!D:D)</f>
         <v>2.08</v>
       </c>
       <c r="C52" s="3"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="42" t="s">
+      <c r="A53" s="40" t="s">
         <v>209</v>
       </c>
-      <c r="B53" s="37">
+      <c r="B53" s="35">
         <f>SUMIF('Work Log'!E:E,"2B: Safety Layer - CTAS Rules",'Work Log'!D:D)</f>
         <v>2.75</v>
       </c>
       <c r="C53" s="3"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="42" t="s">
+      <c r="A54" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="B54" s="37">
+      <c r="B54" s="35">
         <f>SUMIF('Work Log'!E:E,"2C: ML Model Training",'Work Log'!D:D)</f>
         <v>9</v>
       </c>
       <c r="C54" s="3"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="42" t="s">
+      <c r="A55" s="40" t="s">
         <v>211</v>
       </c>
-      <c r="B55" s="37">
+      <c r="B55" s="35">
         <f>SUMIF('Work Log'!E:E,"2D: Chatbot UI + Integration",'Work Log'!D:D)</f>
         <v>16.16</v>
       </c>
       <c r="C55" s="3"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="44" t="s">
+      <c r="A56" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="B56" s="37">
+      <c r="B56" s="35">
         <f>SUMIF('Work Log'!E:E,"3A: Home Dashboard",'Work Log'!D:D)</f>
         <v>6.75</v>
       </c>
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="44" t="s">
+      <c r="A57" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="B57" s="37">
+      <c r="B57" s="35">
         <f>SUMIF('Work Log'!E:E,"3B: My Dashboard - Personal Analytics ",'Work Log'!D:D)</f>
         <v>11.5</v>
       </c>
       <c r="C57" s="3"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="44" t="s">
+      <c r="A58" s="42" t="s">
         <v>214</v>
       </c>
-      <c r="B58" s="37">
+      <c r="B58" s="35">
         <f>SUMIF('Work Log'!E:E,"3C: Facility Finder",'Work Log'!D:D)</f>
         <v>3.5</v>
       </c>
       <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="44" t="s">
+      <c r="A59" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="B59" s="37">
+      <c r="B59" s="35">
         <f>SUMIF('Work Log'!E:E,"3D: Health Education Library",'Work Log'!D:D)</f>
         <v>10.25</v>
       </c>
       <c r="C59" s="3"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="44" t="s">
+      <c r="A60" s="42" t="s">
         <v>413</v>
       </c>
-      <c r="B60" s="37">
+      <c r="B60" s="35">
         <f>SUMIF('Work Log'!E:E,"3E: Multi-Turn Chatbot Enhancement",'Work Log'!D:D)</f>
         <v>4.75</v>
       </c>
       <c r="C60" s="3"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="46" t="s">
+      <c r="A61" s="44" t="s">
         <v>216</v>
       </c>
-      <c r="B61" s="37">
+      <c r="B61" s="35">
         <f>SUMIF('Work Log'!E:E,"4A: System Analytics Data",'Work Log'!D:D)</f>
         <v>2.75</v>
       </c>
       <c r="C61" s="3"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="46" t="s">
+      <c r="A62" s="44" t="s">
         <v>217</v>
       </c>
-      <c r="B62" s="37">
+      <c r="B62" s="35">
         <f>SUMIF('Work Log'!E:E,"4B: System Analytics Dashboard",'Work Log'!D:D)</f>
         <v>5.25</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="48" t="s">
+      <c r="A63" s="46" t="s">
         <v>218</v>
       </c>
-      <c r="B63" s="37">
+      <c r="B63" s="35">
         <f>SUMIF('Work Log'!E:E,"5A: Deployment",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="48" t="s">
+      <c r="A64" s="46" t="s">
         <v>219</v>
       </c>
-      <c r="B64" s="37">
+      <c r="B64" s="35">
         <f>SUMIF('Work Log'!E:E,"5B: Testing",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="50" t="s">
+      <c r="A65" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="B65" s="37">
+      <c r="B65" s="35">
         <f>SUMIF('Work Log'!E:E,"6: Documentation + Submission",'Work Log'!D:D)</f>
-        <v>15</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="66" t="s">
+      <c r="A66" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B66" s="37">
+      <c r="B66" s="35">
         <f>SUMIF('Work Log'!E:E,"Learning &amp; Research",'Work Log'!D:D)</f>
         <v>23.25</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="67" t="s">
+      <c r="A67" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="B67" s="54">
+      <c r="B67" s="52">
         <f>SUMIF('Work Log'!E:E,"Proof of Concept",'Work Log'!D:D)</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="51" t="s">
+      <c r="A68" s="49" t="s">
         <v>151</v>
       </c>
-      <c r="B68" s="93">
+      <c r="B68" s="90">
         <f>SUM(B46:B67)</f>
-        <v>139.10000000000002</v>
+        <v>152.60000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -8664,7 +9553,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="30" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="8">
